--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6780" tabRatio="500" firstSheet="2"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="R2" t="str">
         <f ca="1">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-05-21</v>
+        <v>2025-01-12</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="R3" t="str">
         <f ca="1" t="shared" ref="R3:R12" si="0">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-09-08</v>
+        <v>2024-08-17</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="R4" t="str">
         <f ca="1" t="shared" si="0"/>
-        <v>2025-09-07</v>
+        <v>2025-04-25</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="R5" t="str">
         <f ca="1" t="shared" si="0"/>
-        <v>2025-02-19</v>
+        <v>2024-10-11</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="R6" t="str">
         <f ca="1" t="shared" si="0"/>
-        <v>2024-11-29</v>
+        <v>2025-05-12</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="R7" t="str">
         <f ca="1" t="shared" si="0"/>
-        <v>2024-08-04</v>
+        <v>2024-11-21</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="R8" t="str">
         <f ca="1" t="shared" si="0"/>
-        <v>2025-04-08</v>
+        <v>2024-10-16</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="R9" t="str">
         <f ca="1" t="shared" si="0"/>
-        <v>2025-03-22</v>
+        <v>2025-05-05</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="R10" t="str">
         <f ca="1" t="shared" si="0"/>
-        <v>2025-05-28</v>
+        <v>2025-07-16</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="R11" t="str">
         <f ca="1" t="shared" si="0"/>
-        <v>2025-05-27</v>
+        <v>2025-06-08</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="R12" t="str">
         <f ca="1" t="shared" si="0"/>
-        <v>2024-11-27</v>
+        <v>2024-08-24</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="R13" t="str">
         <f ca="1" t="shared" ref="R13:R22" si="1">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-09-30</v>
+        <v>2025-06-22</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="R14" t="str">
         <f ca="1" t="shared" si="1"/>
-        <v>2024-10-18</v>
+        <v>2025-01-30</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="R15" t="str">
         <f ca="1" t="shared" si="1"/>
-        <v>2025-09-19</v>
+        <v>2024-08-14</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="R16" t="str">
         <f ca="1" t="shared" si="1"/>
-        <v>2024-11-01</v>
+        <v>2024-08-17</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="R17" t="str">
         <f ca="1" t="shared" si="1"/>
-        <v>2025-04-19</v>
+        <v>2024-08-12</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="R18" t="str">
         <f ca="1" t="shared" si="1"/>
-        <v>2024-09-18</v>
+        <v>2024-09-27</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="R19" t="str">
         <f ca="1" t="shared" si="1"/>
-        <v>2024-08-19</v>
+        <v>2025-05-27</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="R20" t="str">
         <f ca="1" t="shared" si="1"/>
-        <v>2025-09-24</v>
+        <v>2025-04-18</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="R21" t="str">
         <f ca="1" t="shared" si="1"/>
-        <v>2025-06-03</v>
+        <v>2024-08-02</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="R22" t="str">
         <f ca="1" t="shared" si="1"/>
-        <v>2025-04-29</v>
+        <v>2025-08-21</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="R23" t="str">
         <f ca="1" t="shared" ref="R23:R32" si="2">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-02-08</v>
+        <v>2025-08-28</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="R24" t="str">
         <f ca="1" t="shared" si="2"/>
-        <v>2024-11-07</v>
+        <v>2025-04-29</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="R25" t="str">
         <f ca="1" t="shared" si="2"/>
-        <v>2025-06-02</v>
+        <v>2025-06-11</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="R26" t="str">
         <f ca="1" t="shared" si="2"/>
-        <v>2025-08-11</v>
+        <v>2025-09-16</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="R27" t="str">
         <f ca="1" t="shared" si="2"/>
-        <v>2025-07-10</v>
+        <v>2025-05-27</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="R28" t="str">
         <f ca="1" t="shared" si="2"/>
-        <v>2024-10-09</v>
+        <v>2025-09-14</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="R29" t="str">
         <f ca="1" t="shared" si="2"/>
-        <v>2024-10-23</v>
+        <v>2024-12-22</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="R30" t="str">
         <f ca="1" t="shared" si="2"/>
-        <v>2025-09-06</v>
+        <v>2025-01-17</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="R31" t="str">
         <f ca="1" t="shared" si="2"/>
-        <v>2025-09-02</v>
+        <v>2025-09-18</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="R32" t="str">
         <f ca="1" t="shared" si="2"/>
-        <v>2025-03-28</v>
+        <v>2025-09-08</v>
       </c>
     </row>
     <row r="33" spans="1:18">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="R33" t="str">
         <f ca="1" t="shared" ref="R33:R42" si="3">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-09-23</v>
+        <v>2025-07-16</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="R34" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>2025-01-25</v>
+        <v>2025-02-22</v>
       </c>
     </row>
     <row r="35" spans="1:18">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="R35" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>2025-04-26</v>
+        <v>2025-03-29</v>
       </c>
     </row>
     <row r="36" spans="1:18">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="R36" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>2025-09-15</v>
+        <v>2025-02-24</v>
       </c>
     </row>
     <row r="37" spans="1:18">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="R37" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>2024-11-25</v>
+        <v>2024-11-22</v>
       </c>
     </row>
     <row r="38" spans="1:18">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="R38" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>2024-08-26</v>
+        <v>2024-09-16</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="R39" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>2025-03-14</v>
+        <v>2025-04-02</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="R40" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>2025-08-28</v>
+        <v>2025-03-08</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="R41" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>2025-09-16</v>
+        <v>2025-05-28</v>
       </c>
     </row>
     <row r="42" spans="1:18">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="R42" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>2025-01-15</v>
+        <v>2025-07-06</v>
       </c>
     </row>
     <row r="43" spans="1:18">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="R43" t="str">
         <f ca="1" t="shared" ref="R43:R52" si="4">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-06-20</v>
+        <v>2024-10-22</v>
       </c>
     </row>
     <row r="44" spans="1:18">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="R44" t="str">
         <f ca="1" t="shared" si="4"/>
-        <v>2025-06-30</v>
+        <v>2024-08-28</v>
       </c>
     </row>
     <row r="45" spans="1:18">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="R45" t="str">
         <f ca="1" t="shared" si="4"/>
-        <v>2025-07-19</v>
+        <v>2025-01-08</v>
       </c>
     </row>
     <row r="46" spans="1:18">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="R46" t="str">
         <f ca="1" t="shared" si="4"/>
-        <v>2025-05-14</v>
+        <v>2025-09-05</v>
       </c>
     </row>
     <row r="47" spans="1:18">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="R47" t="str">
         <f ca="1" t="shared" si="4"/>
-        <v>2024-12-24</v>
+        <v>2025-02-21</v>
       </c>
     </row>
     <row r="48" spans="1:18">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="R48" t="str">
         <f ca="1" t="shared" si="4"/>
-        <v>2025-06-18</v>
+        <v>2024-10-08</v>
       </c>
     </row>
     <row r="49" spans="1:18">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="R49" t="str">
         <f ca="1" t="shared" si="4"/>
-        <v>2024-09-06</v>
+        <v>2024-08-01</v>
       </c>
     </row>
     <row r="50" spans="1:18">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="R50" t="str">
         <f ca="1" t="shared" si="4"/>
-        <v>2025-05-30</v>
+        <v>2025-03-04</v>
       </c>
     </row>
     <row r="51" spans="1:18">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="R51" t="str">
         <f ca="1" t="shared" si="4"/>
-        <v>2025-08-02</v>
+        <v>2025-07-05</v>
       </c>
     </row>
     <row r="52" spans="1:18">
@@ -9111,7 +9111,7 @@
       </c>
       <c r="R52" t="str">
         <f ca="1" t="shared" si="4"/>
-        <v>2024-10-09</v>
+        <v>2024-09-02</v>
       </c>
     </row>
     <row r="53" spans="1:18">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="R53" t="str">
         <f ca="1" t="shared" ref="R53:R62" si="5">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-08-08</v>
+        <v>2025-04-25</v>
       </c>
     </row>
     <row r="54" spans="1:18">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="R54" t="str">
         <f ca="1" t="shared" si="5"/>
-        <v>2025-07-14</v>
+        <v>2025-02-08</v>
       </c>
     </row>
     <row r="55" spans="1:18">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="R55" t="str">
         <f ca="1" t="shared" si="5"/>
-        <v>2025-08-28</v>
+        <v>2025-02-26</v>
       </c>
     </row>
     <row r="56" spans="1:18">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="R56" t="str">
         <f ca="1" t="shared" si="5"/>
-        <v>2025-01-15</v>
+        <v>2024-12-13</v>
       </c>
     </row>
     <row r="57" spans="1:18">
@@ -9390,7 +9390,7 @@
       </c>
       <c r="R57" t="str">
         <f ca="1" t="shared" si="5"/>
-        <v>2024-09-15</v>
+        <v>2025-10-08</v>
       </c>
     </row>
     <row r="58" spans="1:18">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="R58" t="str">
         <f ca="1" t="shared" si="5"/>
-        <v>2025-04-23</v>
+        <v>2025-04-04</v>
       </c>
     </row>
     <row r="59" spans="1:18">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="R59" t="str">
         <f ca="1" t="shared" si="5"/>
-        <v>2024-08-30</v>
+        <v>2025-03-29</v>
       </c>
     </row>
     <row r="60" spans="1:18">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="R60" t="str">
         <f ca="1" t="shared" si="5"/>
-        <v>2025-01-20</v>
+        <v>2024-12-09</v>
       </c>
     </row>
     <row r="61" spans="1:18">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="R61" t="str">
         <f ca="1" t="shared" si="5"/>
-        <v>2025-03-09</v>
+        <v>2024-10-22</v>
       </c>
     </row>
     <row r="62" spans="1:18">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="R62" t="str">
         <f ca="1" t="shared" si="5"/>
-        <v>2024-08-09</v>
+        <v>2025-08-27</v>
       </c>
     </row>
     <row r="63" spans="1:18">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="R63" t="str">
         <f ca="1" t="shared" ref="R63:R72" si="6">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-03-15</v>
+        <v>2025-02-13</v>
       </c>
     </row>
     <row r="64" spans="1:18">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="R64" t="str">
         <f ca="1" t="shared" si="6"/>
-        <v>2025-01-28</v>
+        <v>2025-07-22</v>
       </c>
     </row>
     <row r="65" spans="1:18">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="R65" t="str">
         <f ca="1" t="shared" si="6"/>
-        <v>2024-08-01</v>
+        <v>2025-04-07</v>
       </c>
     </row>
     <row r="66" spans="1:18">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="R66" t="str">
         <f ca="1" t="shared" si="6"/>
-        <v>2025-06-19</v>
+        <v>2025-06-07</v>
       </c>
     </row>
     <row r="67" spans="1:18">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="R67" t="str">
         <f ca="1" t="shared" si="6"/>
-        <v>2025-07-02</v>
+        <v>2025-07-11</v>
       </c>
     </row>
     <row r="68" spans="1:18">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="R68" t="str">
         <f ca="1" t="shared" si="6"/>
-        <v>2024-10-10</v>
+        <v>2025-08-15</v>
       </c>
     </row>
     <row r="69" spans="1:18">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="R69" t="str">
         <f ca="1" t="shared" si="6"/>
-        <v>2025-09-29</v>
+        <v>2025-03-19</v>
       </c>
     </row>
     <row r="70" spans="1:18">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="R70" t="str">
         <f ca="1" t="shared" si="6"/>
-        <v>2025-03-03</v>
+        <v>2025-01-29</v>
       </c>
     </row>
     <row r="71" spans="1:18">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="R71" t="str">
         <f ca="1" t="shared" si="6"/>
-        <v>2025-04-06</v>
+        <v>2025-09-22</v>
       </c>
     </row>
     <row r="72" spans="1:18">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="R72" t="str">
         <f ca="1" t="shared" si="6"/>
-        <v>2024-09-26</v>
+        <v>2025-01-30</v>
       </c>
     </row>
     <row r="73" spans="1:18">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="R73" t="str">
         <f ca="1" t="shared" ref="R73:R82" si="7">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-02-15</v>
+        <v>2025-03-05</v>
       </c>
     </row>
     <row r="74" spans="1:18">
@@ -10357,7 +10357,7 @@
       </c>
       <c r="R74" t="str">
         <f ca="1" t="shared" si="7"/>
-        <v>2024-10-09</v>
+        <v>2025-06-18</v>
       </c>
     </row>
     <row r="75" spans="1:18">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="R75" t="str">
         <f ca="1" t="shared" si="7"/>
-        <v>2025-07-01</v>
+        <v>2025-07-12</v>
       </c>
     </row>
     <row r="76" spans="1:18">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="R76" t="str">
         <f ca="1" t="shared" si="7"/>
-        <v>2025-05-11</v>
+        <v>2025-01-20</v>
       </c>
     </row>
     <row r="77" spans="1:18">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="R77" t="str">
         <f ca="1" t="shared" si="7"/>
-        <v>2024-09-03</v>
+        <v>2025-07-06</v>
       </c>
     </row>
     <row r="78" spans="1:18">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="R78" t="str">
         <f ca="1" t="shared" si="7"/>
-        <v>2024-12-21</v>
+        <v>2024-08-20</v>
       </c>
     </row>
     <row r="79" spans="1:18">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="R79" t="str">
         <f ca="1" t="shared" si="7"/>
-        <v>2025-06-09</v>
+        <v>2024-12-11</v>
       </c>
     </row>
     <row r="80" spans="1:18">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="R80" t="str">
         <f ca="1" t="shared" si="7"/>
-        <v>2024-08-02</v>
+        <v>2024-12-30</v>
       </c>
     </row>
     <row r="81" spans="1:18">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="R81" t="str">
         <f ca="1" t="shared" si="7"/>
-        <v>2025-06-10</v>
+        <v>2024-09-06</v>
       </c>
     </row>
     <row r="82" spans="1:18">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="R82" t="str">
         <f ca="1" t="shared" si="7"/>
-        <v>2025-01-27</v>
+        <v>2024-10-25</v>
       </c>
     </row>
     <row r="83" spans="1:18">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="R83" t="str">
         <f ca="1" t="shared" ref="R83:R92" si="8">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-08-05</v>
+        <v>2025-02-24</v>
       </c>
     </row>
     <row r="84" spans="1:18">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="R84" t="str">
         <f ca="1" t="shared" si="8"/>
-        <v>2024-11-27</v>
+        <v>2025-02-15</v>
       </c>
     </row>
     <row r="85" spans="1:18">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="R85" t="str">
         <f ca="1" t="shared" si="8"/>
-        <v>2024-12-10</v>
+        <v>2024-09-25</v>
       </c>
     </row>
     <row r="86" spans="1:18">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="R86" t="str">
         <f ca="1" t="shared" si="8"/>
-        <v>2024-11-21</v>
+        <v>2024-10-03</v>
       </c>
     </row>
     <row r="87" spans="1:18">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="R87" t="str">
         <f ca="1" t="shared" si="8"/>
-        <v>2025-02-03</v>
+        <v>2025-04-13</v>
       </c>
     </row>
     <row r="88" spans="1:18">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="R88" t="str">
         <f ca="1" t="shared" si="8"/>
-        <v>2025-06-02</v>
+        <v>2024-09-10</v>
       </c>
     </row>
     <row r="89" spans="1:18">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="R89" t="str">
         <f ca="1" t="shared" si="8"/>
-        <v>2025-08-12</v>
+        <v>2025-08-07</v>
       </c>
     </row>
     <row r="90" spans="1:18">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="R90" t="str">
         <f ca="1" t="shared" si="8"/>
-        <v>2024-10-07</v>
+        <v>2025-06-27</v>
       </c>
     </row>
     <row r="91" spans="1:18">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="R91" t="str">
         <f ca="1" t="shared" si="8"/>
-        <v>2025-08-29</v>
+        <v>2025-04-15</v>
       </c>
     </row>
     <row r="92" spans="1:18">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="R92" t="str">
         <f ca="1" t="shared" si="8"/>
-        <v>2025-01-14</v>
+        <v>2024-12-09</v>
       </c>
     </row>
     <row r="93" spans="1:18">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="R93" t="str">
         <f ca="1" t="shared" ref="R93:R102" si="9">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-05-14</v>
+        <v>2025-08-18</v>
       </c>
     </row>
     <row r="94" spans="1:18">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="R94" t="str">
         <f ca="1" t="shared" si="9"/>
-        <v>2025-04-05</v>
+        <v>2025-01-07</v>
       </c>
     </row>
     <row r="95" spans="1:18">
@@ -11547,7 +11547,7 @@
       </c>
       <c r="R95" t="str">
         <f ca="1" t="shared" si="9"/>
-        <v>2025-06-23</v>
+        <v>2024-12-17</v>
       </c>
     </row>
     <row r="96" spans="1:18">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="R96" t="str">
         <f ca="1" t="shared" si="9"/>
-        <v>2025-01-25</v>
+        <v>2025-09-15</v>
       </c>
     </row>
     <row r="97" spans="1:18">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="R97" t="str">
         <f ca="1" t="shared" si="9"/>
-        <v>2024-12-14</v>
+        <v>2025-10-07</v>
       </c>
     </row>
     <row r="98" spans="1:18">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="R98" t="str">
         <f ca="1" t="shared" si="9"/>
-        <v>2025-06-27</v>
+        <v>2024-12-13</v>
       </c>
     </row>
     <row r="99" spans="1:18">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="R99" t="str">
         <f ca="1" t="shared" si="9"/>
-        <v>2025-04-23</v>
+        <v>2024-11-05</v>
       </c>
     </row>
     <row r="100" spans="1:18">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="R100" t="str">
         <f ca="1" t="shared" si="9"/>
-        <v>2024-09-20</v>
+        <v>2025-09-09</v>
       </c>
     </row>
     <row r="101" spans="1:18">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="R101" t="str">
         <f ca="1" t="shared" si="9"/>
-        <v>2025-06-02</v>
+        <v>2024-09-23</v>
       </c>
     </row>
     <row r="102" spans="1:18">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="R102" t="str">
         <f ca="1" t="shared" si="9"/>
-        <v>2025-09-29</v>
+        <v>2024-09-05</v>
       </c>
     </row>
     <row r="103" spans="1:18">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="R103" t="str">
         <f ca="1" t="shared" ref="R103:R112" si="10">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-06-13</v>
+        <v>2025-08-02</v>
       </c>
     </row>
     <row r="104" spans="1:18">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="R104" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>2025-09-01</v>
+        <v>2024-10-04</v>
       </c>
     </row>
     <row r="105" spans="1:18">
@@ -12110,7 +12110,7 @@
       </c>
       <c r="R105" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>2025-08-08</v>
+        <v>2025-01-10</v>
       </c>
     </row>
     <row r="106" spans="1:18">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="R106" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>2025-04-01</v>
+        <v>2025-03-10</v>
       </c>
     </row>
     <row r="107" spans="1:18">
@@ -12221,7 +12221,7 @@
       </c>
       <c r="R107" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>2025-10-03</v>
+        <v>2025-08-23</v>
       </c>
     </row>
     <row r="108" spans="1:18">
@@ -12278,7 +12278,7 @@
       </c>
       <c r="R108" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>2025-04-15</v>
+        <v>2025-04-05</v>
       </c>
     </row>
     <row r="109" spans="1:18">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="R109" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>2025-05-22</v>
+        <v>2024-08-13</v>
       </c>
     </row>
     <row r="110" spans="1:18">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="R110" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>2025-07-05</v>
+        <v>2025-08-19</v>
       </c>
     </row>
     <row r="111" spans="1:18">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="R111" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>2025-09-24</v>
+        <v>2024-12-04</v>
       </c>
     </row>
     <row r="112" spans="1:18">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="R112" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>2025-01-02</v>
+        <v>2024-12-06</v>
       </c>
     </row>
     <row r="113" spans="1:18">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="R113" t="str">
         <f ca="1" t="shared" ref="R113:R122" si="11">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-05-10</v>
+        <v>2025-03-07</v>
       </c>
     </row>
     <row r="114" spans="1:18">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="R114" t="str">
         <f ca="1" t="shared" si="11"/>
-        <v>2024-08-30</v>
+        <v>2024-08-29</v>
       </c>
     </row>
     <row r="115" spans="1:18">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="R115" t="str">
         <f ca="1" t="shared" si="11"/>
-        <v>2024-11-09</v>
+        <v>2025-09-20</v>
       </c>
     </row>
     <row r="116" spans="1:18">
@@ -12722,7 +12722,7 @@
       </c>
       <c r="R116" t="str">
         <f ca="1" t="shared" si="11"/>
-        <v>2025-03-13</v>
+        <v>2025-09-23</v>
       </c>
     </row>
     <row r="117" spans="1:18">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="R117" t="str">
         <f ca="1" t="shared" si="11"/>
-        <v>2025-01-23</v>
+        <v>2024-11-19</v>
       </c>
     </row>
     <row r="118" spans="1:18">
@@ -12838,7 +12838,7 @@
       </c>
       <c r="R118" t="str">
         <f ca="1" t="shared" si="11"/>
-        <v>2025-04-24</v>
+        <v>2024-12-23</v>
       </c>
     </row>
     <row r="119" spans="1:18">
@@ -12896,7 +12896,7 @@
       </c>
       <c r="R119" t="str">
         <f ca="1" t="shared" si="11"/>
-        <v>2025-09-06</v>
+        <v>2025-07-12</v>
       </c>
     </row>
     <row r="120" spans="1:18">
@@ -12950,7 +12950,7 @@
       </c>
       <c r="R120" t="str">
         <f ca="1" t="shared" si="11"/>
-        <v>2025-03-15</v>
+        <v>2025-01-31</v>
       </c>
     </row>
     <row r="121" spans="1:18">
@@ -13004,7 +13004,7 @@
       </c>
       <c r="R121" t="str">
         <f ca="1" t="shared" si="11"/>
-        <v>2025-06-28</v>
+        <v>2025-09-21</v>
       </c>
     </row>
     <row r="122" spans="1:18">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="R122" t="str">
         <f ca="1" t="shared" si="11"/>
-        <v>2024-11-07</v>
+        <v>2025-07-11</v>
       </c>
     </row>
     <row r="123" spans="1:18">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="R123" t="str">
         <f ca="1" t="shared" ref="R123:R132" si="12">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-05-02</v>
+        <v>2025-04-24</v>
       </c>
     </row>
     <row r="124" spans="1:18">
@@ -13170,7 +13170,7 @@
       </c>
       <c r="R124" t="str">
         <f ca="1" t="shared" si="12"/>
-        <v>2024-11-05</v>
+        <v>2024-09-14</v>
       </c>
     </row>
     <row r="125" spans="1:18">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="R125" t="str">
         <f ca="1" t="shared" si="12"/>
-        <v>2025-01-18</v>
+        <v>2025-04-01</v>
       </c>
     </row>
     <row r="126" spans="1:18">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="R126" t="str">
         <f ca="1" t="shared" si="12"/>
-        <v>2025-04-21</v>
+        <v>2024-10-04</v>
       </c>
     </row>
     <row r="127" spans="1:18">
@@ -13332,7 +13332,7 @@
       </c>
       <c r="R127" t="str">
         <f ca="1" t="shared" si="12"/>
-        <v>2025-09-09</v>
+        <v>2024-10-07</v>
       </c>
     </row>
     <row r="128" spans="1:18">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="R128" t="str">
         <f ca="1" t="shared" si="12"/>
-        <v>2024-09-14</v>
+        <v>2025-07-18</v>
       </c>
     </row>
     <row r="129" spans="1:18">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="R129" t="str">
         <f ca="1" t="shared" si="12"/>
-        <v>2024-09-15</v>
+        <v>2025-02-07</v>
       </c>
     </row>
     <row r="130" spans="1:18">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="R130" t="str">
         <f ca="1" t="shared" si="12"/>
-        <v>2024-11-30</v>
+        <v>2025-02-05</v>
       </c>
     </row>
     <row r="131" spans="1:18">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="R131" t="str">
         <f ca="1" t="shared" si="12"/>
-        <v>2025-04-24</v>
+        <v>2024-10-26</v>
       </c>
     </row>
     <row r="132" spans="1:18">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="R132" t="str">
         <f ca="1" t="shared" si="12"/>
-        <v>2025-04-23</v>
+        <v>2024-11-06</v>
       </c>
     </row>
     <row r="133" spans="1:18">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="R133" t="str">
         <f ca="1" t="shared" ref="R133:R142" si="13">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-02-09</v>
+        <v>2024-08-25</v>
       </c>
     </row>
     <row r="134" spans="1:18">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="R134" t="str">
         <f ca="1" t="shared" si="13"/>
-        <v>2025-03-05</v>
+        <v>2025-01-10</v>
       </c>
     </row>
     <row r="135" spans="1:18">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="R135" t="str">
         <f ca="1" t="shared" si="13"/>
-        <v>2025-02-05</v>
+        <v>2025-07-16</v>
       </c>
     </row>
     <row r="136" spans="1:18">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="R136" t="str">
         <f ca="1" t="shared" si="13"/>
-        <v>2024-12-27</v>
+        <v>2025-04-02</v>
       </c>
     </row>
     <row r="137" spans="1:18">
@@ -13895,7 +13895,7 @@
       </c>
       <c r="R137" t="str">
         <f ca="1" t="shared" si="13"/>
-        <v>2024-09-23</v>
+        <v>2025-05-23</v>
       </c>
     </row>
     <row r="138" spans="1:18">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="R138" t="str">
         <f ca="1" t="shared" si="13"/>
-        <v>2024-12-05</v>
+        <v>2025-03-03</v>
       </c>
     </row>
     <row r="139" spans="1:18">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="R139" t="str">
         <f ca="1" t="shared" si="13"/>
-        <v>2025-04-20</v>
+        <v>2025-09-10</v>
       </c>
     </row>
     <row r="140" spans="1:18">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="R140" t="str">
         <f ca="1" t="shared" si="13"/>
-        <v>2024-10-31</v>
+        <v>2024-08-15</v>
       </c>
     </row>
     <row r="141" spans="1:18">
@@ -14123,7 +14123,7 @@
       </c>
       <c r="R141" t="str">
         <f ca="1" t="shared" si="13"/>
-        <v>2025-01-24</v>
+        <v>2025-03-26</v>
       </c>
     </row>
     <row r="142" spans="1:18">
@@ -14181,7 +14181,7 @@
       </c>
       <c r="R142" t="str">
         <f ca="1" t="shared" si="13"/>
-        <v>2024-12-06</v>
+        <v>2025-01-05</v>
       </c>
     </row>
     <row r="143" spans="1:18">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="R143" t="str">
         <f ca="1" t="shared" ref="R143:R152" si="14">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-08-04</v>
+        <v>2025-06-03</v>
       </c>
     </row>
     <row r="144" spans="1:18">
@@ -14297,7 +14297,7 @@
       </c>
       <c r="R144" t="str">
         <f ca="1" t="shared" si="14"/>
-        <v>2024-10-18</v>
+        <v>2025-09-13</v>
       </c>
     </row>
     <row r="145" spans="1:18">
@@ -14351,7 +14351,7 @@
       </c>
       <c r="R145" t="str">
         <f ca="1" t="shared" si="14"/>
-        <v>2024-12-01</v>
+        <v>2025-03-20</v>
       </c>
     </row>
     <row r="146" spans="1:18">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="R146" t="str">
         <f ca="1" t="shared" si="14"/>
-        <v>2024-10-23</v>
+        <v>2025-04-18</v>
       </c>
     </row>
     <row r="147" spans="1:18">
@@ -14463,7 +14463,7 @@
       </c>
       <c r="R147" t="str">
         <f ca="1" t="shared" si="14"/>
-        <v>2025-04-10</v>
+        <v>2024-08-10</v>
       </c>
     </row>
     <row r="148" spans="1:18">
@@ -14521,7 +14521,7 @@
       </c>
       <c r="R148" t="str">
         <f ca="1" t="shared" si="14"/>
-        <v>2025-05-22</v>
+        <v>2025-07-18</v>
       </c>
     </row>
     <row r="149" spans="1:18">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="R149" t="str">
         <f ca="1" t="shared" si="14"/>
-        <v>2025-09-23</v>
+        <v>2024-08-30</v>
       </c>
     </row>
     <row r="150" spans="1:18">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="R150" t="str">
         <f ca="1" t="shared" si="14"/>
-        <v>2024-12-07</v>
+        <v>2025-06-16</v>
       </c>
     </row>
     <row r="151" spans="1:18">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="R151" t="str">
         <f ca="1" t="shared" si="14"/>
-        <v>2024-09-22</v>
+        <v>2025-06-27</v>
       </c>
     </row>
     <row r="152" spans="1:18">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="R152" t="str">
         <f ca="1" t="shared" si="14"/>
-        <v>2025-07-24</v>
+        <v>2025-03-25</v>
       </c>
     </row>
     <row r="153" spans="1:18">
@@ -14811,7 +14811,7 @@
       </c>
       <c r="R153" t="str">
         <f ca="1" t="shared" ref="R153:R162" si="15">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-12-28</v>
+        <v>2025-08-22</v>
       </c>
     </row>
     <row r="154" spans="1:18">
@@ -14869,7 +14869,7 @@
       </c>
       <c r="R154" t="str">
         <f ca="1" t="shared" si="15"/>
-        <v>2025-07-09</v>
+        <v>2025-06-28</v>
       </c>
     </row>
     <row r="155" spans="1:18">
@@ -14927,7 +14927,7 @@
       </c>
       <c r="R155" t="str">
         <f ca="1" t="shared" si="15"/>
-        <v>2025-10-02</v>
+        <v>2025-10-07</v>
       </c>
     </row>
     <row r="156" spans="1:18">
@@ -14985,7 +14985,7 @@
       </c>
       <c r="R156" t="str">
         <f ca="1" t="shared" si="15"/>
-        <v>2025-08-16</v>
+        <v>2024-11-21</v>
       </c>
     </row>
     <row r="157" spans="1:18">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="R157" t="str">
         <f ca="1" t="shared" si="15"/>
-        <v>2025-07-29</v>
+        <v>2025-05-07</v>
       </c>
     </row>
     <row r="158" spans="1:18">
@@ -15101,7 +15101,7 @@
       </c>
       <c r="R158" t="str">
         <f ca="1" t="shared" si="15"/>
-        <v>2024-11-25</v>
+        <v>2025-08-22</v>
       </c>
     </row>
     <row r="159" spans="1:18">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="R159" t="str">
         <f ca="1" t="shared" si="15"/>
-        <v>2025-04-07</v>
+        <v>2025-07-10</v>
       </c>
     </row>
     <row r="160" spans="1:18">
@@ -15217,7 +15217,7 @@
       </c>
       <c r="R160" t="str">
         <f ca="1" t="shared" si="15"/>
-        <v>2024-09-23</v>
+        <v>2024-12-13</v>
       </c>
     </row>
     <row r="161" spans="1:18">
@@ -15275,7 +15275,7 @@
       </c>
       <c r="R161" t="str">
         <f ca="1" t="shared" si="15"/>
-        <v>2025-02-11</v>
+        <v>2024-09-08</v>
       </c>
     </row>
     <row r="162" spans="1:18">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="R162" t="str">
         <f ca="1" t="shared" si="15"/>
-        <v>2024-12-13</v>
+        <v>2025-01-06</v>
       </c>
     </row>
     <row r="163" spans="1:18">
@@ -15391,7 +15391,7 @@
       </c>
       <c r="R163" t="str">
         <f ca="1" t="shared" ref="R163:R172" si="16">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-06-15</v>
+        <v>2025-04-09</v>
       </c>
     </row>
     <row r="164" spans="1:18">
@@ -15445,7 +15445,7 @@
       </c>
       <c r="R164" t="str">
         <f ca="1" t="shared" si="16"/>
-        <v>2025-02-27</v>
+        <v>2024-12-26</v>
       </c>
     </row>
     <row r="165" spans="1:18">
@@ -15503,7 +15503,7 @@
       </c>
       <c r="R165" t="str">
         <f ca="1" t="shared" si="16"/>
-        <v>2024-08-03</v>
+        <v>2025-02-28</v>
       </c>
     </row>
     <row r="166" spans="1:18">
@@ -15557,7 +15557,7 @@
       </c>
       <c r="R166" t="str">
         <f ca="1" t="shared" si="16"/>
-        <v>2025-09-05</v>
+        <v>2025-04-27</v>
       </c>
     </row>
     <row r="167" spans="1:18">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="R167" t="str">
         <f ca="1" t="shared" si="16"/>
-        <v>2025-03-30</v>
+        <v>2024-08-17</v>
       </c>
     </row>
     <row r="168" spans="1:18">
@@ -15673,7 +15673,7 @@
       </c>
       <c r="R168" t="str">
         <f ca="1" t="shared" si="16"/>
-        <v>2025-10-05</v>
+        <v>2025-05-04</v>
       </c>
     </row>
     <row r="169" spans="1:18">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="R169" t="str">
         <f ca="1" t="shared" si="16"/>
-        <v>2025-01-01</v>
+        <v>2024-08-27</v>
       </c>
     </row>
     <row r="170" spans="1:18">
@@ -15785,7 +15785,7 @@
       </c>
       <c r="R170" t="str">
         <f ca="1" t="shared" si="16"/>
-        <v>2025-05-27</v>
+        <v>2024-11-01</v>
       </c>
     </row>
     <row r="171" spans="1:18">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="R171" t="str">
         <f ca="1" t="shared" si="16"/>
-        <v>2025-01-20</v>
+        <v>2025-05-10</v>
       </c>
     </row>
     <row r="172" spans="1:18">
@@ -15896,7 +15896,7 @@
       </c>
       <c r="R172" t="str">
         <f ca="1" t="shared" si="16"/>
-        <v>2025-03-17</v>
+        <v>2025-01-11</v>
       </c>
     </row>
     <row r="173" spans="1:18">
@@ -15953,7 +15953,7 @@
       </c>
       <c r="R173" t="str">
         <f ca="1" t="shared" ref="R173:R182" si="17">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-01-13</v>
+        <v>2025-07-14</v>
       </c>
     </row>
     <row r="174" spans="1:18">
@@ -16010,7 +16010,7 @@
       </c>
       <c r="R174" t="str">
         <f ca="1" t="shared" si="17"/>
-        <v>2024-10-05</v>
+        <v>2025-09-25</v>
       </c>
     </row>
     <row r="175" spans="1:18">
@@ -16067,7 +16067,7 @@
       </c>
       <c r="R175" t="str">
         <f ca="1" t="shared" si="17"/>
-        <v>2025-05-16</v>
+        <v>2024-12-26</v>
       </c>
     </row>
     <row r="176" spans="1:18">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="R176" t="str">
         <f ca="1" t="shared" si="17"/>
-        <v>2025-06-12</v>
+        <v>2024-11-10</v>
       </c>
     </row>
     <row r="177" spans="1:18">
@@ -16183,7 +16183,7 @@
       </c>
       <c r="R177" t="str">
         <f ca="1" t="shared" si="17"/>
-        <v>2025-08-20</v>
+        <v>2024-12-27</v>
       </c>
     </row>
     <row r="178" spans="1:18">
@@ -16237,7 +16237,7 @@
       </c>
       <c r="R178" t="str">
         <f ca="1" t="shared" si="17"/>
-        <v>2025-05-14</v>
+        <v>2025-01-15</v>
       </c>
     </row>
     <row r="179" spans="1:18">
@@ -16295,7 +16295,7 @@
       </c>
       <c r="R179" t="str">
         <f ca="1" t="shared" si="17"/>
-        <v>2024-10-22</v>
+        <v>2024-09-03</v>
       </c>
     </row>
     <row r="180" spans="1:18">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="R180" t="str">
         <f ca="1" t="shared" si="17"/>
-        <v>2024-11-15</v>
+        <v>2025-05-10</v>
       </c>
     </row>
     <row r="181" spans="1:18">
@@ -16403,7 +16403,7 @@
       </c>
       <c r="R181" t="str">
         <f ca="1" t="shared" si="17"/>
-        <v>2024-10-10</v>
+        <v>2025-01-22</v>
       </c>
     </row>
     <row r="182" spans="1:18">
@@ -16461,7 +16461,7 @@
       </c>
       <c r="R182" t="str">
         <f ca="1" t="shared" si="17"/>
-        <v>2025-09-05</v>
+        <v>2024-12-05</v>
       </c>
     </row>
     <row r="183" spans="1:18">
@@ -16519,7 +16519,7 @@
       </c>
       <c r="R183" t="str">
         <f ca="1" t="shared" ref="R183:R192" si="18">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-10-23</v>
+        <v>2024-09-23</v>
       </c>
     </row>
     <row r="184" spans="1:18">
@@ -16573,7 +16573,7 @@
       </c>
       <c r="R184" t="str">
         <f ca="1" t="shared" si="18"/>
-        <v>2025-03-01</v>
+        <v>2025-02-08</v>
       </c>
     </row>
     <row r="185" spans="1:18">
@@ -16631,7 +16631,7 @@
       </c>
       <c r="R185" t="str">
         <f ca="1" t="shared" si="18"/>
-        <v>2024-09-16</v>
+        <v>2024-12-09</v>
       </c>
     </row>
     <row r="186" spans="1:18">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="R186" t="str">
         <f ca="1" t="shared" si="18"/>
-        <v>2024-10-10</v>
+        <v>2025-03-06</v>
       </c>
     </row>
     <row r="187" spans="1:18">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="R187" t="str">
         <f ca="1" t="shared" si="18"/>
-        <v>2025-02-23</v>
+        <v>2025-07-12</v>
       </c>
     </row>
     <row r="188" spans="1:18">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="R188" t="str">
         <f ca="1" t="shared" si="18"/>
-        <v>2025-05-06</v>
+        <v>2025-09-16</v>
       </c>
     </row>
     <row r="189" spans="1:18">
@@ -16857,7 +16857,7 @@
       </c>
       <c r="R189" t="str">
         <f ca="1" t="shared" si="18"/>
-        <v>2025-09-26</v>
+        <v>2025-01-13</v>
       </c>
     </row>
     <row r="190" spans="1:18">
@@ -16915,7 +16915,7 @@
       </c>
       <c r="R190" t="str">
         <f ca="1" t="shared" si="18"/>
-        <v>2025-02-19</v>
+        <v>2025-01-31</v>
       </c>
     </row>
     <row r="191" spans="1:18">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="R191" t="str">
         <f ca="1" t="shared" si="18"/>
-        <v>2025-02-04</v>
+        <v>2025-03-26</v>
       </c>
     </row>
     <row r="192" spans="1:18">
@@ -17031,7 +17031,7 @@
       </c>
       <c r="R192" t="str">
         <f ca="1" t="shared" si="18"/>
-        <v>2025-01-29</v>
+        <v>2025-05-30</v>
       </c>
     </row>
     <row r="193" spans="1:18">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="R193" t="str">
         <f ca="1" t="shared" ref="R193:R202" si="19">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-10-03</v>
+        <v>2025-06-03</v>
       </c>
     </row>
     <row r="194" spans="1:18">
@@ -17147,7 +17147,7 @@
       </c>
       <c r="R194" t="str">
         <f ca="1" t="shared" si="19"/>
-        <v>2025-08-10</v>
+        <v>2025-02-21</v>
       </c>
     </row>
     <row r="195" spans="1:18">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="R195" t="str">
         <f ca="1" t="shared" si="19"/>
-        <v>2025-05-14</v>
+        <v>2025-10-07</v>
       </c>
     </row>
     <row r="196" spans="1:18">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="R196" t="str">
         <f ca="1" t="shared" si="19"/>
-        <v>2024-12-15</v>
+        <v>2025-08-27</v>
       </c>
     </row>
     <row r="197" spans="1:18">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="R197" t="str">
         <f ca="1" t="shared" si="19"/>
-        <v>2024-10-11</v>
+        <v>2025-02-15</v>
       </c>
     </row>
     <row r="198" spans="1:18">
@@ -17375,7 +17375,7 @@
       </c>
       <c r="R198" t="str">
         <f ca="1" t="shared" si="19"/>
-        <v>2025-05-12</v>
+        <v>2025-07-27</v>
       </c>
     </row>
     <row r="199" spans="1:18">
@@ -17433,7 +17433,7 @@
       </c>
       <c r="R199" t="str">
         <f ca="1" t="shared" si="19"/>
-        <v>2024-11-13</v>
+        <v>2024-11-15</v>
       </c>
     </row>
     <row r="200" spans="1:18">
@@ -17487,7 +17487,7 @@
       </c>
       <c r="R200" t="str">
         <f ca="1" t="shared" si="19"/>
-        <v>2025-06-12</v>
+        <v>2025-03-18</v>
       </c>
     </row>
     <row r="201" spans="1:18">
@@ -17541,7 +17541,7 @@
       </c>
       <c r="R201" t="str">
         <f ca="1" t="shared" si="19"/>
-        <v>2025-02-04</v>
+        <v>2024-10-21</v>
       </c>
     </row>
     <row r="202" spans="1:18">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="R202" t="str">
         <f ca="1" t="shared" si="19"/>
-        <v>2025-07-08</v>
+        <v>2024-11-24</v>
       </c>
     </row>
     <row r="203" spans="1:18">
@@ -17657,7 +17657,7 @@
       </c>
       <c r="R203" t="str">
         <f ca="1" t="shared" ref="R203:R212" si="20">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-10-06</v>
+        <v>2025-09-27</v>
       </c>
     </row>
     <row r="204" spans="1:18">
@@ -17711,7 +17711,7 @@
       </c>
       <c r="R204" t="str">
         <f ca="1" t="shared" si="20"/>
-        <v>2025-01-10</v>
+        <v>2024-08-12</v>
       </c>
     </row>
     <row r="205" spans="1:18">
@@ -17769,7 +17769,7 @@
       </c>
       <c r="R205" t="str">
         <f ca="1" t="shared" si="20"/>
-        <v>2024-11-01</v>
+        <v>2025-09-25</v>
       </c>
     </row>
     <row r="206" spans="1:18">
@@ -17823,7 +17823,7 @@
       </c>
       <c r="R206" t="str">
         <f ca="1" t="shared" si="20"/>
-        <v>2024-11-10</v>
+        <v>2024-10-17</v>
       </c>
     </row>
     <row r="207" spans="1:18">
@@ -17881,7 +17881,7 @@
       </c>
       <c r="R207" t="str">
         <f ca="1" t="shared" si="20"/>
-        <v>2025-10-03</v>
+        <v>2025-06-08</v>
       </c>
     </row>
     <row r="208" spans="1:18">
@@ -17939,7 +17939,7 @@
       </c>
       <c r="R208" t="str">
         <f ca="1" t="shared" si="20"/>
-        <v>2025-07-27</v>
+        <v>2025-01-04</v>
       </c>
     </row>
     <row r="209" spans="1:18">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="R209" t="str">
         <f ca="1" t="shared" si="20"/>
-        <v>2024-08-05</v>
+        <v>2024-11-02</v>
       </c>
     </row>
     <row r="210" spans="1:18">
@@ -18055,7 +18055,7 @@
       </c>
       <c r="R210" t="str">
         <f ca="1" t="shared" si="20"/>
-        <v>2025-01-08</v>
+        <v>2024-08-18</v>
       </c>
     </row>
     <row r="211" spans="1:18">
@@ -18109,7 +18109,7 @@
       </c>
       <c r="R211" t="str">
         <f ca="1" t="shared" si="20"/>
-        <v>2025-06-21</v>
+        <v>2024-12-03</v>
       </c>
     </row>
     <row r="212" spans="1:18">
@@ -18167,7 +18167,7 @@
       </c>
       <c r="R212" t="str">
         <f ca="1" t="shared" si="20"/>
-        <v>2025-04-08</v>
+        <v>2025-01-27</v>
       </c>
     </row>
     <row r="213" spans="1:18">
@@ -18225,7 +18225,7 @@
       </c>
       <c r="R213" t="str">
         <f ca="1" t="shared" ref="R213:R222" si="21">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-09-30</v>
+        <v>2025-03-13</v>
       </c>
     </row>
     <row r="214" spans="1:18">
@@ -18283,7 +18283,7 @@
       </c>
       <c r="R214" t="str">
         <f ca="1" t="shared" si="21"/>
-        <v>2025-07-01</v>
+        <v>2025-04-25</v>
       </c>
     </row>
     <row r="215" spans="1:18">
@@ -18337,7 +18337,7 @@
       </c>
       <c r="R215" t="str">
         <f ca="1" t="shared" si="21"/>
-        <v>2024-10-28</v>
+        <v>2025-07-05</v>
       </c>
     </row>
     <row r="216" spans="1:18">
@@ -18395,7 +18395,7 @@
       </c>
       <c r="R216" t="str">
         <f ca="1" t="shared" si="21"/>
-        <v>2025-09-20</v>
+        <v>2025-09-28</v>
       </c>
     </row>
     <row r="217" spans="1:18">
@@ -18453,7 +18453,7 @@
       </c>
       <c r="R217" t="str">
         <f ca="1" t="shared" si="21"/>
-        <v>2025-06-15</v>
+        <v>2024-11-06</v>
       </c>
     </row>
     <row r="218" spans="1:18">
@@ -18511,7 +18511,7 @@
       </c>
       <c r="R218" t="str">
         <f ca="1" t="shared" si="21"/>
-        <v>2025-02-14</v>
+        <v>2024-09-07</v>
       </c>
     </row>
     <row r="219" spans="1:18">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="R219" t="str">
         <f ca="1" t="shared" si="21"/>
-        <v>2025-03-04</v>
+        <v>2025-08-22</v>
       </c>
     </row>
     <row r="220" spans="1:18">
@@ -18620,7 +18620,7 @@
       </c>
       <c r="R220" t="str">
         <f ca="1" t="shared" si="21"/>
-        <v>2025-08-23</v>
+        <v>2025-08-05</v>
       </c>
     </row>
     <row r="221" spans="1:18">
@@ -18678,7 +18678,7 @@
       </c>
       <c r="R221" t="str">
         <f ca="1" t="shared" si="21"/>
-        <v>2025-08-18</v>
+        <v>2024-09-21</v>
       </c>
     </row>
     <row r="222" spans="1:18">
@@ -18733,7 +18733,7 @@
       </c>
       <c r="R222" t="str">
         <f ca="1" t="shared" si="21"/>
-        <v>2025-10-02</v>
+        <v>2025-07-20</v>
       </c>
     </row>
     <row r="223" spans="1:18">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="R223" t="str">
         <f ca="1" t="shared" ref="R223:R232" si="22">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-03-12</v>
+        <v>2025-04-13</v>
       </c>
     </row>
     <row r="224" spans="1:18">
@@ -18848,7 +18848,7 @@
       </c>
       <c r="R224" t="str">
         <f ca="1" t="shared" si="22"/>
-        <v>2025-07-19</v>
+        <v>2025-07-28</v>
       </c>
     </row>
     <row r="225" spans="1:18">
@@ -18906,7 +18906,7 @@
       </c>
       <c r="R225" t="str">
         <f ca="1" t="shared" si="22"/>
-        <v>2025-07-15</v>
+        <v>2025-09-23</v>
       </c>
     </row>
     <row r="226" spans="1:18">
@@ -18960,7 +18960,7 @@
       </c>
       <c r="R226" t="str">
         <f ca="1" t="shared" si="22"/>
-        <v>2024-09-09</v>
+        <v>2024-09-11</v>
       </c>
     </row>
     <row r="227" spans="1:18">
@@ -19018,7 +19018,7 @@
       </c>
       <c r="R227" t="str">
         <f ca="1" t="shared" si="22"/>
-        <v>2024-11-09</v>
+        <v>2025-08-09</v>
       </c>
     </row>
     <row r="228" spans="1:18">
@@ -19073,7 +19073,7 @@
       </c>
       <c r="R228" t="str">
         <f ca="1" t="shared" si="22"/>
-        <v>2025-02-07</v>
+        <v>2025-03-06</v>
       </c>
     </row>
     <row r="229" spans="1:18">
@@ -19131,7 +19131,7 @@
       </c>
       <c r="R229" t="str">
         <f ca="1" t="shared" si="22"/>
-        <v>2024-08-30</v>
+        <v>2024-11-30</v>
       </c>
     </row>
     <row r="230" spans="1:18">
@@ -19185,7 +19185,7 @@
       </c>
       <c r="R230" t="str">
         <f ca="1" t="shared" si="22"/>
-        <v>2025-09-30</v>
+        <v>2025-01-03</v>
       </c>
     </row>
     <row r="231" spans="1:18">
@@ -19239,7 +19239,7 @@
       </c>
       <c r="R231" t="str">
         <f ca="1" t="shared" si="22"/>
-        <v>2024-11-18</v>
+        <v>2024-12-17</v>
       </c>
     </row>
     <row r="232" spans="1:18">
@@ -19296,7 +19296,7 @@
       </c>
       <c r="R232" t="str">
         <f ca="1" t="shared" si="22"/>
-        <v>2024-10-12</v>
+        <v>2025-04-27</v>
       </c>
     </row>
     <row r="233" spans="1:18">
@@ -19354,7 +19354,7 @@
       </c>
       <c r="R233" t="str">
         <f ca="1" t="shared" ref="R233:R242" si="23">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-07-19</v>
+        <v>2025-08-08</v>
       </c>
     </row>
     <row r="234" spans="1:18">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="R234" t="str">
         <f ca="1" t="shared" si="23"/>
-        <v>2024-09-06</v>
+        <v>2025-02-13</v>
       </c>
     </row>
     <row r="235" spans="1:18">
@@ -19462,7 +19462,7 @@
       </c>
       <c r="R235" t="str">
         <f ca="1" t="shared" si="23"/>
-        <v>2025-06-14</v>
+        <v>2025-04-23</v>
       </c>
     </row>
     <row r="236" spans="1:18">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="R236" t="str">
         <f ca="1" t="shared" si="23"/>
-        <v>2025-03-18</v>
+        <v>2024-09-07</v>
       </c>
     </row>
     <row r="237" spans="1:18">
@@ -19575,7 +19575,7 @@
       </c>
       <c r="R237" t="str">
         <f ca="1" t="shared" si="23"/>
-        <v>2024-08-04</v>
+        <v>2025-03-20</v>
       </c>
     </row>
     <row r="238" spans="1:18">
@@ -19633,7 +19633,7 @@
       </c>
       <c r="R238" t="str">
         <f ca="1" t="shared" si="23"/>
-        <v>2024-09-04</v>
+        <v>2025-03-03</v>
       </c>
     </row>
     <row r="239" spans="1:18">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="R239" t="str">
         <f ca="1" t="shared" si="23"/>
-        <v>2024-09-01</v>
+        <v>2025-03-26</v>
       </c>
     </row>
     <row r="240" spans="1:18">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="R240" t="str">
         <f ca="1" t="shared" si="23"/>
-        <v>2025-06-03</v>
+        <v>2024-11-30</v>
       </c>
     </row>
     <row r="241" spans="1:18">
@@ -19807,7 +19807,7 @@
       </c>
       <c r="R241" t="str">
         <f ca="1" t="shared" si="23"/>
-        <v>2025-04-14</v>
+        <v>2024-09-11</v>
       </c>
     </row>
     <row r="242" spans="1:18">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="R242" t="str">
         <f ca="1" t="shared" si="23"/>
-        <v>2025-05-30</v>
+        <v>2025-05-10</v>
       </c>
     </row>
     <row r="243" spans="1:18">
@@ -19919,7 +19919,7 @@
       </c>
       <c r="R243" t="str">
         <f ca="1" t="shared" ref="R243:R252" si="24">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-01-28</v>
+        <v>2025-03-15</v>
       </c>
     </row>
     <row r="244" spans="1:18">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="R244" t="str">
         <f ca="1" t="shared" si="24"/>
-        <v>2025-04-28</v>
+        <v>2024-08-24</v>
       </c>
     </row>
     <row r="245" spans="1:18">
@@ -20027,7 +20027,7 @@
       </c>
       <c r="R245" t="str">
         <f ca="1" t="shared" si="24"/>
-        <v>2025-07-19</v>
+        <v>2025-04-30</v>
       </c>
     </row>
     <row r="246" spans="1:18">
@@ -20081,7 +20081,7 @@
       </c>
       <c r="R246" t="str">
         <f ca="1" t="shared" si="24"/>
-        <v>2025-08-02</v>
+        <v>2024-12-12</v>
       </c>
     </row>
     <row r="247" spans="1:18">
@@ -20138,7 +20138,7 @@
       </c>
       <c r="R247" t="str">
         <f ca="1" t="shared" si="24"/>
-        <v>2025-02-22</v>
+        <v>2024-08-25</v>
       </c>
     </row>
     <row r="248" spans="1:18">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="R248" t="str">
         <f ca="1" t="shared" si="24"/>
-        <v>2025-09-30</v>
+        <v>2025-06-03</v>
       </c>
     </row>
     <row r="249" spans="1:18">
@@ -20250,7 +20250,7 @@
       </c>
       <c r="R249" t="str">
         <f ca="1" t="shared" si="24"/>
-        <v>2024-12-13</v>
+        <v>2025-10-04</v>
       </c>
     </row>
     <row r="250" spans="1:18">
@@ -20308,7 +20308,7 @@
       </c>
       <c r="R250" t="str">
         <f ca="1" t="shared" si="24"/>
-        <v>2025-07-05</v>
+        <v>2024-09-03</v>
       </c>
     </row>
     <row r="251" spans="1:18">
@@ -20366,7 +20366,7 @@
       </c>
       <c r="R251" t="str">
         <f ca="1" t="shared" si="24"/>
-        <v>2025-04-06</v>
+        <v>2024-08-23</v>
       </c>
     </row>
     <row r="252" spans="1:18">
@@ -20424,7 +20424,7 @@
       </c>
       <c r="R252" t="str">
         <f ca="1" t="shared" si="24"/>
-        <v>2025-01-23</v>
+        <v>2024-08-27</v>
       </c>
     </row>
     <row r="253" spans="1:18">
@@ -20482,7 +20482,7 @@
       </c>
       <c r="R253" t="str">
         <f ca="1" t="shared" ref="R253:R262" si="25">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-01-02</v>
+        <v>2025-09-20</v>
       </c>
     </row>
     <row r="254" spans="1:18">
@@ -20540,7 +20540,7 @@
       </c>
       <c r="R254" t="str">
         <f ca="1" t="shared" si="25"/>
-        <v>2025-03-20</v>
+        <v>2025-09-21</v>
       </c>
     </row>
     <row r="255" spans="1:18">
@@ -20598,7 +20598,7 @@
       </c>
       <c r="R255" t="str">
         <f ca="1" t="shared" si="25"/>
-        <v>2025-02-23</v>
+        <v>2025-08-01</v>
       </c>
     </row>
     <row r="256" spans="1:18">
@@ -20656,7 +20656,7 @@
       </c>
       <c r="R256" t="str">
         <f ca="1" t="shared" si="25"/>
-        <v>2025-03-13</v>
+        <v>2025-01-04</v>
       </c>
     </row>
     <row r="257" spans="1:18">
@@ -20711,7 +20711,7 @@
       </c>
       <c r="R257" t="str">
         <f ca="1" t="shared" si="25"/>
-        <v>2025-02-28</v>
+        <v>2025-09-19</v>
       </c>
     </row>
     <row r="258" spans="1:18">
@@ -20769,7 +20769,7 @@
       </c>
       <c r="R258" t="str">
         <f ca="1" t="shared" si="25"/>
-        <v>2024-12-25</v>
+        <v>2024-10-24</v>
       </c>
     </row>
     <row r="259" spans="1:18">
@@ -20824,7 +20824,7 @@
       </c>
       <c r="R259" t="str">
         <f ca="1" t="shared" si="25"/>
-        <v>2024-08-15</v>
+        <v>2025-02-17</v>
       </c>
     </row>
     <row r="260" spans="1:18">
@@ -20882,7 +20882,7 @@
       </c>
       <c r="R260" t="str">
         <f ca="1" t="shared" si="25"/>
-        <v>2024-11-27</v>
+        <v>2025-06-12</v>
       </c>
     </row>
     <row r="261" spans="1:18">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="R261" t="str">
         <f ca="1" t="shared" si="25"/>
-        <v>2025-08-31</v>
+        <v>2025-06-07</v>
       </c>
     </row>
     <row r="262" spans="1:18">
@@ -20997,7 +20997,7 @@
       </c>
       <c r="R262" t="str">
         <f ca="1" t="shared" si="25"/>
-        <v>2025-02-16</v>
+        <v>2025-04-22</v>
       </c>
     </row>
     <row r="263" spans="1:18">
@@ -21055,7 +21055,7 @@
       </c>
       <c r="R263" t="str">
         <f ca="1" t="shared" ref="R263:R272" si="26">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-07-14</v>
+        <v>2024-09-05</v>
       </c>
     </row>
     <row r="264" spans="1:18">
@@ -21113,7 +21113,7 @@
       </c>
       <c r="R264" t="str">
         <f ca="1" t="shared" si="26"/>
-        <v>2025-06-14</v>
+        <v>2025-08-15</v>
       </c>
     </row>
     <row r="265" spans="1:18">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="R265" t="str">
         <f ca="1" t="shared" si="26"/>
-        <v>2025-08-08</v>
+        <v>2025-04-01</v>
       </c>
     </row>
     <row r="266" spans="1:18">
@@ -21226,7 +21226,7 @@
       </c>
       <c r="R266" t="str">
         <f ca="1" t="shared" si="26"/>
-        <v>2024-10-05</v>
+        <v>2025-05-26</v>
       </c>
     </row>
     <row r="267" spans="1:18">
@@ -21283,7 +21283,7 @@
       </c>
       <c r="R267" t="str">
         <f ca="1" t="shared" si="26"/>
-        <v>2025-08-14</v>
+        <v>2025-10-06</v>
       </c>
     </row>
     <row r="268" spans="1:18">
@@ -21340,7 +21340,7 @@
       </c>
       <c r="R268" t="str">
         <f ca="1" t="shared" si="26"/>
-        <v>2025-09-01</v>
+        <v>2025-07-23</v>
       </c>
     </row>
     <row r="269" spans="1:18">
@@ -21398,7 +21398,7 @@
       </c>
       <c r="R269" t="str">
         <f ca="1" t="shared" si="26"/>
-        <v>2025-02-10</v>
+        <v>2025-04-19</v>
       </c>
     </row>
     <row r="270" spans="1:18">
@@ -21452,7 +21452,7 @@
       </c>
       <c r="R270" t="str">
         <f ca="1" t="shared" si="26"/>
-        <v>2025-08-10</v>
+        <v>2024-12-31</v>
       </c>
     </row>
     <row r="271" spans="1:18">
@@ -21510,7 +21510,7 @@
       </c>
       <c r="R271" t="str">
         <f ca="1" t="shared" si="26"/>
-        <v>2025-04-03</v>
+        <v>2024-11-17</v>
       </c>
     </row>
     <row r="272" spans="1:18">
@@ -21568,7 +21568,7 @@
       </c>
       <c r="R272" t="str">
         <f ca="1" t="shared" si="26"/>
-        <v>2025-05-09</v>
+        <v>2025-09-29</v>
       </c>
     </row>
     <row r="273" spans="1:18">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="R273" t="str">
         <f ca="1" t="shared" ref="R273:R282" si="27">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-07-22</v>
+        <v>2025-01-05</v>
       </c>
     </row>
     <row r="274" spans="1:18">
@@ -21680,7 +21680,7 @@
       </c>
       <c r="R274" t="str">
         <f ca="1" t="shared" si="27"/>
-        <v>2025-03-28</v>
+        <v>2025-05-14</v>
       </c>
     </row>
     <row r="275" spans="1:18">
@@ -21734,7 +21734,7 @@
       </c>
       <c r="R275" t="str">
         <f ca="1" t="shared" si="27"/>
-        <v>2025-09-07</v>
+        <v>2025-01-08</v>
       </c>
     </row>
     <row r="276" spans="1:18">
@@ -21788,7 +21788,7 @@
       </c>
       <c r="R276" t="str">
         <f ca="1" t="shared" si="27"/>
-        <v>2025-03-09</v>
+        <v>2025-02-23</v>
       </c>
     </row>
     <row r="277" spans="1:18">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="R277" t="str">
         <f ca="1" t="shared" si="27"/>
-        <v>2025-01-19</v>
+        <v>2025-06-09</v>
       </c>
     </row>
     <row r="278" spans="1:18">
@@ -21900,7 +21900,7 @@
       </c>
       <c r="R278" t="str">
         <f ca="1" t="shared" si="27"/>
-        <v>2024-11-03</v>
+        <v>2025-08-25</v>
       </c>
     </row>
     <row r="279" spans="1:18">
@@ -21958,7 +21958,7 @@
       </c>
       <c r="R279" t="str">
         <f ca="1" t="shared" si="27"/>
-        <v>2024-08-27</v>
+        <v>2025-05-06</v>
       </c>
     </row>
     <row r="280" spans="1:18">
@@ -22016,7 +22016,7 @@
       </c>
       <c r="R280" t="str">
         <f ca="1" t="shared" si="27"/>
-        <v>2025-05-06</v>
+        <v>2025-02-28</v>
       </c>
     </row>
     <row r="281" spans="1:18">
@@ -22074,7 +22074,7 @@
       </c>
       <c r="R281" t="str">
         <f ca="1" t="shared" si="27"/>
-        <v>2025-08-17</v>
+        <v>2025-06-24</v>
       </c>
     </row>
     <row r="282" spans="1:18">
@@ -22132,7 +22132,7 @@
       </c>
       <c r="R282" t="str">
         <f ca="1" t="shared" si="27"/>
-        <v>2025-06-18</v>
+        <v>2025-08-31</v>
       </c>
     </row>
     <row r="283" spans="1:18">
@@ -22186,7 +22186,7 @@
       </c>
       <c r="R283" t="str">
         <f ca="1" t="shared" ref="R283:R292" si="28">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-10-17</v>
+        <v>2025-03-21</v>
       </c>
     </row>
     <row r="284" spans="1:18">
@@ -22240,7 +22240,7 @@
       </c>
       <c r="R284" t="str">
         <f ca="1" t="shared" si="28"/>
-        <v>2025-04-11</v>
+        <v>2025-01-15</v>
       </c>
     </row>
     <row r="285" spans="1:18">
@@ -22294,7 +22294,7 @@
       </c>
       <c r="R285" t="str">
         <f ca="1" t="shared" si="28"/>
-        <v>2024-10-03</v>
+        <v>2024-08-26</v>
       </c>
     </row>
     <row r="286" spans="1:18">
@@ -22351,7 +22351,7 @@
       </c>
       <c r="R286" t="str">
         <f ca="1" t="shared" si="28"/>
-        <v>2025-03-04</v>
+        <v>2025-04-25</v>
       </c>
     </row>
     <row r="287" spans="1:18">
@@ -22405,7 +22405,7 @@
       </c>
       <c r="R287" t="str">
         <f ca="1" t="shared" si="28"/>
-        <v>2025-09-28</v>
+        <v>2025-05-15</v>
       </c>
     </row>
     <row r="288" spans="1:18">
@@ -22463,7 +22463,7 @@
       </c>
       <c r="R288" t="str">
         <f ca="1" t="shared" si="28"/>
-        <v>2024-09-19</v>
+        <v>2025-07-07</v>
       </c>
     </row>
     <row r="289" spans="1:18">
@@ -22517,7 +22517,7 @@
       </c>
       <c r="R289" t="str">
         <f ca="1" t="shared" si="28"/>
-        <v>2025-08-26</v>
+        <v>2025-08-13</v>
       </c>
     </row>
     <row r="290" spans="1:18">
@@ -22575,7 +22575,7 @@
       </c>
       <c r="R290" t="str">
         <f ca="1" t="shared" si="28"/>
-        <v>2024-10-18</v>
+        <v>2025-04-15</v>
       </c>
     </row>
     <row r="291" spans="1:18">
@@ -22633,7 +22633,7 @@
       </c>
       <c r="R291" t="str">
         <f ca="1" t="shared" si="28"/>
-        <v>2025-09-28</v>
+        <v>2024-11-30</v>
       </c>
     </row>
     <row r="292" spans="1:18">
@@ -22687,7 +22687,7 @@
       </c>
       <c r="R292" t="str">
         <f ca="1" t="shared" si="28"/>
-        <v>2025-06-10</v>
+        <v>2025-01-21</v>
       </c>
     </row>
     <row r="293" spans="1:18">
@@ -22742,7 +22742,7 @@
       </c>
       <c r="R293" t="str">
         <f ca="1" t="shared" ref="R293:R302" si="29">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-07-04</v>
+        <v>2024-11-23</v>
       </c>
     </row>
     <row r="294" spans="1:18">
@@ -22800,7 +22800,7 @@
       </c>
       <c r="R294" t="str">
         <f ca="1" t="shared" si="29"/>
-        <v>2024-10-31</v>
+        <v>2025-01-05</v>
       </c>
     </row>
     <row r="295" spans="1:18">
@@ -22858,7 +22858,7 @@
       </c>
       <c r="R295" t="str">
         <f ca="1" t="shared" si="29"/>
-        <v>2024-08-14</v>
+        <v>2025-09-26</v>
       </c>
     </row>
     <row r="296" spans="1:18">
@@ -22916,7 +22916,7 @@
       </c>
       <c r="R296" t="str">
         <f ca="1" t="shared" si="29"/>
-        <v>2025-01-01</v>
+        <v>2024-08-26</v>
       </c>
     </row>
     <row r="297" spans="1:18">
@@ -22970,7 +22970,7 @@
       </c>
       <c r="R297" t="str">
         <f ca="1" t="shared" si="29"/>
-        <v>2024-09-04</v>
+        <v>2025-07-05</v>
       </c>
     </row>
     <row r="298" spans="1:18">
@@ -23024,7 +23024,7 @@
       </c>
       <c r="R298" t="str">
         <f ca="1" t="shared" si="29"/>
-        <v>2025-03-16</v>
+        <v>2024-10-02</v>
       </c>
     </row>
     <row r="299" spans="1:18">
@@ -23082,7 +23082,7 @@
       </c>
       <c r="R299" t="str">
         <f ca="1" t="shared" si="29"/>
-        <v>2024-10-31</v>
+        <v>2025-05-10</v>
       </c>
     </row>
     <row r="300" spans="1:18">
@@ -23139,7 +23139,7 @@
       </c>
       <c r="R300" t="str">
         <f ca="1" t="shared" si="29"/>
-        <v>2025-04-06</v>
+        <v>2025-05-03</v>
       </c>
     </row>
     <row r="301" spans="1:18">
@@ -23197,7 +23197,7 @@
       </c>
       <c r="R301" t="str">
         <f ca="1" t="shared" si="29"/>
-        <v>2025-05-15</v>
+        <v>2024-09-03</v>
       </c>
     </row>
     <row r="302" spans="1:18">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="R302" t="str">
         <f ca="1" t="shared" si="29"/>
-        <v>2025-03-25</v>
+        <v>2025-06-21</v>
       </c>
     </row>
     <row r="303" spans="1:18">
@@ -23305,7 +23305,7 @@
       </c>
       <c r="R303" t="str">
         <f ca="1" t="shared" ref="R303:R312" si="30">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-01-10</v>
+        <v>2025-03-02</v>
       </c>
     </row>
     <row r="304" spans="1:18">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="R304" t="str">
         <f ca="1" t="shared" si="30"/>
-        <v>2025-04-13</v>
+        <v>2025-04-18</v>
       </c>
     </row>
     <row r="305" spans="1:18">
@@ -23421,7 +23421,7 @@
       </c>
       <c r="R305" t="str">
         <f ca="1" t="shared" si="30"/>
-        <v>2024-09-02</v>
+        <v>2025-02-13</v>
       </c>
     </row>
     <row r="306" spans="1:18">
@@ -23479,7 +23479,7 @@
       </c>
       <c r="R306" t="str">
         <f ca="1" t="shared" si="30"/>
-        <v>2025-08-03</v>
+        <v>2025-04-05</v>
       </c>
     </row>
     <row r="307" spans="1:18">
@@ -23537,7 +23537,7 @@
       </c>
       <c r="R307" t="str">
         <f ca="1" t="shared" si="30"/>
-        <v>2024-09-09</v>
+        <v>2025-03-07</v>
       </c>
     </row>
     <row r="308" spans="1:18">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="R308" t="str">
         <f ca="1" t="shared" si="30"/>
-        <v>2025-06-11</v>
+        <v>2025-08-17</v>
       </c>
     </row>
     <row r="309" spans="1:18">
@@ -23653,7 +23653,7 @@
       </c>
       <c r="R309" t="str">
         <f ca="1" t="shared" si="30"/>
-        <v>2025-01-29</v>
+        <v>2024-12-16</v>
       </c>
     </row>
     <row r="310" spans="1:18">
@@ -23711,7 +23711,7 @@
       </c>
       <c r="R310" t="str">
         <f ca="1" t="shared" si="30"/>
-        <v>2025-04-18</v>
+        <v>2024-12-06</v>
       </c>
     </row>
     <row r="311" spans="1:18">
@@ -23765,7 +23765,7 @@
       </c>
       <c r="R311" t="str">
         <f ca="1" t="shared" si="30"/>
-        <v>2024-10-02</v>
+        <v>2025-10-03</v>
       </c>
     </row>
     <row r="312" spans="1:18">
@@ -23823,7 +23823,7 @@
       </c>
       <c r="R312" t="str">
         <f ca="1" t="shared" si="30"/>
-        <v>2025-09-22</v>
+        <v>2024-08-09</v>
       </c>
     </row>
     <row r="313" spans="1:18">
@@ -23878,7 +23878,7 @@
       </c>
       <c r="R313" t="str">
         <f ca="1" t="shared" ref="R313:R322" si="31">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-04-14</v>
+        <v>2025-02-16</v>
       </c>
     </row>
     <row r="314" spans="1:18">
@@ -23932,7 +23932,7 @@
       </c>
       <c r="R314" t="str">
         <f ca="1" t="shared" si="31"/>
-        <v>2025-08-06</v>
+        <v>2025-05-11</v>
       </c>
     </row>
     <row r="315" spans="1:18">
@@ -23990,7 +23990,7 @@
       </c>
       <c r="R315" t="str">
         <f ca="1" t="shared" si="31"/>
-        <v>2025-02-19</v>
+        <v>2025-08-02</v>
       </c>
     </row>
     <row r="316" spans="1:18">
@@ -24048,7 +24048,7 @@
       </c>
       <c r="R316" t="str">
         <f ca="1" t="shared" si="31"/>
-        <v>2025-06-25</v>
+        <v>2024-11-04</v>
       </c>
     </row>
     <row r="317" spans="1:18">
@@ -24106,7 +24106,7 @@
       </c>
       <c r="R317" t="str">
         <f ca="1" t="shared" si="31"/>
-        <v>2025-01-03</v>
+        <v>2025-05-08</v>
       </c>
     </row>
     <row r="318" spans="1:18">
@@ -24161,7 +24161,7 @@
       </c>
       <c r="R318" t="str">
         <f ca="1" t="shared" si="31"/>
-        <v>2025-09-16</v>
+        <v>2025-03-01</v>
       </c>
     </row>
     <row r="319" spans="1:18">
@@ -24219,7 +24219,7 @@
       </c>
       <c r="R319" t="str">
         <f ca="1" t="shared" si="31"/>
-        <v>2024-09-14</v>
+        <v>2024-09-24</v>
       </c>
     </row>
     <row r="320" spans="1:18">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="R320" t="str">
         <f ca="1" t="shared" si="31"/>
-        <v>2025-03-07</v>
+        <v>2024-08-01</v>
       </c>
     </row>
     <row r="321" spans="1:18">
@@ -24335,7 +24335,7 @@
       </c>
       <c r="R321" t="str">
         <f ca="1" t="shared" si="31"/>
-        <v>2025-04-21</v>
+        <v>2025-08-29</v>
       </c>
     </row>
     <row r="322" spans="1:18">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="R322" t="str">
         <f ca="1" t="shared" si="31"/>
-        <v>2024-10-13</v>
+        <v>2025-07-17</v>
       </c>
     </row>
     <row r="323" spans="1:18">
@@ -24451,7 +24451,7 @@
       </c>
       <c r="R323" t="str">
         <f ca="1" t="shared" ref="R323:R332" si="32">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-03-05</v>
+        <v>2025-09-02</v>
       </c>
     </row>
     <row r="324" spans="1:18">
@@ -24505,7 +24505,7 @@
       </c>
       <c r="R324" t="str">
         <f ca="1" t="shared" si="32"/>
-        <v>2024-12-31</v>
+        <v>2025-01-28</v>
       </c>
     </row>
     <row r="325" spans="1:18">
@@ -24562,7 +24562,7 @@
       </c>
       <c r="R325" t="str">
         <f ca="1" t="shared" si="32"/>
-        <v>2025-04-28</v>
+        <v>2025-08-13</v>
       </c>
     </row>
     <row r="326" spans="1:18">
@@ -24616,7 +24616,7 @@
       </c>
       <c r="R326" t="str">
         <f ca="1" t="shared" si="32"/>
-        <v>2025-01-05</v>
+        <v>2025-05-14</v>
       </c>
     </row>
     <row r="327" spans="1:18">
@@ -24674,7 +24674,7 @@
       </c>
       <c r="R327" t="str">
         <f ca="1" t="shared" si="32"/>
-        <v>2024-10-19</v>
+        <v>2025-08-20</v>
       </c>
     </row>
     <row r="328" spans="1:18">
@@ -24732,7 +24732,7 @@
       </c>
       <c r="R328" t="str">
         <f ca="1" t="shared" si="32"/>
-        <v>2024-10-04</v>
+        <v>2024-08-31</v>
       </c>
     </row>
     <row r="329" spans="1:18">
@@ -24789,7 +24789,7 @@
       </c>
       <c r="R329" t="str">
         <f ca="1" t="shared" si="32"/>
-        <v>2025-05-07</v>
+        <v>2024-09-29</v>
       </c>
     </row>
     <row r="330" spans="1:18">
@@ -24843,7 +24843,7 @@
       </c>
       <c r="R330" t="str">
         <f ca="1" t="shared" si="32"/>
-        <v>2025-08-07</v>
+        <v>2024-09-24</v>
       </c>
     </row>
     <row r="331" spans="1:18">
@@ -24897,7 +24897,7 @@
       </c>
       <c r="R331" t="str">
         <f ca="1" t="shared" si="32"/>
-        <v>2025-07-09</v>
+        <v>2025-03-16</v>
       </c>
     </row>
     <row r="332" spans="1:18">
@@ -24955,7 +24955,7 @@
       </c>
       <c r="R332" t="str">
         <f ca="1" t="shared" si="32"/>
-        <v>2025-09-19</v>
+        <v>2025-04-28</v>
       </c>
     </row>
     <row r="333" spans="1:18">
@@ -25009,7 +25009,7 @@
       </c>
       <c r="R333" t="str">
         <f ca="1" t="shared" ref="R333:R342" si="33">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-08-18</v>
+        <v>2024-12-10</v>
       </c>
     </row>
     <row r="334" spans="1:18">
@@ -25063,7 +25063,7 @@
       </c>
       <c r="R334" t="str">
         <f ca="1" t="shared" si="33"/>
-        <v>2025-05-25</v>
+        <v>2024-09-18</v>
       </c>
     </row>
     <row r="335" spans="1:18">
@@ -25117,7 +25117,7 @@
       </c>
       <c r="R335" t="str">
         <f ca="1" t="shared" si="33"/>
-        <v>2025-08-01</v>
+        <v>2024-10-10</v>
       </c>
     </row>
     <row r="336" spans="1:18">
@@ -25175,7 +25175,7 @@
       </c>
       <c r="R336" t="str">
         <f ca="1" t="shared" si="33"/>
-        <v>2025-06-16</v>
+        <v>2024-09-02</v>
       </c>
     </row>
     <row r="337" spans="1:18">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="R337" t="str">
         <f ca="1" t="shared" si="33"/>
-        <v>2024-12-10</v>
+        <v>2024-10-20</v>
       </c>
     </row>
     <row r="338" spans="1:18">
@@ -25291,7 +25291,7 @@
       </c>
       <c r="R338" t="str">
         <f ca="1" t="shared" si="33"/>
-        <v>2025-01-16</v>
+        <v>2024-12-06</v>
       </c>
     </row>
     <row r="339" spans="1:18">
@@ -25349,7 +25349,7 @@
       </c>
       <c r="R339" t="str">
         <f ca="1" t="shared" si="33"/>
-        <v>2025-07-31</v>
+        <v>2024-10-18</v>
       </c>
     </row>
     <row r="340" spans="1:18">
@@ -25407,7 +25407,7 @@
       </c>
       <c r="R340" t="str">
         <f ca="1" t="shared" si="33"/>
-        <v>2025-01-07</v>
+        <v>2025-08-16</v>
       </c>
     </row>
     <row r="341" spans="1:18">
@@ -25464,7 +25464,7 @@
       </c>
       <c r="R341" t="str">
         <f ca="1" t="shared" si="33"/>
-        <v>2024-08-23</v>
+        <v>2025-09-14</v>
       </c>
     </row>
     <row r="342" spans="1:18">
@@ -25522,7 +25522,7 @@
       </c>
       <c r="R342" t="str">
         <f ca="1" t="shared" si="33"/>
-        <v>2025-09-11</v>
+        <v>2025-06-01</v>
       </c>
     </row>
     <row r="343" spans="1:18">
@@ -25576,7 +25576,7 @@
       </c>
       <c r="R343" t="str">
         <f ca="1" t="shared" ref="R343:R352" si="34">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-04-18</v>
+        <v>2025-08-19</v>
       </c>
     </row>
     <row r="344" spans="1:18">
@@ -25631,7 +25631,7 @@
       </c>
       <c r="R344" t="str">
         <f ca="1" t="shared" si="34"/>
-        <v>2025-04-25</v>
+        <v>2025-03-30</v>
       </c>
     </row>
     <row r="345" spans="1:18">
@@ -25686,7 +25686,7 @@
       </c>
       <c r="R345" t="str">
         <f ca="1" t="shared" si="34"/>
-        <v>2025-02-14</v>
+        <v>2025-08-27</v>
       </c>
     </row>
     <row r="346" spans="1:18">
@@ -25744,7 +25744,7 @@
       </c>
       <c r="R346" t="str">
         <f ca="1" t="shared" si="34"/>
-        <v>2025-01-07</v>
+        <v>2024-10-21</v>
       </c>
     </row>
     <row r="347" spans="1:18">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="R347" t="str">
         <f ca="1" t="shared" si="34"/>
-        <v>2025-07-14</v>
+        <v>2024-12-03</v>
       </c>
     </row>
     <row r="348" spans="1:18">
@@ -25855,7 +25855,7 @@
       </c>
       <c r="R348" t="str">
         <f ca="1" t="shared" si="34"/>
-        <v>2024-09-28</v>
+        <v>2025-07-20</v>
       </c>
     </row>
     <row r="349" spans="1:18">
@@ -25913,7 +25913,7 @@
       </c>
       <c r="R349" t="str">
         <f ca="1" t="shared" si="34"/>
-        <v>2024-12-01</v>
+        <v>2025-09-18</v>
       </c>
     </row>
     <row r="350" spans="1:18">
@@ -25971,7 +25971,7 @@
       </c>
       <c r="R350" t="str">
         <f ca="1" t="shared" si="34"/>
-        <v>2025-07-15</v>
+        <v>2025-09-23</v>
       </c>
     </row>
     <row r="351" spans="1:18">
@@ -26028,7 +26028,7 @@
       </c>
       <c r="R351" t="str">
         <f ca="1" t="shared" si="34"/>
-        <v>2025-08-27</v>
+        <v>2024-11-30</v>
       </c>
     </row>
     <row r="352" spans="1:18">
@@ -26082,7 +26082,7 @@
       </c>
       <c r="R352" t="str">
         <f ca="1" t="shared" si="34"/>
-        <v>2024-11-12</v>
+        <v>2024-10-20</v>
       </c>
     </row>
     <row r="353" spans="1:18">
@@ -26136,7 +26136,7 @@
       </c>
       <c r="R353" t="str">
         <f ca="1" t="shared" ref="R353:R362" si="35">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-09-20</v>
+        <v>2024-08-16</v>
       </c>
     </row>
     <row r="354" spans="1:18">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="R354" t="str">
         <f ca="1" t="shared" si="35"/>
-        <v>2025-09-23</v>
+        <v>2024-10-05</v>
       </c>
     </row>
     <row r="355" spans="1:18">
@@ -26249,7 +26249,7 @@
       </c>
       <c r="R355" t="str">
         <f ca="1" t="shared" si="35"/>
-        <v>2025-10-07</v>
+        <v>2025-09-29</v>
       </c>
     </row>
     <row r="356" spans="1:18">
@@ -26306,7 +26306,7 @@
       </c>
       <c r="R356" t="str">
         <f ca="1" t="shared" si="35"/>
-        <v>2024-09-25</v>
+        <v>2024-10-16</v>
       </c>
     </row>
     <row r="357" spans="1:18">
@@ -26364,7 +26364,7 @@
       </c>
       <c r="R357" t="str">
         <f ca="1" t="shared" si="35"/>
-        <v>2025-06-28</v>
+        <v>2025-04-04</v>
       </c>
     </row>
     <row r="358" spans="1:18">
@@ -26422,7 +26422,7 @@
       </c>
       <c r="R358" t="str">
         <f ca="1" t="shared" si="35"/>
-        <v>2025-05-21</v>
+        <v>2024-08-22</v>
       </c>
     </row>
     <row r="359" spans="1:18">
@@ -26480,7 +26480,7 @@
       </c>
       <c r="R359" t="str">
         <f ca="1" t="shared" si="35"/>
-        <v>2024-11-23</v>
+        <v>2024-11-17</v>
       </c>
     </row>
     <row r="360" spans="1:18">
@@ -26538,7 +26538,7 @@
       </c>
       <c r="R360" t="str">
         <f ca="1" t="shared" si="35"/>
-        <v>2025-08-18</v>
+        <v>2024-12-31</v>
       </c>
     </row>
     <row r="361" spans="1:18">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="R361" t="str">
         <f ca="1" t="shared" si="35"/>
-        <v>2025-04-17</v>
+        <v>2025-03-05</v>
       </c>
     </row>
     <row r="362" spans="1:18">
@@ -26654,7 +26654,7 @@
       </c>
       <c r="R362" t="str">
         <f ca="1" t="shared" si="35"/>
-        <v>2025-02-06</v>
+        <v>2025-08-24</v>
       </c>
     </row>
     <row r="363" spans="1:18">
@@ -26712,7 +26712,7 @@
       </c>
       <c r="R363" t="str">
         <f ca="1" t="shared" ref="R363:R372" si="36">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-08-15</v>
+        <v>2025-07-26</v>
       </c>
     </row>
     <row r="364" spans="1:18">
@@ -26770,7 +26770,7 @@
       </c>
       <c r="R364" t="str">
         <f ca="1" t="shared" si="36"/>
-        <v>2025-01-10</v>
+        <v>2025-08-08</v>
       </c>
     </row>
     <row r="365" spans="1:18">
@@ -26828,7 +26828,7 @@
       </c>
       <c r="R365" t="str">
         <f ca="1" t="shared" si="36"/>
-        <v>2024-10-17</v>
+        <v>2025-02-16</v>
       </c>
     </row>
     <row r="366" spans="1:18">
@@ -26886,7 +26886,7 @@
       </c>
       <c r="R366" t="str">
         <f ca="1" t="shared" si="36"/>
-        <v>2025-09-24</v>
+        <v>2024-08-12</v>
       </c>
     </row>
     <row r="367" spans="1:18">
@@ -26944,7 +26944,7 @@
       </c>
       <c r="R367" t="str">
         <f ca="1" t="shared" si="36"/>
-        <v>2024-11-08</v>
+        <v>2024-11-11</v>
       </c>
     </row>
     <row r="368" spans="1:18">
@@ -26998,7 +26998,7 @@
       </c>
       <c r="R368" t="str">
         <f ca="1" t="shared" si="36"/>
-        <v>2025-06-15</v>
+        <v>2024-10-15</v>
       </c>
     </row>
     <row r="369" spans="1:18">
@@ -27052,7 +27052,7 @@
       </c>
       <c r="R369" t="str">
         <f ca="1" t="shared" si="36"/>
-        <v>2025-09-08</v>
+        <v>2025-01-13</v>
       </c>
     </row>
     <row r="370" spans="1:18">
@@ -27110,7 +27110,7 @@
       </c>
       <c r="R370" t="str">
         <f ca="1" t="shared" si="36"/>
-        <v>2024-12-09</v>
+        <v>2025-09-13</v>
       </c>
     </row>
     <row r="371" spans="1:18">
@@ -27168,7 +27168,7 @@
       </c>
       <c r="R371" t="str">
         <f ca="1" t="shared" si="36"/>
-        <v>2024-09-01</v>
+        <v>2025-01-27</v>
       </c>
     </row>
     <row r="372" spans="1:18">
@@ -27222,7 +27222,7 @@
       </c>
       <c r="R372" t="str">
         <f ca="1" t="shared" si="36"/>
-        <v>2025-06-19</v>
+        <v>2025-03-03</v>
       </c>
     </row>
     <row r="373" spans="1:18">
@@ -27280,7 +27280,7 @@
       </c>
       <c r="R373" t="str">
         <f ca="1" t="shared" ref="R373:R382" si="37">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-09-21</v>
+        <v>2025-07-16</v>
       </c>
     </row>
     <row r="374" spans="1:18">
@@ -27334,7 +27334,7 @@
       </c>
       <c r="R374" t="str">
         <f ca="1" t="shared" si="37"/>
-        <v>2024-11-27</v>
+        <v>2024-12-24</v>
       </c>
     </row>
     <row r="375" spans="1:18">
@@ -27388,7 +27388,7 @@
       </c>
       <c r="R375" t="str">
         <f ca="1" t="shared" si="37"/>
-        <v>2024-11-04</v>
+        <v>2024-11-13</v>
       </c>
     </row>
     <row r="376" spans="1:18">
@@ -27442,7 +27442,7 @@
       </c>
       <c r="R376" t="str">
         <f ca="1" t="shared" si="37"/>
-        <v>2025-07-03</v>
+        <v>2025-01-09</v>
       </c>
     </row>
     <row r="377" spans="1:18">
@@ -27500,7 +27500,7 @@
       </c>
       <c r="R377" t="str">
         <f ca="1" t="shared" si="37"/>
-        <v>2024-12-29</v>
+        <v>2025-07-29</v>
       </c>
     </row>
     <row r="378" spans="1:18">
@@ -27558,7 +27558,7 @@
       </c>
       <c r="R378" t="str">
         <f ca="1" t="shared" si="37"/>
-        <v>2024-12-18</v>
+        <v>2025-03-14</v>
       </c>
     </row>
     <row r="379" spans="1:18">
@@ -27616,7 +27616,7 @@
       </c>
       <c r="R379" t="str">
         <f ca="1" t="shared" si="37"/>
-        <v>2025-07-06</v>
+        <v>2025-03-22</v>
       </c>
     </row>
     <row r="380" spans="1:18">
@@ -27674,7 +27674,7 @@
       </c>
       <c r="R380" t="str">
         <f ca="1" t="shared" si="37"/>
-        <v>2024-12-24</v>
+        <v>2025-10-07</v>
       </c>
     </row>
     <row r="381" spans="1:18">
@@ -27732,7 +27732,7 @@
       </c>
       <c r="R381" t="str">
         <f ca="1" t="shared" si="37"/>
-        <v>2025-10-03</v>
+        <v>2025-02-13</v>
       </c>
     </row>
     <row r="382" spans="1:18">
@@ -27790,7 +27790,7 @@
       </c>
       <c r="R382" t="str">
         <f ca="1" t="shared" si="37"/>
-        <v>2024-12-16</v>
+        <v>2025-08-23</v>
       </c>
     </row>
     <row r="383" spans="1:18">
@@ -27848,7 +27848,7 @@
       </c>
       <c r="R383" t="str">
         <f ca="1" t="shared" ref="R383:R392" si="38">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-06-12</v>
+        <v>2024-12-13</v>
       </c>
     </row>
     <row r="384" spans="1:18">
@@ -27906,7 +27906,7 @@
       </c>
       <c r="R384" t="str">
         <f ca="1" t="shared" si="38"/>
-        <v>2025-04-27</v>
+        <v>2025-06-12</v>
       </c>
     </row>
     <row r="385" spans="1:18">
@@ -27964,7 +27964,7 @@
       </c>
       <c r="R385" t="str">
         <f ca="1" t="shared" si="38"/>
-        <v>2025-04-03</v>
+        <v>2024-12-27</v>
       </c>
     </row>
     <row r="386" spans="1:18">
@@ -28022,7 +28022,7 @@
       </c>
       <c r="R386" t="str">
         <f ca="1" t="shared" si="38"/>
-        <v>2024-09-14</v>
+        <v>2025-01-11</v>
       </c>
     </row>
     <row r="387" spans="1:18">
@@ -28080,7 +28080,7 @@
       </c>
       <c r="R387" t="str">
         <f ca="1" t="shared" si="38"/>
-        <v>2025-03-12</v>
+        <v>2024-09-23</v>
       </c>
     </row>
     <row r="388" spans="1:18">
@@ -28134,7 +28134,7 @@
       </c>
       <c r="R388" t="str">
         <f ca="1" t="shared" si="38"/>
-        <v>2025-04-07</v>
+        <v>2025-02-20</v>
       </c>
     </row>
     <row r="389" spans="1:18">
@@ -28192,7 +28192,7 @@
       </c>
       <c r="R389" t="str">
         <f ca="1" t="shared" si="38"/>
-        <v>2024-09-10</v>
+        <v>2024-10-26</v>
       </c>
     </row>
     <row r="390" spans="1:18">
@@ -28249,7 +28249,7 @@
       </c>
       <c r="R390" t="str">
         <f ca="1" t="shared" si="38"/>
-        <v>2024-10-08</v>
+        <v>2025-07-19</v>
       </c>
     </row>
     <row r="391" spans="1:18">
@@ -28307,7 +28307,7 @@
       </c>
       <c r="R391" t="str">
         <f ca="1" t="shared" si="38"/>
-        <v>2025-01-13</v>
+        <v>2024-09-14</v>
       </c>
     </row>
     <row r="392" spans="1:18">
@@ -28361,7 +28361,7 @@
       </c>
       <c r="R392" t="str">
         <f ca="1" t="shared" si="38"/>
-        <v>2025-07-08</v>
+        <v>2025-04-05</v>
       </c>
     </row>
     <row r="393" spans="1:18">
@@ -28415,7 +28415,7 @@
       </c>
       <c r="R393" t="str">
         <f ca="1" t="shared" ref="R393:R402" si="39">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-02-24</v>
+        <v>2024-09-17</v>
       </c>
     </row>
     <row r="394" spans="1:18">
@@ -28470,7 +28470,7 @@
       </c>
       <c r="R394" t="str">
         <f ca="1" t="shared" si="39"/>
-        <v>2024-11-22</v>
+        <v>2025-08-01</v>
       </c>
     </row>
     <row r="395" spans="1:18">
@@ -28528,7 +28528,7 @@
       </c>
       <c r="R395" t="str">
         <f ca="1" t="shared" si="39"/>
-        <v>2025-04-06</v>
+        <v>2025-10-05</v>
       </c>
     </row>
     <row r="396" spans="1:18">
@@ -28582,7 +28582,7 @@
       </c>
       <c r="R396" t="str">
         <f ca="1" t="shared" si="39"/>
-        <v>2024-08-02</v>
+        <v>2024-11-23</v>
       </c>
     </row>
     <row r="397" spans="1:18">
@@ -28639,7 +28639,7 @@
       </c>
       <c r="R397" t="str">
         <f ca="1" t="shared" si="39"/>
-        <v>2024-10-27</v>
+        <v>2024-08-03</v>
       </c>
     </row>
     <row r="398" spans="1:18">
@@ -28696,7 +28696,7 @@
       </c>
       <c r="R398" t="str">
         <f ca="1" t="shared" si="39"/>
-        <v>2025-04-16</v>
+        <v>2025-08-22</v>
       </c>
     </row>
     <row r="399" spans="1:18">
@@ -28750,7 +28750,7 @@
       </c>
       <c r="R399" t="str">
         <f ca="1" t="shared" si="39"/>
-        <v>2024-11-01</v>
+        <v>2024-12-21</v>
       </c>
     </row>
     <row r="400" spans="1:18">
@@ -28804,7 +28804,7 @@
       </c>
       <c r="R400" t="str">
         <f ca="1" t="shared" si="39"/>
-        <v>2025-04-15</v>
+        <v>2025-05-26</v>
       </c>
     </row>
     <row r="401" spans="1:18">
@@ -28862,7 +28862,7 @@
       </c>
       <c r="R401" t="str">
         <f ca="1" t="shared" si="39"/>
-        <v>2025-03-06</v>
+        <v>2025-10-07</v>
       </c>
     </row>
     <row r="402" spans="1:18">
@@ -28916,7 +28916,7 @@
       </c>
       <c r="R402" t="str">
         <f ca="1" t="shared" si="39"/>
-        <v>2025-02-16</v>
+        <v>2025-06-11</v>
       </c>
     </row>
     <row r="403" spans="1:18">
@@ -28974,7 +28974,7 @@
       </c>
       <c r="R403" t="str">
         <f ca="1" t="shared" ref="R403:R412" si="40">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-04-23</v>
+        <v>2025-01-04</v>
       </c>
     </row>
     <row r="404" spans="1:18">
@@ -29032,7 +29032,7 @@
       </c>
       <c r="R404" t="str">
         <f ca="1" t="shared" si="40"/>
-        <v>2025-06-05</v>
+        <v>2024-10-10</v>
       </c>
     </row>
     <row r="405" spans="1:18">
@@ -29090,7 +29090,7 @@
       </c>
       <c r="R405" t="str">
         <f ca="1" t="shared" si="40"/>
-        <v>2025-01-04</v>
+        <v>2025-08-07</v>
       </c>
     </row>
     <row r="406" spans="1:18">
@@ -29144,7 +29144,7 @@
       </c>
       <c r="R406" t="str">
         <f ca="1" t="shared" si="40"/>
-        <v>2025-03-28</v>
+        <v>2025-06-22</v>
       </c>
     </row>
     <row r="407" spans="1:18">
@@ -29202,7 +29202,7 @@
       </c>
       <c r="R407" t="str">
         <f ca="1" t="shared" si="40"/>
-        <v>2025-02-25</v>
+        <v>2024-11-14</v>
       </c>
     </row>
     <row r="408" spans="1:18">
@@ -29260,7 +29260,7 @@
       </c>
       <c r="R408" t="str">
         <f ca="1" t="shared" si="40"/>
-        <v>2025-02-20</v>
+        <v>2025-02-09</v>
       </c>
     </row>
     <row r="409" spans="1:18">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="R409" t="str">
         <f ca="1" t="shared" si="40"/>
-        <v>2025-03-07</v>
+        <v>2025-03-17</v>
       </c>
     </row>
     <row r="410" spans="1:18">
@@ -29373,7 +29373,7 @@
       </c>
       <c r="R410" t="str">
         <f ca="1" t="shared" si="40"/>
-        <v>2025-07-21</v>
+        <v>2024-11-22</v>
       </c>
     </row>
     <row r="411" spans="1:18">
@@ -29431,7 +29431,7 @@
       </c>
       <c r="R411" t="str">
         <f ca="1" t="shared" si="40"/>
-        <v>2024-12-19</v>
+        <v>2025-07-28</v>
       </c>
     </row>
     <row r="412" spans="1:18">
@@ -29489,7 +29489,7 @@
       </c>
       <c r="R412" t="str">
         <f ca="1" t="shared" si="40"/>
-        <v>2024-11-08</v>
+        <v>2024-12-13</v>
       </c>
     </row>
     <row r="413" spans="1:18">
@@ -29547,7 +29547,7 @@
       </c>
       <c r="R413" t="str">
         <f ca="1" t="shared" ref="R413:R422" si="41">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-10-09</v>
+        <v>2024-09-13</v>
       </c>
     </row>
     <row r="414" spans="1:18">
@@ -29601,7 +29601,7 @@
       </c>
       <c r="R414" t="str">
         <f ca="1" t="shared" si="41"/>
-        <v>2025-04-06</v>
+        <v>2024-08-02</v>
       </c>
     </row>
     <row r="415" spans="1:18">
@@ -29659,7 +29659,7 @@
       </c>
       <c r="R415" t="str">
         <f ca="1" t="shared" si="41"/>
-        <v>2024-12-20</v>
+        <v>2025-05-11</v>
       </c>
     </row>
     <row r="416" spans="1:18">
@@ -29717,7 +29717,7 @@
       </c>
       <c r="R416" t="str">
         <f ca="1" t="shared" si="41"/>
-        <v>2024-11-03</v>
+        <v>2024-11-22</v>
       </c>
     </row>
     <row r="417" spans="1:18">
@@ -29775,7 +29775,7 @@
       </c>
       <c r="R417" t="str">
         <f ca="1" t="shared" si="41"/>
-        <v>2025-04-09</v>
+        <v>2024-12-16</v>
       </c>
     </row>
     <row r="418" spans="1:18">
@@ -29833,7 +29833,7 @@
       </c>
       <c r="R418" t="str">
         <f ca="1" t="shared" si="41"/>
-        <v>2025-06-17</v>
+        <v>2024-09-19</v>
       </c>
     </row>
     <row r="419" spans="1:18">
@@ -29887,7 +29887,7 @@
       </c>
       <c r="R419" t="str">
         <f ca="1" t="shared" si="41"/>
-        <v>2025-02-23</v>
+        <v>2025-07-29</v>
       </c>
     </row>
     <row r="420" spans="1:18">
@@ -29945,7 +29945,7 @@
       </c>
       <c r="R420" t="str">
         <f ca="1" t="shared" si="41"/>
-        <v>2025-02-24</v>
+        <v>2025-06-13</v>
       </c>
     </row>
     <row r="421" spans="1:18">
@@ -30003,7 +30003,7 @@
       </c>
       <c r="R421" t="str">
         <f ca="1" t="shared" si="41"/>
-        <v>2025-05-29</v>
+        <v>2025-05-02</v>
       </c>
     </row>
     <row r="422" spans="1:18">
@@ -30057,7 +30057,7 @@
       </c>
       <c r="R422" t="str">
         <f ca="1" t="shared" si="41"/>
-        <v>2025-03-05</v>
+        <v>2024-11-11</v>
       </c>
     </row>
     <row r="423" spans="1:18">
@@ -30111,7 +30111,7 @@
       </c>
       <c r="R423" t="str">
         <f ca="1" t="shared" ref="R423:R432" si="42">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-08-11</v>
+        <v>2025-04-20</v>
       </c>
     </row>
     <row r="424" spans="1:18">
@@ -30169,7 +30169,7 @@
       </c>
       <c r="R424" t="str">
         <f ca="1" t="shared" si="42"/>
-        <v>2025-08-26</v>
+        <v>2025-04-20</v>
       </c>
     </row>
     <row r="425" spans="1:18">
@@ -30227,7 +30227,7 @@
       </c>
       <c r="R425" t="str">
         <f ca="1" t="shared" si="42"/>
-        <v>2024-11-04</v>
+        <v>2024-12-14</v>
       </c>
     </row>
     <row r="426" spans="1:18">
@@ -30285,7 +30285,7 @@
       </c>
       <c r="R426" t="str">
         <f ca="1" t="shared" si="42"/>
-        <v>2024-12-04</v>
+        <v>2025-10-01</v>
       </c>
     </row>
     <row r="427" spans="1:18">
@@ -30343,7 +30343,7 @@
       </c>
       <c r="R427" t="str">
         <f ca="1" t="shared" si="42"/>
-        <v>2025-03-12</v>
+        <v>2024-08-24</v>
       </c>
     </row>
     <row r="428" spans="1:18">
@@ -30401,7 +30401,7 @@
       </c>
       <c r="R428" t="str">
         <f ca="1" t="shared" si="42"/>
-        <v>2024-12-17</v>
+        <v>2025-08-19</v>
       </c>
     </row>
     <row r="429" spans="1:18">
@@ -30459,7 +30459,7 @@
       </c>
       <c r="R429" t="str">
         <f ca="1" t="shared" si="42"/>
-        <v>2024-11-20</v>
+        <v>2025-07-15</v>
       </c>
     </row>
     <row r="430" spans="1:18">
@@ -30517,7 +30517,7 @@
       </c>
       <c r="R430" t="str">
         <f ca="1" t="shared" si="42"/>
-        <v>2025-10-04</v>
+        <v>2025-01-13</v>
       </c>
     </row>
     <row r="431" spans="1:18">
@@ -30571,7 +30571,7 @@
       </c>
       <c r="R431" t="str">
         <f ca="1" t="shared" si="42"/>
-        <v>2024-09-20</v>
+        <v>2025-05-02</v>
       </c>
     </row>
     <row r="432" spans="1:18">
@@ -30629,7 +30629,7 @@
       </c>
       <c r="R432" t="str">
         <f ca="1" t="shared" si="42"/>
-        <v>2025-07-07</v>
+        <v>2024-09-26</v>
       </c>
     </row>
     <row r="433" spans="1:18">
@@ -30687,7 +30687,7 @@
       </c>
       <c r="R433" t="str">
         <f ca="1" t="shared" ref="R433:R442" si="43">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-11-05</v>
+        <v>2025-01-26</v>
       </c>
     </row>
     <row r="434" spans="1:18">
@@ -30741,7 +30741,7 @@
       </c>
       <c r="R434" t="str">
         <f ca="1" t="shared" si="43"/>
-        <v>2025-02-24</v>
+        <v>2025-05-02</v>
       </c>
     </row>
     <row r="435" spans="1:18">
@@ -30799,7 +30799,7 @@
       </c>
       <c r="R435" t="str">
         <f ca="1" t="shared" si="43"/>
-        <v>2024-12-03</v>
+        <v>2025-02-23</v>
       </c>
     </row>
     <row r="436" spans="1:18">
@@ -30853,7 +30853,7 @@
       </c>
       <c r="R436" t="str">
         <f ca="1" t="shared" si="43"/>
-        <v>2024-08-04</v>
+        <v>2025-05-17</v>
       </c>
     </row>
     <row r="437" spans="1:18">
@@ -30911,7 +30911,7 @@
       </c>
       <c r="R437" t="str">
         <f ca="1" t="shared" si="43"/>
-        <v>2024-10-29</v>
+        <v>2025-02-27</v>
       </c>
     </row>
     <row r="438" spans="1:18">
@@ -30969,7 +30969,7 @@
       </c>
       <c r="R438" t="str">
         <f ca="1" t="shared" si="43"/>
-        <v>2025-08-19</v>
+        <v>2025-03-09</v>
       </c>
     </row>
     <row r="439" spans="1:18">
@@ -31023,7 +31023,7 @@
       </c>
       <c r="R439" t="str">
         <f ca="1" t="shared" si="43"/>
-        <v>2024-08-13</v>
+        <v>2025-08-14</v>
       </c>
     </row>
     <row r="440" spans="1:18">
@@ -31081,7 +31081,7 @@
       </c>
       <c r="R440" t="str">
         <f ca="1" t="shared" si="43"/>
-        <v>2025-08-08</v>
+        <v>2024-12-18</v>
       </c>
     </row>
     <row r="441" spans="1:18">
@@ -31135,7 +31135,7 @@
       </c>
       <c r="R441" t="str">
         <f ca="1" t="shared" si="43"/>
-        <v>2024-10-04</v>
+        <v>2025-04-18</v>
       </c>
     </row>
     <row r="442" spans="1:18">
@@ -31193,7 +31193,7 @@
       </c>
       <c r="R442" t="str">
         <f ca="1" t="shared" si="43"/>
-        <v>2024-11-16</v>
+        <v>2025-01-11</v>
       </c>
     </row>
     <row r="443" spans="1:18">
@@ -31251,7 +31251,7 @@
       </c>
       <c r="R443" t="str">
         <f ca="1" t="shared" ref="R443:R452" si="44">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-08-25</v>
+        <v>2025-03-29</v>
       </c>
     </row>
     <row r="444" spans="1:18">
@@ -31309,7 +31309,7 @@
       </c>
       <c r="R444" t="str">
         <f ca="1" t="shared" si="44"/>
-        <v>2024-08-20</v>
+        <v>2025-08-22</v>
       </c>
     </row>
     <row r="445" spans="1:18">
@@ -31367,7 +31367,7 @@
       </c>
       <c r="R445" t="str">
         <f ca="1" t="shared" si="44"/>
-        <v>2024-09-27</v>
+        <v>2024-09-24</v>
       </c>
     </row>
     <row r="446" spans="1:18">
@@ -31425,7 +31425,7 @@
       </c>
       <c r="R446" t="str">
         <f ca="1" t="shared" si="44"/>
-        <v>2025-07-25</v>
+        <v>2024-09-11</v>
       </c>
     </row>
     <row r="447" spans="1:18">
@@ -31479,7 +31479,7 @@
       </c>
       <c r="R447" t="str">
         <f ca="1" t="shared" si="44"/>
-        <v>2025-02-23</v>
+        <v>2024-08-07</v>
       </c>
     </row>
     <row r="448" spans="1:18">
@@ -31537,7 +31537,7 @@
       </c>
       <c r="R448" t="str">
         <f ca="1" t="shared" si="44"/>
-        <v>2025-08-27</v>
+        <v>2024-11-18</v>
       </c>
     </row>
     <row r="449" spans="1:18">
@@ -31595,7 +31595,7 @@
       </c>
       <c r="R449" t="str">
         <f ca="1" t="shared" si="44"/>
-        <v>2025-09-01</v>
+        <v>2025-08-19</v>
       </c>
     </row>
     <row r="450" spans="1:18">
@@ -31653,7 +31653,7 @@
       </c>
       <c r="R450" t="str">
         <f ca="1" t="shared" si="44"/>
-        <v>2024-10-19</v>
+        <v>2025-09-16</v>
       </c>
     </row>
     <row r="451" spans="1:18">
@@ -31711,7 +31711,7 @@
       </c>
       <c r="R451" t="str">
         <f ca="1" t="shared" si="44"/>
-        <v>2025-08-03</v>
+        <v>2024-10-21</v>
       </c>
     </row>
     <row r="452" spans="1:18">
@@ -31769,7 +31769,7 @@
       </c>
       <c r="R452" t="str">
         <f ca="1" t="shared" si="44"/>
-        <v>2025-04-20</v>
+        <v>2024-08-17</v>
       </c>
     </row>
     <row r="453" spans="1:18">
@@ -31827,7 +31827,7 @@
       </c>
       <c r="R453" t="str">
         <f ca="1" t="shared" ref="R453:R462" si="45">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-08-10</v>
+        <v>2024-11-15</v>
       </c>
     </row>
     <row r="454" spans="1:18">
@@ -31885,7 +31885,7 @@
       </c>
       <c r="R454" t="str">
         <f ca="1" t="shared" si="45"/>
-        <v>2025-07-14</v>
+        <v>2025-03-22</v>
       </c>
     </row>
     <row r="455" spans="1:18">
@@ -31943,7 +31943,7 @@
       </c>
       <c r="R455" t="str">
         <f ca="1" t="shared" si="45"/>
-        <v>2025-05-14</v>
+        <v>2024-11-01</v>
       </c>
     </row>
     <row r="456" spans="1:18">
@@ -32001,7 +32001,7 @@
       </c>
       <c r="R456" t="str">
         <f ca="1" t="shared" si="45"/>
-        <v>2025-05-06</v>
+        <v>2025-09-03</v>
       </c>
     </row>
     <row r="457" spans="1:18">
@@ -32059,7 +32059,7 @@
       </c>
       <c r="R457" t="str">
         <f ca="1" t="shared" si="45"/>
-        <v>2024-12-16</v>
+        <v>2024-11-21</v>
       </c>
     </row>
     <row r="458" spans="1:18">
@@ -32117,7 +32117,7 @@
       </c>
       <c r="R458" t="str">
         <f ca="1" t="shared" si="45"/>
-        <v>2025-05-13</v>
+        <v>2025-01-14</v>
       </c>
     </row>
     <row r="459" spans="1:18">
@@ -32175,7 +32175,7 @@
       </c>
       <c r="R459" t="str">
         <f ca="1" t="shared" si="45"/>
-        <v>2025-01-19</v>
+        <v>2024-08-30</v>
       </c>
     </row>
     <row r="460" spans="1:18">
@@ -32233,7 +32233,7 @@
       </c>
       <c r="R460" t="str">
         <f ca="1" t="shared" si="45"/>
-        <v>2024-10-04</v>
+        <v>2025-02-20</v>
       </c>
     </row>
     <row r="461" spans="1:18">
@@ -32291,7 +32291,7 @@
       </c>
       <c r="R461" t="str">
         <f ca="1" t="shared" si="45"/>
-        <v>2024-10-30</v>
+        <v>2024-09-15</v>
       </c>
     </row>
     <row r="462" spans="1:18">
@@ -32345,7 +32345,7 @@
       </c>
       <c r="R462" t="str">
         <f ca="1" t="shared" si="45"/>
-        <v>2025-07-13</v>
+        <v>2025-02-03</v>
       </c>
     </row>
     <row r="463" spans="1:18">
@@ -32399,7 +32399,7 @@
       </c>
       <c r="R463" t="str">
         <f ca="1" t="shared" ref="R463:R472" si="46">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-09-26</v>
+        <v>2024-09-01</v>
       </c>
     </row>
     <row r="464" spans="1:18">
@@ -32457,7 +32457,7 @@
       </c>
       <c r="R464" t="str">
         <f ca="1" t="shared" si="46"/>
-        <v>2025-06-03</v>
+        <v>2025-01-22</v>
       </c>
     </row>
     <row r="465" spans="1:18">
@@ -32511,7 +32511,7 @@
       </c>
       <c r="R465" t="str">
         <f ca="1" t="shared" si="46"/>
-        <v>2024-10-13</v>
+        <v>2024-08-25</v>
       </c>
     </row>
     <row r="466" spans="1:18">
@@ -32569,7 +32569,7 @@
       </c>
       <c r="R466" t="str">
         <f ca="1" t="shared" si="46"/>
-        <v>2025-08-02</v>
+        <v>2025-06-24</v>
       </c>
     </row>
     <row r="467" spans="1:18">
@@ -32627,7 +32627,7 @@
       </c>
       <c r="R467" t="str">
         <f ca="1" t="shared" si="46"/>
-        <v>2025-04-25</v>
+        <v>2025-07-08</v>
       </c>
     </row>
     <row r="468" spans="1:18">
@@ -32685,7 +32685,7 @@
       </c>
       <c r="R468" t="str">
         <f ca="1" t="shared" si="46"/>
-        <v>2025-08-15</v>
+        <v>2025-07-28</v>
       </c>
     </row>
     <row r="469" spans="1:18">
@@ -32743,7 +32743,7 @@
       </c>
       <c r="R469" t="str">
         <f ca="1" t="shared" si="46"/>
-        <v>2025-09-11</v>
+        <v>2025-09-09</v>
       </c>
     </row>
     <row r="470" spans="1:18">
@@ -32801,7 +32801,7 @@
       </c>
       <c r="R470" t="str">
         <f ca="1" t="shared" si="46"/>
-        <v>2025-04-18</v>
+        <v>2025-06-02</v>
       </c>
     </row>
     <row r="471" spans="1:18">
@@ -32858,7 +32858,7 @@
       </c>
       <c r="R471" t="str">
         <f ca="1" t="shared" si="46"/>
-        <v>2025-01-26</v>
+        <v>2024-10-22</v>
       </c>
     </row>
     <row r="472" spans="1:18">
@@ -32915,7 +32915,7 @@
       </c>
       <c r="R472" t="str">
         <f ca="1" t="shared" si="46"/>
-        <v>2025-09-24</v>
+        <v>2025-01-03</v>
       </c>
     </row>
     <row r="473" spans="1:18">
@@ -32973,7 +32973,7 @@
       </c>
       <c r="R473" t="str">
         <f ca="1" t="shared" ref="R473:R482" si="47">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-09-22</v>
+        <v>2025-07-23</v>
       </c>
     </row>
     <row r="474" spans="1:18">
@@ -33031,7 +33031,7 @@
       </c>
       <c r="R474" t="str">
         <f ca="1" t="shared" si="47"/>
-        <v>2024-10-16</v>
+        <v>2025-06-22</v>
       </c>
     </row>
     <row r="475" spans="1:18">
@@ -33089,7 +33089,7 @@
       </c>
       <c r="R475" t="str">
         <f ca="1" t="shared" si="47"/>
-        <v>2024-08-21</v>
+        <v>2025-01-23</v>
       </c>
     </row>
     <row r="476" spans="1:18">
@@ -33143,7 +33143,7 @@
       </c>
       <c r="R476" t="str">
         <f ca="1" t="shared" si="47"/>
-        <v>2024-10-29</v>
+        <v>2024-08-18</v>
       </c>
     </row>
     <row r="477" spans="1:18">
@@ -33200,7 +33200,7 @@
       </c>
       <c r="R477" t="str">
         <f ca="1" t="shared" si="47"/>
-        <v>2024-11-12</v>
+        <v>2024-09-29</v>
       </c>
     </row>
     <row r="478" spans="1:18">
@@ -33257,7 +33257,7 @@
       </c>
       <c r="R478" t="str">
         <f ca="1" t="shared" si="47"/>
-        <v>2024-09-12</v>
+        <v>2024-08-24</v>
       </c>
     </row>
     <row r="479" spans="1:18">
@@ -33315,7 +33315,7 @@
       </c>
       <c r="R479" t="str">
         <f ca="1" t="shared" si="47"/>
-        <v>2025-02-23</v>
+        <v>2024-09-08</v>
       </c>
     </row>
     <row r="480" spans="1:18">
@@ -33369,7 +33369,7 @@
       </c>
       <c r="R480" t="str">
         <f ca="1" t="shared" si="47"/>
-        <v>2024-09-11</v>
+        <v>2024-12-07</v>
       </c>
     </row>
     <row r="481" spans="1:18">
@@ -33427,7 +33427,7 @@
       </c>
       <c r="R481" t="str">
         <f ca="1" t="shared" si="47"/>
-        <v>2025-05-29</v>
+        <v>2025-07-09</v>
       </c>
     </row>
     <row r="482" spans="1:18">
@@ -33485,7 +33485,7 @@
       </c>
       <c r="R482" t="str">
         <f ca="1" t="shared" si="47"/>
-        <v>2024-10-11</v>
+        <v>2024-09-05</v>
       </c>
     </row>
     <row r="483" spans="1:18">
@@ -33543,7 +33543,7 @@
       </c>
       <c r="R483" t="str">
         <f ca="1" t="shared" ref="R483:R492" si="48">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-09-01</v>
+        <v>2025-01-08</v>
       </c>
     </row>
     <row r="484" spans="1:18">
@@ -33597,7 +33597,7 @@
       </c>
       <c r="R484" t="str">
         <f ca="1" t="shared" si="48"/>
-        <v>2025-07-18</v>
+        <v>2025-08-30</v>
       </c>
     </row>
     <row r="485" spans="1:18">
@@ -33651,7 +33651,7 @@
       </c>
       <c r="R485" t="str">
         <f ca="1" t="shared" si="48"/>
-        <v>2025-04-01</v>
+        <v>2025-02-04</v>
       </c>
     </row>
     <row r="486" spans="1:18">
@@ -33709,7 +33709,7 @@
       </c>
       <c r="R486" t="str">
         <f ca="1" t="shared" si="48"/>
-        <v>2025-09-29</v>
+        <v>2025-05-07</v>
       </c>
     </row>
     <row r="487" spans="1:18">
@@ -33763,7 +33763,7 @@
       </c>
       <c r="R487" t="str">
         <f ca="1" t="shared" si="48"/>
-        <v>2025-08-26</v>
+        <v>2025-01-14</v>
       </c>
     </row>
     <row r="488" spans="1:18">
@@ -33821,7 +33821,7 @@
       </c>
       <c r="R488" t="str">
         <f ca="1" t="shared" si="48"/>
-        <v>2024-12-31</v>
+        <v>2024-12-29</v>
       </c>
     </row>
     <row r="489" spans="1:18">
@@ -33879,7 +33879,7 @@
       </c>
       <c r="R489" t="str">
         <f ca="1" t="shared" si="48"/>
-        <v>2025-01-19</v>
+        <v>2025-07-25</v>
       </c>
     </row>
     <row r="490" spans="1:18">
@@ -33937,7 +33937,7 @@
       </c>
       <c r="R490" t="str">
         <f ca="1" t="shared" si="48"/>
-        <v>2025-07-09</v>
+        <v>2025-09-12</v>
       </c>
     </row>
     <row r="491" spans="1:18">
@@ -33991,7 +33991,7 @@
       </c>
       <c r="R491" t="str">
         <f ca="1" t="shared" si="48"/>
-        <v>2025-08-09</v>
+        <v>2025-02-20</v>
       </c>
     </row>
     <row r="492" spans="1:18">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="R492" t="str">
         <f ca="1" t="shared" si="48"/>
-        <v>2025-03-22</v>
+        <v>2024-10-26</v>
       </c>
     </row>
     <row r="493" spans="1:18">
@@ -34101,7 +34101,7 @@
       </c>
       <c r="R493" t="str">
         <f ca="1" t="shared" ref="R493:R502" si="49">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-07-05</v>
+        <v>2025-07-06</v>
       </c>
     </row>
     <row r="494" spans="1:18">
@@ -34159,7 +34159,7 @@
       </c>
       <c r="R494" t="str">
         <f ca="1" t="shared" si="49"/>
-        <v>2024-08-10</v>
+        <v>2025-10-02</v>
       </c>
     </row>
     <row r="495" spans="1:18">
@@ -34214,7 +34214,7 @@
       </c>
       <c r="R495" t="str">
         <f ca="1" t="shared" si="49"/>
-        <v>2025-02-08</v>
+        <v>2025-07-10</v>
       </c>
     </row>
     <row r="496" spans="1:18">
@@ -34272,7 +34272,7 @@
       </c>
       <c r="R496" t="str">
         <f ca="1" t="shared" si="49"/>
-        <v>2025-03-23</v>
+        <v>2025-10-02</v>
       </c>
     </row>
     <row r="497" spans="1:18">
@@ -34326,7 +34326,7 @@
       </c>
       <c r="R497" t="str">
         <f ca="1" t="shared" si="49"/>
-        <v>2025-03-12</v>
+        <v>2025-05-31</v>
       </c>
     </row>
     <row r="498" spans="1:18">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="R498" t="str">
         <f ca="1" t="shared" si="49"/>
-        <v>2024-09-04</v>
+        <v>2025-04-03</v>
       </c>
     </row>
     <row r="499" spans="1:18">
@@ -34438,7 +34438,7 @@
       </c>
       <c r="R499" t="str">
         <f ca="1" t="shared" si="49"/>
-        <v>2024-08-24</v>
+        <v>2025-06-05</v>
       </c>
     </row>
     <row r="500" spans="1:18">
@@ -34492,7 +34492,7 @@
       </c>
       <c r="R500" t="str">
         <f ca="1" t="shared" si="49"/>
-        <v>2025-05-02</v>
+        <v>2025-04-26</v>
       </c>
     </row>
     <row r="501" spans="1:18">
@@ -34550,7 +34550,7 @@
       </c>
       <c r="R501" t="str">
         <f ca="1" t="shared" si="49"/>
-        <v>2025-06-14</v>
+        <v>2024-12-04</v>
       </c>
     </row>
     <row r="502" spans="1:18">
@@ -34607,7 +34607,7 @@
       </c>
       <c r="R502" t="str">
         <f ca="1" t="shared" si="49"/>
-        <v>2024-12-12</v>
+        <v>2025-05-06</v>
       </c>
     </row>
     <row r="503" spans="1:18">
@@ -34665,7 +34665,7 @@
       </c>
       <c r="R503" t="str">
         <f ca="1" t="shared" ref="R503:R512" si="50">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-11-04</v>
+        <v>2025-02-23</v>
       </c>
     </row>
     <row r="504" spans="1:18">
@@ -34723,7 +34723,7 @@
       </c>
       <c r="R504" t="str">
         <f ca="1" t="shared" si="50"/>
-        <v>2025-02-19</v>
+        <v>2025-09-07</v>
       </c>
     </row>
     <row r="505" spans="1:18">
@@ -34781,7 +34781,7 @@
       </c>
       <c r="R505" t="str">
         <f ca="1" t="shared" si="50"/>
-        <v>2025-09-16</v>
+        <v>2025-07-27</v>
       </c>
     </row>
     <row r="506" spans="1:18">
@@ -34839,7 +34839,7 @@
       </c>
       <c r="R506" t="str">
         <f ca="1" t="shared" si="50"/>
-        <v>2024-11-17</v>
+        <v>2025-06-24</v>
       </c>
     </row>
     <row r="507" spans="1:18">
@@ -34894,7 +34894,7 @@
       </c>
       <c r="R507" t="str">
         <f ca="1" t="shared" si="50"/>
-        <v>2024-12-23</v>
+        <v>2024-09-27</v>
       </c>
     </row>
     <row r="508" spans="1:18">
@@ -34952,7 +34952,7 @@
       </c>
       <c r="R508" t="str">
         <f ca="1" t="shared" si="50"/>
-        <v>2025-01-20</v>
+        <v>2024-11-21</v>
       </c>
     </row>
     <row r="509" spans="1:18">
@@ -35006,7 +35006,7 @@
       </c>
       <c r="R509" t="str">
         <f ca="1" t="shared" si="50"/>
-        <v>2025-01-21</v>
+        <v>2025-03-18</v>
       </c>
     </row>
     <row r="510" spans="1:18">
@@ -35064,7 +35064,7 @@
       </c>
       <c r="R510" t="str">
         <f ca="1" t="shared" si="50"/>
-        <v>2024-12-25</v>
+        <v>2025-03-02</v>
       </c>
     </row>
     <row r="511" spans="1:18">
@@ -35118,7 +35118,7 @@
       </c>
       <c r="R511" t="str">
         <f ca="1" t="shared" si="50"/>
-        <v>2025-04-23</v>
+        <v>2025-01-07</v>
       </c>
     </row>
     <row r="512" spans="1:18">
@@ -35172,7 +35172,7 @@
       </c>
       <c r="R512" t="str">
         <f ca="1" t="shared" si="50"/>
-        <v>2025-08-21</v>
+        <v>2025-08-31</v>
       </c>
     </row>
     <row r="513" spans="1:18">
@@ -35226,7 +35226,7 @@
       </c>
       <c r="R513" t="str">
         <f ca="1" t="shared" ref="R513:R522" si="51">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-09-11</v>
+        <v>2025-09-29</v>
       </c>
     </row>
     <row r="514" spans="1:18">
@@ -35280,7 +35280,7 @@
       </c>
       <c r="R514" t="str">
         <f ca="1" t="shared" si="51"/>
-        <v>2024-12-20</v>
+        <v>2025-02-11</v>
       </c>
     </row>
     <row r="515" spans="1:18">
@@ -35334,7 +35334,7 @@
       </c>
       <c r="R515" t="str">
         <f ca="1" t="shared" si="51"/>
-        <v>2024-10-16</v>
+        <v>2024-12-19</v>
       </c>
     </row>
     <row r="516" spans="1:18">
@@ -35392,7 +35392,7 @@
       </c>
       <c r="R516" t="str">
         <f ca="1" t="shared" si="51"/>
-        <v>2025-03-29</v>
+        <v>2025-07-18</v>
       </c>
     </row>
     <row r="517" spans="1:18">
@@ -35446,7 +35446,7 @@
       </c>
       <c r="R517" t="str">
         <f ca="1" t="shared" si="51"/>
-        <v>2025-10-01</v>
+        <v>2024-11-08</v>
       </c>
     </row>
     <row r="518" spans="1:18">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="R518" t="str">
         <f ca="1" t="shared" si="51"/>
-        <v>2025-08-25</v>
+        <v>2024-10-15</v>
       </c>
     </row>
     <row r="519" spans="1:18">
@@ -35562,7 +35562,7 @@
       </c>
       <c r="R519" t="str">
         <f ca="1" t="shared" si="51"/>
-        <v>2025-02-28</v>
+        <v>2025-05-31</v>
       </c>
     </row>
     <row r="520" spans="1:18">
@@ -35616,7 +35616,7 @@
       </c>
       <c r="R520" t="str">
         <f ca="1" t="shared" si="51"/>
-        <v>2024-10-13</v>
+        <v>2024-08-27</v>
       </c>
     </row>
     <row r="521" spans="1:18">
@@ -35673,7 +35673,7 @@
       </c>
       <c r="R521" t="str">
         <f ca="1" t="shared" si="51"/>
-        <v>2025-04-13</v>
+        <v>2025-04-16</v>
       </c>
     </row>
     <row r="522" spans="1:18">
@@ -35727,7 +35727,7 @@
       </c>
       <c r="R522" t="str">
         <f ca="1" t="shared" si="51"/>
-        <v>2025-02-22</v>
+        <v>2024-10-03</v>
       </c>
     </row>
     <row r="523" spans="1:18">
@@ -35781,7 +35781,7 @@
       </c>
       <c r="R523" t="str">
         <f ca="1" t="shared" ref="R523:R532" si="52">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-09-20</v>
+        <v>2024-12-29</v>
       </c>
     </row>
     <row r="524" spans="1:18">
@@ -35838,7 +35838,7 @@
       </c>
       <c r="R524" t="str">
         <f ca="1" t="shared" si="52"/>
-        <v>2024-09-25</v>
+        <v>2025-08-28</v>
       </c>
     </row>
     <row r="525" spans="1:18">
@@ -35892,7 +35892,7 @@
       </c>
       <c r="R525" t="str">
         <f ca="1" t="shared" si="52"/>
-        <v>2025-08-20</v>
+        <v>2025-10-07</v>
       </c>
     </row>
     <row r="526" spans="1:18">
@@ -35950,7 +35950,7 @@
       </c>
       <c r="R526" t="str">
         <f ca="1" t="shared" si="52"/>
-        <v>2024-10-23</v>
+        <v>2025-03-13</v>
       </c>
     </row>
     <row r="527" spans="1:18">
@@ -36008,7 +36008,7 @@
       </c>
       <c r="R527" t="str">
         <f ca="1" t="shared" si="52"/>
-        <v>2025-07-30</v>
+        <v>2025-03-14</v>
       </c>
     </row>
     <row r="528" spans="1:18">
@@ -36065,7 +36065,7 @@
       </c>
       <c r="R528" t="str">
         <f ca="1" t="shared" si="52"/>
-        <v>2024-09-03</v>
+        <v>2025-01-06</v>
       </c>
     </row>
     <row r="529" spans="1:18">
@@ -36119,7 +36119,7 @@
       </c>
       <c r="R529" t="str">
         <f ca="1" t="shared" si="52"/>
-        <v>2024-09-28</v>
+        <v>2024-09-13</v>
       </c>
     </row>
     <row r="530" spans="1:18">
@@ -36176,7 +36176,7 @@
       </c>
       <c r="R530" t="str">
         <f ca="1" t="shared" si="52"/>
-        <v>2024-08-07</v>
+        <v>2025-09-24</v>
       </c>
     </row>
     <row r="531" spans="1:18">
@@ -36234,7 +36234,7 @@
       </c>
       <c r="R531" t="str">
         <f ca="1" t="shared" si="52"/>
-        <v>2025-04-08</v>
+        <v>2024-08-06</v>
       </c>
     </row>
     <row r="532" spans="1:18">
@@ -36292,7 +36292,7 @@
       </c>
       <c r="R532" t="str">
         <f ca="1" t="shared" si="52"/>
-        <v>2024-10-01</v>
+        <v>2025-08-20</v>
       </c>
     </row>
     <row r="533" spans="1:18">
@@ -36350,7 +36350,7 @@
       </c>
       <c r="R533" t="str">
         <f ca="1" t="shared" ref="R533:R542" si="53">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-12-18</v>
+        <v>2024-12-02</v>
       </c>
     </row>
     <row r="534" spans="1:18">
@@ -36408,7 +36408,7 @@
       </c>
       <c r="R534" t="str">
         <f ca="1" t="shared" si="53"/>
-        <v>2024-11-05</v>
+        <v>2025-07-29</v>
       </c>
     </row>
     <row r="535" spans="1:18">
@@ -36462,7 +36462,7 @@
       </c>
       <c r="R535" t="str">
         <f ca="1" t="shared" si="53"/>
-        <v>2025-03-26</v>
+        <v>2024-09-18</v>
       </c>
     </row>
     <row r="536" spans="1:18">
@@ -36520,7 +36520,7 @@
       </c>
       <c r="R536" t="str">
         <f ca="1" t="shared" si="53"/>
-        <v>2024-08-17</v>
+        <v>2025-03-29</v>
       </c>
     </row>
     <row r="537" spans="1:18">
@@ -36574,7 +36574,7 @@
       </c>
       <c r="R537" t="str">
         <f ca="1" t="shared" si="53"/>
-        <v>2024-12-21</v>
+        <v>2025-02-01</v>
       </c>
     </row>
     <row r="538" spans="1:18">
@@ -36631,7 +36631,7 @@
       </c>
       <c r="R538" t="str">
         <f ca="1" t="shared" si="53"/>
-        <v>2025-06-25</v>
+        <v>2024-08-04</v>
       </c>
     </row>
     <row r="539" spans="1:18">
@@ -36685,7 +36685,7 @@
       </c>
       <c r="R539" t="str">
         <f ca="1" t="shared" si="53"/>
-        <v>2025-05-14</v>
+        <v>2025-08-31</v>
       </c>
     </row>
     <row r="540" spans="1:18">
@@ -36743,7 +36743,7 @@
       </c>
       <c r="R540" t="str">
         <f ca="1" t="shared" si="53"/>
-        <v>2025-07-26</v>
+        <v>2025-09-20</v>
       </c>
     </row>
     <row r="541" spans="1:18">
@@ -36801,7 +36801,7 @@
       </c>
       <c r="R541" t="str">
         <f ca="1" t="shared" si="53"/>
-        <v>2025-04-22</v>
+        <v>2024-11-27</v>
       </c>
     </row>
     <row r="542" spans="1:18">
@@ -36859,7 +36859,7 @@
       </c>
       <c r="R542" t="str">
         <f ca="1" t="shared" si="53"/>
-        <v>2025-02-23</v>
+        <v>2025-06-07</v>
       </c>
     </row>
     <row r="543" spans="1:18">
@@ -36913,7 +36913,7 @@
       </c>
       <c r="R543" t="str">
         <f ca="1" t="shared" ref="R543:R552" si="54">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-09-21</v>
+        <v>2024-08-18</v>
       </c>
     </row>
     <row r="544" spans="1:18">
@@ -36971,7 +36971,7 @@
       </c>
       <c r="R544" t="str">
         <f ca="1" t="shared" si="54"/>
-        <v>2025-09-11</v>
+        <v>2025-01-29</v>
       </c>
     </row>
     <row r="545" spans="1:18">
@@ -37025,7 +37025,7 @@
       </c>
       <c r="R545" t="str">
         <f ca="1" t="shared" si="54"/>
-        <v>2025-05-04</v>
+        <v>2024-11-09</v>
       </c>
     </row>
     <row r="546" spans="1:18">
@@ -37083,7 +37083,7 @@
       </c>
       <c r="R546" t="str">
         <f ca="1" t="shared" si="54"/>
-        <v>2025-02-14</v>
+        <v>2024-12-20</v>
       </c>
     </row>
     <row r="547" spans="1:18">
@@ -37137,7 +37137,7 @@
       </c>
       <c r="R547" t="str">
         <f ca="1" t="shared" si="54"/>
-        <v>2024-12-07</v>
+        <v>2024-08-29</v>
       </c>
     </row>
     <row r="548" spans="1:18">
@@ -37195,7 +37195,7 @@
       </c>
       <c r="R548" t="str">
         <f ca="1" t="shared" si="54"/>
-        <v>2025-05-14</v>
+        <v>2025-02-21</v>
       </c>
     </row>
     <row r="549" spans="1:18">
@@ -37249,7 +37249,7 @@
       </c>
       <c r="R549" t="str">
         <f ca="1" t="shared" si="54"/>
-        <v>2024-10-03</v>
+        <v>2024-11-26</v>
       </c>
     </row>
     <row r="550" spans="1:18">
@@ -37303,7 +37303,7 @@
       </c>
       <c r="R550" t="str">
         <f ca="1" t="shared" si="54"/>
-        <v>2025-07-31</v>
+        <v>2024-08-26</v>
       </c>
     </row>
     <row r="551" spans="1:18">
@@ -37360,7 +37360,7 @@
       </c>
       <c r="R551" t="str">
         <f ca="1" t="shared" si="54"/>
-        <v>2025-03-23</v>
+        <v>2025-03-29</v>
       </c>
     </row>
     <row r="552" spans="1:18">
@@ -37414,7 +37414,7 @@
       </c>
       <c r="R552" t="str">
         <f ca="1" t="shared" si="54"/>
-        <v>2025-04-20</v>
+        <v>2024-10-13</v>
       </c>
     </row>
     <row r="553" spans="1:18">
@@ -37471,7 +37471,7 @@
       </c>
       <c r="R553" t="str">
         <f ca="1" t="shared" ref="R553:R562" si="55">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-09-17</v>
+        <v>2025-04-21</v>
       </c>
     </row>
     <row r="554" spans="1:18">
@@ -37529,7 +37529,7 @@
       </c>
       <c r="R554" t="str">
         <f ca="1" t="shared" si="55"/>
-        <v>2024-09-24</v>
+        <v>2025-03-23</v>
       </c>
     </row>
     <row r="555" spans="1:18">
@@ -37587,7 +37587,7 @@
       </c>
       <c r="R555" t="str">
         <f ca="1" t="shared" si="55"/>
-        <v>2025-03-23</v>
+        <v>2025-10-04</v>
       </c>
     </row>
     <row r="556" spans="1:18">
@@ -37645,7 +37645,7 @@
       </c>
       <c r="R556" t="str">
         <f ca="1" t="shared" si="55"/>
-        <v>2024-10-01</v>
+        <v>2025-03-09</v>
       </c>
     </row>
     <row r="557" spans="1:18">
@@ -37703,7 +37703,7 @@
       </c>
       <c r="R557" t="str">
         <f ca="1" t="shared" si="55"/>
-        <v>2025-04-06</v>
+        <v>2024-12-17</v>
       </c>
     </row>
     <row r="558" spans="1:18">
@@ -37761,7 +37761,7 @@
       </c>
       <c r="R558" t="str">
         <f ca="1" t="shared" si="55"/>
-        <v>2025-04-15</v>
+        <v>2024-11-04</v>
       </c>
     </row>
     <row r="559" spans="1:18">
@@ -37819,7 +37819,7 @@
       </c>
       <c r="R559" t="str">
         <f ca="1" t="shared" si="55"/>
-        <v>2025-07-10</v>
+        <v>2025-04-18</v>
       </c>
     </row>
     <row r="560" spans="1:18">
@@ -37877,7 +37877,7 @@
       </c>
       <c r="R560" t="str">
         <f ca="1" t="shared" si="55"/>
-        <v>2025-09-04</v>
+        <v>2025-08-21</v>
       </c>
     </row>
     <row r="561" spans="1:18">
@@ -37935,7 +37935,7 @@
       </c>
       <c r="R561" t="str">
         <f ca="1" t="shared" si="55"/>
-        <v>2024-10-12</v>
+        <v>2025-01-22</v>
       </c>
     </row>
     <row r="562" spans="1:18">
@@ -37993,7 +37993,7 @@
       </c>
       <c r="R562" t="str">
         <f ca="1" t="shared" si="55"/>
-        <v>2025-05-24</v>
+        <v>2024-08-03</v>
       </c>
     </row>
     <row r="563" spans="1:18">
@@ -38051,7 +38051,7 @@
       </c>
       <c r="R563" t="str">
         <f ca="1" t="shared" ref="R563:R572" si="56">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-07-29</v>
+        <v>2025-04-12</v>
       </c>
     </row>
     <row r="564" spans="1:18">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="R564" t="str">
         <f ca="1" t="shared" si="56"/>
-        <v>2025-07-12</v>
+        <v>2024-10-26</v>
       </c>
     </row>
     <row r="565" spans="1:18">
@@ -38167,7 +38167,7 @@
       </c>
       <c r="R565" t="str">
         <f ca="1" t="shared" si="56"/>
-        <v>2025-07-22</v>
+        <v>2024-08-31</v>
       </c>
     </row>
     <row r="566" spans="1:18">
@@ -38221,7 +38221,7 @@
       </c>
       <c r="R566" t="str">
         <f ca="1" t="shared" si="56"/>
-        <v>2024-10-24</v>
+        <v>2024-08-11</v>
       </c>
     </row>
     <row r="567" spans="1:18">
@@ -38279,7 +38279,7 @@
       </c>
       <c r="R567" t="str">
         <f ca="1" t="shared" si="56"/>
-        <v>2024-08-06</v>
+        <v>2025-06-28</v>
       </c>
     </row>
     <row r="568" spans="1:18">
@@ -38337,7 +38337,7 @@
       </c>
       <c r="R568" t="str">
         <f ca="1" t="shared" si="56"/>
-        <v>2024-12-11</v>
+        <v>2025-04-16</v>
       </c>
     </row>
     <row r="569" spans="1:18">
@@ -38395,7 +38395,7 @@
       </c>
       <c r="R569" t="str">
         <f ca="1" t="shared" si="56"/>
-        <v>2024-11-13</v>
+        <v>2025-07-24</v>
       </c>
     </row>
     <row r="570" spans="1:18">
@@ -38453,7 +38453,7 @@
       </c>
       <c r="R570" t="str">
         <f ca="1" t="shared" si="56"/>
-        <v>2025-09-10</v>
+        <v>2025-06-20</v>
       </c>
     </row>
     <row r="571" spans="1:18">
@@ -38507,7 +38507,7 @@
       </c>
       <c r="R571" t="str">
         <f ca="1" t="shared" si="56"/>
-        <v>2025-04-18</v>
+        <v>2025-05-02</v>
       </c>
     </row>
     <row r="572" spans="1:18">
@@ -38565,7 +38565,7 @@
       </c>
       <c r="R572" t="str">
         <f ca="1" t="shared" si="56"/>
-        <v>2025-04-13</v>
+        <v>2025-04-16</v>
       </c>
     </row>
     <row r="573" spans="1:18">
@@ -38619,7 +38619,7 @@
       </c>
       <c r="R573" t="str">
         <f ca="1" t="shared" ref="R573:R582" si="57">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-10-10</v>
+        <v>2025-05-28</v>
       </c>
     </row>
     <row r="574" spans="1:18">
@@ -38677,7 +38677,7 @@
       </c>
       <c r="R574" t="str">
         <f ca="1" t="shared" si="57"/>
-        <v>2025-07-13</v>
+        <v>2024-09-15</v>
       </c>
     </row>
     <row r="575" spans="1:18">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="R575" t="str">
         <f ca="1" t="shared" si="57"/>
-        <v>2024-10-23</v>
+        <v>2025-04-11</v>
       </c>
     </row>
     <row r="576" spans="1:18">
@@ -38793,7 +38793,7 @@
       </c>
       <c r="R576" t="str">
         <f ca="1" t="shared" si="57"/>
-        <v>2025-07-28</v>
+        <v>2024-09-13</v>
       </c>
     </row>
     <row r="577" spans="1:18">
@@ -38851,7 +38851,7 @@
       </c>
       <c r="R577" t="str">
         <f ca="1" t="shared" si="57"/>
-        <v>2025-07-03</v>
+        <v>2025-09-22</v>
       </c>
     </row>
     <row r="578" spans="1:18">
@@ -38909,7 +38909,7 @@
       </c>
       <c r="R578" t="str">
         <f ca="1" t="shared" si="57"/>
-        <v>2025-05-11</v>
+        <v>2025-03-11</v>
       </c>
     </row>
     <row r="579" spans="1:18">
@@ -38963,7 +38963,7 @@
       </c>
       <c r="R579" t="str">
         <f ca="1" t="shared" si="57"/>
-        <v>2025-05-12</v>
+        <v>2024-09-14</v>
       </c>
     </row>
     <row r="580" spans="1:18">
@@ -39020,7 +39020,7 @@
       </c>
       <c r="R580" t="str">
         <f ca="1" t="shared" si="57"/>
-        <v>2025-09-05</v>
+        <v>2025-08-22</v>
       </c>
     </row>
     <row r="581" spans="1:18">
@@ -39078,7 +39078,7 @@
       </c>
       <c r="R581" t="str">
         <f ca="1" t="shared" si="57"/>
-        <v>2024-12-31</v>
+        <v>2025-01-13</v>
       </c>
     </row>
     <row r="582" spans="1:18">
@@ -39133,7 +39133,7 @@
       </c>
       <c r="R582" t="str">
         <f ca="1" t="shared" si="57"/>
-        <v>2025-03-16</v>
+        <v>2025-10-06</v>
       </c>
     </row>
     <row r="583" spans="1:18">
@@ -39191,7 +39191,7 @@
       </c>
       <c r="R583" t="str">
         <f ca="1" t="shared" ref="R583:R592" si="58">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-09-30</v>
+        <v>2025-08-25</v>
       </c>
     </row>
     <row r="584" spans="1:18">
@@ -39248,7 +39248,7 @@
       </c>
       <c r="R584" t="str">
         <f ca="1" t="shared" si="58"/>
-        <v>2024-09-20</v>
+        <v>2024-09-01</v>
       </c>
     </row>
     <row r="585" spans="1:18">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="R585" t="str">
         <f ca="1" t="shared" si="58"/>
-        <v>2025-07-07</v>
+        <v>2025-07-17</v>
       </c>
     </row>
     <row r="586" spans="1:18">
@@ -39364,7 +39364,7 @@
       </c>
       <c r="R586" t="str">
         <f ca="1" t="shared" si="58"/>
-        <v>2024-09-22</v>
+        <v>2024-10-10</v>
       </c>
     </row>
     <row r="587" spans="1:18">
@@ -39422,7 +39422,7 @@
       </c>
       <c r="R587" t="str">
         <f ca="1" t="shared" si="58"/>
-        <v>2025-02-22</v>
+        <v>2025-05-31</v>
       </c>
     </row>
     <row r="588" spans="1:18">
@@ -39476,7 +39476,7 @@
       </c>
       <c r="R588" t="str">
         <f ca="1" t="shared" si="58"/>
-        <v>2025-06-25</v>
+        <v>2024-10-31</v>
       </c>
     </row>
     <row r="589" spans="1:18">
@@ -39534,7 +39534,7 @@
       </c>
       <c r="R589" t="str">
         <f ca="1" t="shared" si="58"/>
-        <v>2025-07-23</v>
+        <v>2024-08-13</v>
       </c>
     </row>
     <row r="590" spans="1:18">
@@ -39588,7 +39588,7 @@
       </c>
       <c r="R590" t="str">
         <f ca="1" t="shared" si="58"/>
-        <v>2025-02-28</v>
+        <v>2025-03-07</v>
       </c>
     </row>
     <row r="591" spans="1:18">
@@ -39646,7 +39646,7 @@
       </c>
       <c r="R591" t="str">
         <f ca="1" t="shared" si="58"/>
-        <v>2025-03-08</v>
+        <v>2025-02-18</v>
       </c>
     </row>
     <row r="592" spans="1:18">
@@ -39704,7 +39704,7 @@
       </c>
       <c r="R592" t="str">
         <f ca="1" t="shared" si="58"/>
-        <v>2025-09-08</v>
+        <v>2024-11-13</v>
       </c>
     </row>
     <row r="593" spans="1:18">
@@ -39762,7 +39762,7 @@
       </c>
       <c r="R593" t="str">
         <f ca="1" t="shared" ref="R593:R602" si="59">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-04-11</v>
+        <v>2025-04-13</v>
       </c>
     </row>
     <row r="594" spans="1:18">
@@ -39816,7 +39816,7 @@
       </c>
       <c r="R594" t="str">
         <f ca="1" t="shared" si="59"/>
-        <v>2025-06-18</v>
+        <v>2025-02-27</v>
       </c>
     </row>
     <row r="595" spans="1:18">
@@ -39871,7 +39871,7 @@
       </c>
       <c r="R595" t="str">
         <f ca="1" t="shared" si="59"/>
-        <v>2024-11-21</v>
+        <v>2024-10-12</v>
       </c>
     </row>
     <row r="596" spans="1:18">
@@ -39929,7 +39929,7 @@
       </c>
       <c r="R596" t="str">
         <f ca="1" t="shared" si="59"/>
-        <v>2025-03-08</v>
+        <v>2025-03-14</v>
       </c>
     </row>
     <row r="597" spans="1:18">
@@ -39983,7 +39983,7 @@
       </c>
       <c r="R597" t="str">
         <f ca="1" t="shared" si="59"/>
-        <v>2025-09-07</v>
+        <v>2024-09-03</v>
       </c>
     </row>
     <row r="598" spans="1:18">
@@ -40040,7 +40040,7 @@
       </c>
       <c r="R598" t="str">
         <f ca="1" t="shared" si="59"/>
-        <v>2025-05-04</v>
+        <v>2025-04-07</v>
       </c>
     </row>
     <row r="599" spans="1:18">
@@ -40094,7 +40094,7 @@
       </c>
       <c r="R599" t="str">
         <f ca="1" t="shared" si="59"/>
-        <v>2025-05-22</v>
+        <v>2025-07-24</v>
       </c>
     </row>
     <row r="600" spans="1:18">
@@ -40148,7 +40148,7 @@
       </c>
       <c r="R600" t="str">
         <f ca="1" t="shared" si="59"/>
-        <v>2024-09-02</v>
+        <v>2025-05-13</v>
       </c>
     </row>
     <row r="601" spans="1:18">
@@ -40202,7 +40202,7 @@
       </c>
       <c r="R601" t="str">
         <f ca="1" t="shared" si="59"/>
-        <v>2025-09-30</v>
+        <v>2025-03-22</v>
       </c>
     </row>
     <row r="602" spans="1:18">
@@ -40260,7 +40260,7 @@
       </c>
       <c r="R602" t="str">
         <f ca="1" t="shared" si="59"/>
-        <v>2025-10-02</v>
+        <v>2025-02-10</v>
       </c>
     </row>
     <row r="603" spans="1:18">
@@ -40317,7 +40317,7 @@
       </c>
       <c r="R603" t="str">
         <f ca="1" t="shared" ref="R603:R612" si="60">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-09-13</v>
+        <v>2025-06-28</v>
       </c>
     </row>
     <row r="604" spans="1:18">
@@ -40375,7 +40375,7 @@
       </c>
       <c r="R604" t="str">
         <f ca="1" t="shared" si="60"/>
-        <v>2024-08-13</v>
+        <v>2025-10-07</v>
       </c>
     </row>
     <row r="605" spans="1:18">
@@ -40429,7 +40429,7 @@
       </c>
       <c r="R605" t="str">
         <f ca="1" t="shared" si="60"/>
-        <v>2025-09-09</v>
+        <v>2024-12-14</v>
       </c>
     </row>
     <row r="606" spans="1:18">
@@ -40486,7 +40486,7 @@
       </c>
       <c r="R606" t="str">
         <f ca="1" t="shared" si="60"/>
-        <v>2025-02-09</v>
+        <v>2024-09-27</v>
       </c>
     </row>
     <row r="607" spans="1:18">
@@ -40544,7 +40544,7 @@
       </c>
       <c r="R607" t="str">
         <f ca="1" t="shared" si="60"/>
-        <v>2025-01-20</v>
+        <v>2025-07-07</v>
       </c>
     </row>
     <row r="608" spans="1:18">
@@ -40598,7 +40598,7 @@
       </c>
       <c r="R608" t="str">
         <f ca="1" t="shared" si="60"/>
-        <v>2025-08-17</v>
+        <v>2025-01-18</v>
       </c>
     </row>
     <row r="609" spans="1:18">
@@ -40656,7 +40656,7 @@
       </c>
       <c r="R609" t="str">
         <f ca="1" t="shared" si="60"/>
-        <v>2025-04-27</v>
+        <v>2024-09-20</v>
       </c>
     </row>
     <row r="610" spans="1:18">
@@ -40714,7 +40714,7 @@
       </c>
       <c r="R610" t="str">
         <f ca="1" t="shared" si="60"/>
-        <v>2024-09-19</v>
+        <v>2025-07-07</v>
       </c>
     </row>
     <row r="611" spans="1:18">
@@ -40769,7 +40769,7 @@
       </c>
       <c r="R611" t="str">
         <f ca="1" t="shared" si="60"/>
-        <v>2025-09-02</v>
+        <v>2024-08-02</v>
       </c>
     </row>
     <row r="612" spans="1:18">
@@ -40823,7 +40823,7 @@
       </c>
       <c r="R612" t="str">
         <f ca="1" t="shared" si="60"/>
-        <v>2025-07-20</v>
+        <v>2025-07-23</v>
       </c>
     </row>
     <row r="613" spans="1:18">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="R613" t="str">
         <f ca="1" t="shared" ref="R613:R622" si="61">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-10-23</v>
+        <v>2025-02-06</v>
       </c>
     </row>
     <row r="614" spans="1:18">
@@ -40935,7 +40935,7 @@
       </c>
       <c r="R614" t="str">
         <f ca="1" t="shared" si="61"/>
-        <v>2025-06-25</v>
+        <v>2024-12-10</v>
       </c>
     </row>
     <row r="615" spans="1:18">
@@ -40992,7 +40992,7 @@
       </c>
       <c r="R615" t="str">
         <f ca="1" t="shared" si="61"/>
-        <v>2025-03-09</v>
+        <v>2024-12-09</v>
       </c>
     </row>
     <row r="616" spans="1:18">
@@ -41050,7 +41050,7 @@
       </c>
       <c r="R616" t="str">
         <f ca="1" t="shared" si="61"/>
-        <v>2024-08-12</v>
+        <v>2025-05-13</v>
       </c>
     </row>
     <row r="617" spans="1:18">
@@ -41108,7 +41108,7 @@
       </c>
       <c r="R617" t="str">
         <f ca="1" t="shared" si="61"/>
-        <v>2024-09-10</v>
+        <v>2025-07-23</v>
       </c>
     </row>
     <row r="618" spans="1:18">
@@ -41166,7 +41166,7 @@
       </c>
       <c r="R618" t="str">
         <f ca="1" t="shared" si="61"/>
-        <v>2024-11-08</v>
+        <v>2025-05-15</v>
       </c>
     </row>
     <row r="619" spans="1:18">
@@ -41223,7 +41223,7 @@
       </c>
       <c r="R619" t="str">
         <f ca="1" t="shared" si="61"/>
-        <v>2024-10-14</v>
+        <v>2025-05-04</v>
       </c>
     </row>
     <row r="620" spans="1:18">
@@ -41280,7 +41280,7 @@
       </c>
       <c r="R620" t="str">
         <f ca="1" t="shared" si="61"/>
-        <v>2024-09-18</v>
+        <v>2025-05-22</v>
       </c>
     </row>
     <row r="621" spans="1:18">
@@ -41337,7 +41337,7 @@
       </c>
       <c r="R621" t="str">
         <f ca="1" t="shared" si="61"/>
-        <v>2025-08-24</v>
+        <v>2024-08-07</v>
       </c>
     </row>
     <row r="622" spans="1:18">
@@ -41394,7 +41394,7 @@
       </c>
       <c r="R622" t="str">
         <f ca="1" t="shared" si="61"/>
-        <v>2024-11-18</v>
+        <v>2025-07-29</v>
       </c>
     </row>
     <row r="623" spans="1:18">
@@ -41448,7 +41448,7 @@
       </c>
       <c r="R623" t="str">
         <f ca="1" t="shared" ref="R623:R632" si="62">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-08-20</v>
+        <v>2025-04-17</v>
       </c>
     </row>
     <row r="624" spans="1:18">
@@ -41506,7 +41506,7 @@
       </c>
       <c r="R624" t="str">
         <f ca="1" t="shared" si="62"/>
-        <v>2025-07-04</v>
+        <v>2025-07-25</v>
       </c>
     </row>
     <row r="625" spans="1:18">
@@ -41560,7 +41560,7 @@
       </c>
       <c r="R625" t="str">
         <f ca="1" t="shared" si="62"/>
-        <v>2025-04-25</v>
+        <v>2025-04-05</v>
       </c>
     </row>
     <row r="626" spans="1:18">
@@ -41618,7 +41618,7 @@
       </c>
       <c r="R626" t="str">
         <f ca="1" t="shared" si="62"/>
-        <v>2025-01-26</v>
+        <v>2024-08-25</v>
       </c>
     </row>
     <row r="627" spans="1:18">
@@ -41676,7 +41676,7 @@
       </c>
       <c r="R627" t="str">
         <f ca="1" t="shared" si="62"/>
-        <v>2025-01-29</v>
+        <v>2024-08-31</v>
       </c>
     </row>
     <row r="628" spans="1:18">
@@ -41731,7 +41731,7 @@
       </c>
       <c r="R628" t="str">
         <f ca="1" t="shared" si="62"/>
-        <v>2025-09-01</v>
+        <v>2025-01-25</v>
       </c>
     </row>
     <row r="629" spans="1:18">
@@ -41789,7 +41789,7 @@
       </c>
       <c r="R629" t="str">
         <f ca="1" t="shared" si="62"/>
-        <v>2024-08-14</v>
+        <v>2025-05-12</v>
       </c>
     </row>
     <row r="630" spans="1:18">
@@ -41847,7 +41847,7 @@
       </c>
       <c r="R630" t="str">
         <f ca="1" t="shared" si="62"/>
-        <v>2024-11-06</v>
+        <v>2025-09-09</v>
       </c>
     </row>
     <row r="631" spans="1:18">
@@ -41905,7 +41905,7 @@
       </c>
       <c r="R631" t="str">
         <f ca="1" t="shared" si="62"/>
-        <v>2025-05-25</v>
+        <v>2025-05-22</v>
       </c>
     </row>
     <row r="632" spans="1:18">
@@ -41959,7 +41959,7 @@
       </c>
       <c r="R632" t="str">
         <f ca="1" t="shared" si="62"/>
-        <v>2025-05-04</v>
+        <v>2025-04-12</v>
       </c>
     </row>
     <row r="633" spans="1:18">
@@ -42017,7 +42017,7 @@
       </c>
       <c r="R633" t="str">
         <f ca="1" t="shared" ref="R633:R642" si="63">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-08-26</v>
+        <v>2025-08-05</v>
       </c>
     </row>
     <row r="634" spans="1:18">
@@ -42072,7 +42072,7 @@
       </c>
       <c r="R634" t="str">
         <f ca="1" t="shared" si="63"/>
-        <v>2024-12-31</v>
+        <v>2025-09-09</v>
       </c>
     </row>
     <row r="635" spans="1:18">
@@ -42127,7 +42127,7 @@
       </c>
       <c r="R635" t="str">
         <f ca="1" t="shared" si="63"/>
-        <v>2024-08-28</v>
+        <v>2025-02-05</v>
       </c>
     </row>
     <row r="636" spans="1:18">
@@ -42185,7 +42185,7 @@
       </c>
       <c r="R636" t="str">
         <f ca="1" t="shared" si="63"/>
-        <v>2025-06-10</v>
+        <v>2025-04-21</v>
       </c>
     </row>
     <row r="637" spans="1:18">
@@ -42243,7 +42243,7 @@
       </c>
       <c r="R637" t="str">
         <f ca="1" t="shared" si="63"/>
-        <v>2025-04-06</v>
+        <v>2025-07-25</v>
       </c>
     </row>
     <row r="638" spans="1:18">
@@ -42301,7 +42301,7 @@
       </c>
       <c r="R638" t="str">
         <f ca="1" t="shared" si="63"/>
-        <v>2025-03-08</v>
+        <v>2025-05-08</v>
       </c>
     </row>
     <row r="639" spans="1:18">
@@ -42355,7 +42355,7 @@
       </c>
       <c r="R639" t="str">
         <f ca="1" t="shared" si="63"/>
-        <v>2024-12-04</v>
+        <v>2024-11-08</v>
       </c>
     </row>
     <row r="640" spans="1:18">
@@ -42410,7 +42410,7 @@
       </c>
       <c r="R640" t="str">
         <f ca="1" t="shared" si="63"/>
-        <v>2025-07-26</v>
+        <v>2024-12-27</v>
       </c>
     </row>
     <row r="641" spans="1:18">
@@ -42468,7 +42468,7 @@
       </c>
       <c r="R641" t="str">
         <f ca="1" t="shared" si="63"/>
-        <v>2025-08-30</v>
+        <v>2024-10-26</v>
       </c>
     </row>
     <row r="642" spans="1:18">
@@ -42522,7 +42522,7 @@
       </c>
       <c r="R642" t="str">
         <f ca="1" t="shared" si="63"/>
-        <v>2025-03-12</v>
+        <v>2024-10-10</v>
       </c>
     </row>
     <row r="643" spans="1:18">
@@ -42580,7 +42580,7 @@
       </c>
       <c r="R643" t="str">
         <f ca="1" t="shared" ref="R643:R652" si="64">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-09-21</v>
+        <v>2024-09-04</v>
       </c>
     </row>
     <row r="644" spans="1:18">
@@ -42638,7 +42638,7 @@
       </c>
       <c r="R644" t="str">
         <f ca="1" t="shared" si="64"/>
-        <v>2025-02-16</v>
+        <v>2024-08-12</v>
       </c>
     </row>
     <row r="645" spans="1:18">
@@ -42692,7 +42692,7 @@
       </c>
       <c r="R645" t="str">
         <f ca="1" t="shared" si="64"/>
-        <v>2024-08-08</v>
+        <v>2024-10-15</v>
       </c>
     </row>
     <row r="646" spans="1:18">
@@ -42750,7 +42750,7 @@
       </c>
       <c r="R646" t="str">
         <f ca="1" t="shared" si="64"/>
-        <v>2025-06-02</v>
+        <v>2025-07-13</v>
       </c>
     </row>
     <row r="647" spans="1:18">
@@ -42807,7 +42807,7 @@
       </c>
       <c r="R647" t="str">
         <f ca="1" t="shared" si="64"/>
-        <v>2025-05-27</v>
+        <v>2025-08-18</v>
       </c>
     </row>
     <row r="648" spans="1:18">
@@ -42861,7 +42861,7 @@
       </c>
       <c r="R648" t="str">
         <f ca="1" t="shared" si="64"/>
-        <v>2025-03-14</v>
+        <v>2024-09-26</v>
       </c>
     </row>
     <row r="649" spans="1:18">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="R649" t="str">
         <f ca="1" t="shared" si="64"/>
-        <v>2025-04-02</v>
+        <v>2025-07-21</v>
       </c>
     </row>
     <row r="650" spans="1:18">
@@ -42977,7 +42977,7 @@
       </c>
       <c r="R650" t="str">
         <f ca="1" t="shared" si="64"/>
-        <v>2025-03-27</v>
+        <v>2025-01-25</v>
       </c>
     </row>
     <row r="651" spans="1:18">
@@ -43035,7 +43035,7 @@
       </c>
       <c r="R651" t="str">
         <f ca="1" t="shared" si="64"/>
-        <v>2025-01-12</v>
+        <v>2025-06-11</v>
       </c>
     </row>
     <row r="652" spans="1:18">
@@ -43089,7 +43089,7 @@
       </c>
       <c r="R652" t="str">
         <f ca="1" t="shared" si="64"/>
-        <v>2025-09-14</v>
+        <v>2024-09-21</v>
       </c>
     </row>
     <row r="653" spans="1:18">
@@ -43146,7 +43146,7 @@
       </c>
       <c r="R653" t="str">
         <f ca="1" t="shared" ref="R653:R662" si="65">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-09-06</v>
+        <v>2024-10-25</v>
       </c>
     </row>
     <row r="654" spans="1:18">
@@ -43200,7 +43200,7 @@
       </c>
       <c r="R654" t="str">
         <f ca="1" t="shared" si="65"/>
-        <v>2025-01-20</v>
+        <v>2024-08-15</v>
       </c>
     </row>
     <row r="655" spans="1:18">
@@ -43257,7 +43257,7 @@
       </c>
       <c r="R655" t="str">
         <f ca="1" t="shared" si="65"/>
-        <v>2025-03-31</v>
+        <v>2025-03-16</v>
       </c>
     </row>
     <row r="656" spans="1:18">
@@ -43315,7 +43315,7 @@
       </c>
       <c r="R656" t="str">
         <f ca="1" t="shared" si="65"/>
-        <v>2024-09-16</v>
+        <v>2025-04-11</v>
       </c>
     </row>
     <row r="657" spans="1:18">
@@ -43373,7 +43373,7 @@
       </c>
       <c r="R657" t="str">
         <f ca="1" t="shared" si="65"/>
-        <v>2025-06-29</v>
+        <v>2025-05-27</v>
       </c>
     </row>
     <row r="658" spans="1:18">
@@ -43431,7 +43431,7 @@
       </c>
       <c r="R658" t="str">
         <f ca="1" t="shared" si="65"/>
-        <v>2024-12-20</v>
+        <v>2025-02-08</v>
       </c>
     </row>
     <row r="659" spans="1:18">
@@ -43486,7 +43486,7 @@
       </c>
       <c r="R659" t="str">
         <f ca="1" t="shared" si="65"/>
-        <v>2025-02-09</v>
+        <v>2025-08-04</v>
       </c>
     </row>
     <row r="660" spans="1:18">
@@ -43540,7 +43540,7 @@
       </c>
       <c r="R660" t="str">
         <f ca="1" t="shared" si="65"/>
-        <v>2025-07-26</v>
+        <v>2025-01-22</v>
       </c>
     </row>
     <row r="661" spans="1:18">
@@ -43594,7 +43594,7 @@
       </c>
       <c r="R661" t="str">
         <f ca="1" t="shared" si="65"/>
-        <v>2024-10-04</v>
+        <v>2025-03-27</v>
       </c>
     </row>
     <row r="662" spans="1:18">
@@ -43652,7 +43652,7 @@
       </c>
       <c r="R662" t="str">
         <f ca="1" t="shared" si="65"/>
-        <v>2024-08-16</v>
+        <v>2024-08-03</v>
       </c>
     </row>
     <row r="663" spans="1:18">
@@ -43710,7 +43710,7 @@
       </c>
       <c r="R663" t="str">
         <f ca="1" t="shared" ref="R663:R672" si="66">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-07-06</v>
+        <v>2024-09-10</v>
       </c>
     </row>
     <row r="664" spans="1:18">
@@ -43764,7 +43764,7 @@
       </c>
       <c r="R664" t="str">
         <f ca="1" t="shared" si="66"/>
-        <v>2025-05-06</v>
+        <v>2025-09-13</v>
       </c>
     </row>
     <row r="665" spans="1:18">
@@ -43822,7 +43822,7 @@
       </c>
       <c r="R665" t="str">
         <f ca="1" t="shared" si="66"/>
-        <v>2024-08-21</v>
+        <v>2025-07-04</v>
       </c>
     </row>
     <row r="666" spans="1:18">
@@ -43876,7 +43876,7 @@
       </c>
       <c r="R666" t="str">
         <f ca="1" t="shared" si="66"/>
-        <v>2025-09-19</v>
+        <v>2024-10-12</v>
       </c>
     </row>
     <row r="667" spans="1:18">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="R667" t="str">
         <f ca="1" t="shared" si="66"/>
-        <v>2025-09-14</v>
+        <v>2025-07-13</v>
       </c>
     </row>
     <row r="668" spans="1:18">
@@ -43988,7 +43988,7 @@
       </c>
       <c r="R668" t="str">
         <f ca="1" t="shared" si="66"/>
-        <v>2025-03-26</v>
+        <v>2024-08-23</v>
       </c>
     </row>
     <row r="669" spans="1:18">
@@ -44042,7 +44042,7 @@
       </c>
       <c r="R669" t="str">
         <f ca="1" t="shared" si="66"/>
-        <v>2025-02-11</v>
+        <v>2024-10-14</v>
       </c>
     </row>
     <row r="670" spans="1:18">
@@ -44096,7 +44096,7 @@
       </c>
       <c r="R670" t="str">
         <f ca="1" t="shared" si="66"/>
-        <v>2025-02-22</v>
+        <v>2025-09-30</v>
       </c>
     </row>
     <row r="671" spans="1:18">
@@ -44154,7 +44154,7 @@
       </c>
       <c r="R671" t="str">
         <f ca="1" t="shared" si="66"/>
-        <v>2025-01-01</v>
+        <v>2024-11-14</v>
       </c>
     </row>
     <row r="672" spans="1:18">
@@ -44212,7 +44212,7 @@
       </c>
       <c r="R672" t="str">
         <f ca="1" t="shared" si="66"/>
-        <v>2024-08-28</v>
+        <v>2025-09-18</v>
       </c>
     </row>
     <row r="673" spans="1:18">
@@ -44270,7 +44270,7 @@
       </c>
       <c r="R673" t="str">
         <f ca="1" t="shared" ref="R673:R682" si="67">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-01-07</v>
+        <v>2025-03-07</v>
       </c>
     </row>
     <row r="674" spans="1:18">
@@ -44328,7 +44328,7 @@
       </c>
       <c r="R674" t="str">
         <f ca="1" t="shared" si="67"/>
-        <v>2025-09-21</v>
+        <v>2025-08-23</v>
       </c>
     </row>
     <row r="675" spans="1:18">
@@ -44386,7 +44386,7 @@
       </c>
       <c r="R675" t="str">
         <f ca="1" t="shared" si="67"/>
-        <v>2024-10-04</v>
+        <v>2025-02-25</v>
       </c>
     </row>
     <row r="676" spans="1:18">
@@ -44444,7 +44444,7 @@
       </c>
       <c r="R676" t="str">
         <f ca="1" t="shared" si="67"/>
-        <v>2025-04-16</v>
+        <v>2025-03-15</v>
       </c>
     </row>
     <row r="677" spans="1:18">
@@ -44498,7 +44498,7 @@
       </c>
       <c r="R677" t="str">
         <f ca="1" t="shared" si="67"/>
-        <v>2024-10-22</v>
+        <v>2025-08-25</v>
       </c>
     </row>
     <row r="678" spans="1:18">
@@ -44556,7 +44556,7 @@
       </c>
       <c r="R678" t="str">
         <f ca="1" t="shared" si="67"/>
-        <v>2025-07-01</v>
+        <v>2024-10-11</v>
       </c>
     </row>
     <row r="679" spans="1:18">
@@ -44614,7 +44614,7 @@
       </c>
       <c r="R679" t="str">
         <f ca="1" t="shared" si="67"/>
-        <v>2025-03-20</v>
+        <v>2024-09-21</v>
       </c>
     </row>
     <row r="680" spans="1:18">
@@ -44668,7 +44668,7 @@
       </c>
       <c r="R680" t="str">
         <f ca="1" t="shared" si="67"/>
-        <v>2025-09-14</v>
+        <v>2024-10-07</v>
       </c>
     </row>
     <row r="681" spans="1:18">
@@ -44726,7 +44726,7 @@
       </c>
       <c r="R681" t="str">
         <f ca="1" t="shared" si="67"/>
-        <v>2025-03-08</v>
+        <v>2024-10-16</v>
       </c>
     </row>
     <row r="682" spans="1:18">
@@ -44783,7 +44783,7 @@
       </c>
       <c r="R682" t="str">
         <f ca="1" t="shared" si="67"/>
-        <v>2024-08-11</v>
+        <v>2025-07-08</v>
       </c>
     </row>
     <row r="683" spans="1:18">
@@ -44837,7 +44837,7 @@
       </c>
       <c r="R683" t="str">
         <f ca="1" t="shared" ref="R683:R692" si="68">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-08-02</v>
+        <v>2024-09-11</v>
       </c>
     </row>
     <row r="684" spans="1:18">
@@ -44895,7 +44895,7 @@
       </c>
       <c r="R684" t="str">
         <f ca="1" t="shared" si="68"/>
-        <v>2024-08-09</v>
+        <v>2024-08-13</v>
       </c>
     </row>
     <row r="685" spans="1:18">
@@ -44952,7 +44952,7 @@
       </c>
       <c r="R685" t="str">
         <f ca="1" t="shared" si="68"/>
-        <v>2024-10-09</v>
+        <v>2025-09-12</v>
       </c>
     </row>
     <row r="686" spans="1:18">
@@ -45010,7 +45010,7 @@
       </c>
       <c r="R686" t="str">
         <f ca="1" t="shared" si="68"/>
-        <v>2024-09-10</v>
+        <v>2024-12-31</v>
       </c>
     </row>
     <row r="687" spans="1:18">
@@ -45068,7 +45068,7 @@
       </c>
       <c r="R687" t="str">
         <f ca="1" t="shared" si="68"/>
-        <v>2025-05-08</v>
+        <v>2025-04-19</v>
       </c>
     </row>
     <row r="688" spans="1:18">
@@ -45122,7 +45122,7 @@
       </c>
       <c r="R688" t="str">
         <f ca="1" t="shared" si="68"/>
-        <v>2024-12-06</v>
+        <v>2025-03-14</v>
       </c>
     </row>
     <row r="689" spans="1:18">
@@ -45176,7 +45176,7 @@
       </c>
       <c r="R689" t="str">
         <f ca="1" t="shared" si="68"/>
-        <v>2024-09-15</v>
+        <v>2024-10-10</v>
       </c>
     </row>
     <row r="690" spans="1:18">
@@ -45230,7 +45230,7 @@
       </c>
       <c r="R690" t="str">
         <f ca="1" t="shared" si="68"/>
-        <v>2024-12-10</v>
+        <v>2025-02-07</v>
       </c>
     </row>
     <row r="691" spans="1:18">
@@ -45284,7 +45284,7 @@
       </c>
       <c r="R691" t="str">
         <f ca="1" t="shared" si="68"/>
-        <v>2024-10-12</v>
+        <v>2025-03-28</v>
       </c>
     </row>
     <row r="692" spans="1:18">
@@ -45342,7 +45342,7 @@
       </c>
       <c r="R692" t="str">
         <f ca="1" t="shared" si="68"/>
-        <v>2024-11-25</v>
+        <v>2025-01-28</v>
       </c>
     </row>
     <row r="693" spans="1:18">
@@ -45400,7 +45400,7 @@
       </c>
       <c r="R693" t="str">
         <f ca="1" t="shared" ref="R693:R702" si="69">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-01-25</v>
+        <v>2024-09-29</v>
       </c>
     </row>
     <row r="694" spans="1:18">
@@ -45458,7 +45458,7 @@
       </c>
       <c r="R694" t="str">
         <f ca="1" t="shared" si="69"/>
-        <v>2025-02-25</v>
+        <v>2025-07-14</v>
       </c>
     </row>
     <row r="695" spans="1:18">
@@ -45516,7 +45516,7 @@
       </c>
       <c r="R695" t="str">
         <f ca="1" t="shared" si="69"/>
-        <v>2024-08-19</v>
+        <v>2024-09-10</v>
       </c>
     </row>
     <row r="696" spans="1:18">
@@ -45570,7 +45570,7 @@
       </c>
       <c r="R696" t="str">
         <f ca="1" t="shared" si="69"/>
-        <v>2025-05-27</v>
+        <v>2025-06-05</v>
       </c>
     </row>
     <row r="697" spans="1:18">
@@ -45627,7 +45627,7 @@
       </c>
       <c r="R697" t="str">
         <f ca="1" t="shared" si="69"/>
-        <v>2024-11-21</v>
+        <v>2024-12-12</v>
       </c>
     </row>
     <row r="698" spans="1:18">
@@ -45685,7 +45685,7 @@
       </c>
       <c r="R698" t="str">
         <f ca="1" t="shared" si="69"/>
-        <v>2025-06-05</v>
+        <v>2025-08-02</v>
       </c>
     </row>
     <row r="699" spans="1:18">
@@ -45743,7 +45743,7 @@
       </c>
       <c r="R699" t="str">
         <f ca="1" t="shared" si="69"/>
-        <v>2024-08-02</v>
+        <v>2025-07-08</v>
       </c>
     </row>
     <row r="700" spans="1:18">
@@ -45801,7 +45801,7 @@
       </c>
       <c r="R700" t="str">
         <f ca="1" t="shared" si="69"/>
-        <v>2024-12-14</v>
+        <v>2025-04-19</v>
       </c>
     </row>
     <row r="701" spans="1:18">
@@ -45859,7 +45859,7 @@
       </c>
       <c r="R701" t="str">
         <f ca="1" t="shared" si="69"/>
-        <v>2024-09-23</v>
+        <v>2025-09-08</v>
       </c>
     </row>
     <row r="702" spans="1:18">
@@ -45917,7 +45917,7 @@
       </c>
       <c r="R702" t="str">
         <f ca="1" t="shared" si="69"/>
-        <v>2024-11-06</v>
+        <v>2025-08-02</v>
       </c>
     </row>
     <row r="703" spans="1:18">
@@ -45975,7 +45975,7 @@
       </c>
       <c r="R703" t="str">
         <f ca="1" t="shared" ref="R703:R710" si="70">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-01-26</v>
+        <v>2025-02-24</v>
       </c>
     </row>
     <row r="704" spans="1:18">
@@ -46033,7 +46033,7 @@
       </c>
       <c r="R704" t="str">
         <f ca="1" t="shared" si="70"/>
-        <v>2024-12-04</v>
+        <v>2025-03-29</v>
       </c>
     </row>
     <row r="705" spans="1:18">
@@ -46091,7 +46091,7 @@
       </c>
       <c r="R705" t="str">
         <f ca="1" t="shared" si="70"/>
-        <v>2025-01-08</v>
+        <v>2024-12-18</v>
       </c>
     </row>
     <row r="706" spans="1:18">
@@ -46149,7 +46149,7 @@
       </c>
       <c r="R706" t="str">
         <f ca="1" t="shared" si="70"/>
-        <v>2025-09-07</v>
+        <v>2025-08-14</v>
       </c>
     </row>
     <row r="707" spans="1:18">
@@ -46207,7 +46207,7 @@
       </c>
       <c r="R707" t="str">
         <f ca="1" t="shared" si="70"/>
-        <v>2025-02-22</v>
+        <v>2025-04-12</v>
       </c>
     </row>
     <row r="708" spans="1:18">
@@ -46265,7 +46265,7 @@
       </c>
       <c r="R708" t="str">
         <f ca="1" t="shared" si="70"/>
-        <v>2024-11-19</v>
+        <v>2025-09-16</v>
       </c>
     </row>
     <row r="709" spans="1:18">
@@ -46319,7 +46319,7 @@
       </c>
       <c r="R709" t="str">
         <f ca="1" t="shared" si="70"/>
-        <v>2025-06-06</v>
+        <v>2024-12-06</v>
       </c>
     </row>
     <row r="710" spans="1:18">
@@ -46377,7 +46377,7 @@
       </c>
       <c r="R710" t="str">
         <f ca="1" t="shared" si="70"/>
-        <v>2025-07-07</v>
+        <v>2025-09-16</v>
       </c>
     </row>
   </sheetData>

--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -6273,8 +6273,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R2" t="str">
-        <f ca="1">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-01-12</v>
+        <f ca="1">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-04-29</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -6327,8 +6327,8 @@
         <v>33</v>
       </c>
       <c r="R3" t="str">
-        <f ca="1" t="shared" ref="R3:R12" si="0">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-08-17</v>
+        <f ca="1" t="shared" ref="R3:R12" si="0">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-05-06</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="R4" t="str">
         <f ca="1" t="shared" si="0"/>
-        <v>2025-04-25</v>
+        <v>2024-10-12</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="R5" t="str">
         <f ca="1" t="shared" si="0"/>
-        <v>2024-10-11</v>
+        <v>2025-10-17</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="R6" t="str">
         <f ca="1" t="shared" si="0"/>
-        <v>2025-05-12</v>
+        <v>2024-08-31</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="R7" t="str">
         <f ca="1" t="shared" si="0"/>
-        <v>2024-11-21</v>
+        <v>2025-10-26</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="R8" t="str">
         <f ca="1" t="shared" si="0"/>
-        <v>2024-10-16</v>
+        <v>2024-08-25</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="R9" t="str">
         <f ca="1" t="shared" si="0"/>
-        <v>2025-05-05</v>
+        <v>2025-11-01</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="R10" t="str">
         <f ca="1" t="shared" si="0"/>
-        <v>2025-07-16</v>
+        <v>2024-11-22</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="R11" t="str">
         <f ca="1" t="shared" si="0"/>
-        <v>2025-06-08</v>
+        <v>2024-11-22</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="R12" t="str">
         <f ca="1" t="shared" si="0"/>
-        <v>2024-08-24</v>
+        <v>2025-08-17</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -6889,8 +6889,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R13" t="str">
-        <f ca="1" t="shared" ref="R13:R22" si="1">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-06-22</v>
+        <f ca="1" t="shared" ref="R13:R22" si="1">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-01-07</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="R14" t="str">
         <f ca="1" t="shared" si="1"/>
-        <v>2025-01-30</v>
+        <v>2025-10-13</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="R15" t="str">
         <f ca="1" t="shared" si="1"/>
-        <v>2024-08-14</v>
+        <v>2024-10-04</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="R16" t="str">
         <f ca="1" t="shared" si="1"/>
-        <v>2024-08-17</v>
+        <v>2025-11-25</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="R17" t="str">
         <f ca="1" t="shared" si="1"/>
-        <v>2024-08-12</v>
+        <v>2025-06-21</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="R18" t="str">
         <f ca="1" t="shared" si="1"/>
-        <v>2024-09-27</v>
+        <v>2025-02-14</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="R19" t="str">
         <f ca="1" t="shared" si="1"/>
-        <v>2025-05-27</v>
+        <v>2025-07-14</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="R20" t="str">
         <f ca="1" t="shared" si="1"/>
-        <v>2025-04-18</v>
+        <v>2024-12-01</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="R21" t="str">
         <f ca="1" t="shared" si="1"/>
-        <v>2024-08-02</v>
+        <v>2025-01-13</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="R22" t="str">
         <f ca="1" t="shared" si="1"/>
-        <v>2025-08-21</v>
+        <v>2025-11-15</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -7461,8 +7461,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R23" t="str">
-        <f ca="1" t="shared" ref="R23:R32" si="2">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-08-28</v>
+        <f ca="1" t="shared" ref="R23:R32" si="2">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-07-30</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="R24" t="str">
         <f ca="1" t="shared" si="2"/>
-        <v>2025-04-29</v>
+        <v>2025-04-01</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="R25" t="str">
         <f ca="1" t="shared" si="2"/>
-        <v>2025-06-11</v>
+        <v>2024-10-24</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="R26" t="str">
         <f ca="1" t="shared" si="2"/>
-        <v>2025-09-16</v>
+        <v>2025-04-13</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="R27" t="str">
         <f ca="1" t="shared" si="2"/>
-        <v>2025-05-27</v>
+        <v>2025-11-01</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="R28" t="str">
         <f ca="1" t="shared" si="2"/>
-        <v>2025-09-14</v>
+        <v>2025-01-17</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="R29" t="str">
         <f ca="1" t="shared" si="2"/>
-        <v>2024-12-22</v>
+        <v>2025-01-10</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="R30" t="str">
         <f ca="1" t="shared" si="2"/>
-        <v>2025-01-17</v>
+        <v>2025-08-13</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="R31" t="str">
         <f ca="1" t="shared" si="2"/>
-        <v>2025-09-18</v>
+        <v>2025-03-11</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="R32" t="str">
         <f ca="1" t="shared" si="2"/>
-        <v>2025-09-08</v>
+        <v>2024-11-08</v>
       </c>
     </row>
     <row r="33" spans="1:18">
@@ -8025,8 +8025,8 @@
         <v>33</v>
       </c>
       <c r="R33" t="str">
-        <f ca="1" t="shared" ref="R33:R42" si="3">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-07-16</v>
+        <f ca="1" t="shared" ref="R33:R42" si="3">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-11-13</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="R34" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>2025-02-22</v>
+        <v>2025-05-26</v>
       </c>
     </row>
     <row r="35" spans="1:18">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="R35" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>2025-03-29</v>
+        <v>2025-05-19</v>
       </c>
     </row>
     <row r="36" spans="1:18">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="R36" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>2025-02-24</v>
+        <v>2025-02-13</v>
       </c>
     </row>
     <row r="37" spans="1:18">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="R37" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>2024-11-22</v>
+        <v>2025-04-17</v>
       </c>
     </row>
     <row r="38" spans="1:18">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="R38" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>2024-09-16</v>
+        <v>2025-02-04</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="R39" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>2025-04-02</v>
+        <v>2025-07-09</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="R40" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>2025-03-08</v>
+        <v>2025-03-03</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="R41" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>2025-05-28</v>
+        <v>2024-10-24</v>
       </c>
     </row>
     <row r="42" spans="1:18">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="R42" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>2025-07-06</v>
+        <v>2025-11-26</v>
       </c>
     </row>
     <row r="43" spans="1:18">
@@ -8593,8 +8593,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R43" t="str">
-        <f ca="1" t="shared" ref="R43:R52" si="4">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-10-22</v>
+        <f ca="1" t="shared" ref="R43:R52" si="4">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-03-21</v>
       </c>
     </row>
     <row r="44" spans="1:18">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="R44" t="str">
         <f ca="1" t="shared" si="4"/>
-        <v>2024-08-28</v>
+        <v>2025-11-03</v>
       </c>
     </row>
     <row r="45" spans="1:18">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="R45" t="str">
         <f ca="1" t="shared" si="4"/>
-        <v>2025-01-08</v>
+        <v>2025-03-23</v>
       </c>
     </row>
     <row r="46" spans="1:18">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="R46" t="str">
         <f ca="1" t="shared" si="4"/>
-        <v>2025-09-05</v>
+        <v>2025-06-25</v>
       </c>
     </row>
     <row r="47" spans="1:18">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="R47" t="str">
         <f ca="1" t="shared" si="4"/>
-        <v>2025-02-21</v>
+        <v>2025-08-29</v>
       </c>
     </row>
     <row r="48" spans="1:18">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="R48" t="str">
         <f ca="1" t="shared" si="4"/>
-        <v>2024-10-08</v>
+        <v>2024-09-15</v>
       </c>
     </row>
     <row r="49" spans="1:18">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="R49" t="str">
         <f ca="1" t="shared" si="4"/>
-        <v>2024-08-01</v>
+        <v>2024-11-15</v>
       </c>
     </row>
     <row r="50" spans="1:18">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="R50" t="str">
         <f ca="1" t="shared" si="4"/>
-        <v>2025-03-04</v>
+        <v>2025-06-06</v>
       </c>
     </row>
     <row r="51" spans="1:18">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="R51" t="str">
         <f ca="1" t="shared" si="4"/>
-        <v>2025-07-05</v>
+        <v>2024-11-08</v>
       </c>
     </row>
     <row r="52" spans="1:18">
@@ -9111,7 +9111,7 @@
       </c>
       <c r="R52" t="str">
         <f ca="1" t="shared" si="4"/>
-        <v>2024-09-02</v>
+        <v>2024-08-26</v>
       </c>
     </row>
     <row r="53" spans="1:18">
@@ -9164,8 +9164,8 @@
         <v>33</v>
       </c>
       <c r="R53" t="str">
-        <f ca="1" t="shared" ref="R53:R62" si="5">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-04-25</v>
+        <f ca="1" t="shared" ref="R53:R62" si="5">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-04-03</v>
       </c>
     </row>
     <row r="54" spans="1:18">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="R54" t="str">
         <f ca="1" t="shared" si="5"/>
-        <v>2025-02-08</v>
+        <v>2025-01-24</v>
       </c>
     </row>
     <row r="55" spans="1:18">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="R55" t="str">
         <f ca="1" t="shared" si="5"/>
-        <v>2025-02-26</v>
+        <v>2025-07-01</v>
       </c>
     </row>
     <row r="56" spans="1:18">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="R56" t="str">
         <f ca="1" t="shared" si="5"/>
-        <v>2024-12-13</v>
+        <v>2025-08-19</v>
       </c>
     </row>
     <row r="57" spans="1:18">
@@ -9390,7 +9390,7 @@
       </c>
       <c r="R57" t="str">
         <f ca="1" t="shared" si="5"/>
-        <v>2025-10-08</v>
+        <v>2025-07-05</v>
       </c>
     </row>
     <row r="58" spans="1:18">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="R58" t="str">
         <f ca="1" t="shared" si="5"/>
-        <v>2025-04-04</v>
+        <v>2025-05-20</v>
       </c>
     </row>
     <row r="59" spans="1:18">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="R59" t="str">
         <f ca="1" t="shared" si="5"/>
-        <v>2025-03-29</v>
+        <v>2025-03-25</v>
       </c>
     </row>
     <row r="60" spans="1:18">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="R60" t="str">
         <f ca="1" t="shared" si="5"/>
-        <v>2024-12-09</v>
+        <v>2025-03-28</v>
       </c>
     </row>
     <row r="61" spans="1:18">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="R61" t="str">
         <f ca="1" t="shared" si="5"/>
-        <v>2024-10-22</v>
+        <v>2025-11-29</v>
       </c>
     </row>
     <row r="62" spans="1:18">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="R62" t="str">
         <f ca="1" t="shared" si="5"/>
-        <v>2025-08-27</v>
+        <v>2025-09-24</v>
       </c>
     </row>
     <row r="63" spans="1:18">
@@ -9735,8 +9735,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R63" t="str">
-        <f ca="1" t="shared" ref="R63:R72" si="6">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-02-13</v>
+        <f ca="1" t="shared" ref="R63:R72" si="6">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-02-23</v>
       </c>
     </row>
     <row r="64" spans="1:18">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="R64" t="str">
         <f ca="1" t="shared" si="6"/>
-        <v>2025-07-22</v>
+        <v>2025-09-08</v>
       </c>
     </row>
     <row r="65" spans="1:18">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="R65" t="str">
         <f ca="1" t="shared" si="6"/>
-        <v>2025-04-07</v>
+        <v>2024-09-14</v>
       </c>
     </row>
     <row r="66" spans="1:18">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="R66" t="str">
         <f ca="1" t="shared" si="6"/>
-        <v>2025-06-07</v>
+        <v>2025-10-26</v>
       </c>
     </row>
     <row r="67" spans="1:18">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="R67" t="str">
         <f ca="1" t="shared" si="6"/>
-        <v>2025-07-11</v>
+        <v>2025-06-25</v>
       </c>
     </row>
     <row r="68" spans="1:18">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="R68" t="str">
         <f ca="1" t="shared" si="6"/>
-        <v>2025-08-15</v>
+        <v>2025-10-18</v>
       </c>
     </row>
     <row r="69" spans="1:18">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="R69" t="str">
         <f ca="1" t="shared" si="6"/>
-        <v>2025-03-19</v>
+        <v>2025-01-25</v>
       </c>
     </row>
     <row r="70" spans="1:18">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="R70" t="str">
         <f ca="1" t="shared" si="6"/>
-        <v>2025-01-29</v>
+        <v>2024-11-21</v>
       </c>
     </row>
     <row r="71" spans="1:18">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="R71" t="str">
         <f ca="1" t="shared" si="6"/>
-        <v>2025-09-22</v>
+        <v>2025-06-30</v>
       </c>
     </row>
     <row r="72" spans="1:18">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="R72" t="str">
         <f ca="1" t="shared" si="6"/>
-        <v>2025-01-30</v>
+        <v>2025-02-21</v>
       </c>
     </row>
     <row r="73" spans="1:18">
@@ -10298,8 +10298,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R73" t="str">
-        <f ca="1" t="shared" ref="R73:R82" si="7">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-03-05</v>
+        <f ca="1" t="shared" ref="R73:R82" si="7">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-07-08</v>
       </c>
     </row>
     <row r="74" spans="1:18">
@@ -10357,7 +10357,7 @@
       </c>
       <c r="R74" t="str">
         <f ca="1" t="shared" si="7"/>
-        <v>2025-06-18</v>
+        <v>2025-05-09</v>
       </c>
     </row>
     <row r="75" spans="1:18">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="R75" t="str">
         <f ca="1" t="shared" si="7"/>
-        <v>2025-07-12</v>
+        <v>2025-07-03</v>
       </c>
     </row>
     <row r="76" spans="1:18">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="R76" t="str">
         <f ca="1" t="shared" si="7"/>
-        <v>2025-01-20</v>
+        <v>2024-11-24</v>
       </c>
     </row>
     <row r="77" spans="1:18">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="R77" t="str">
         <f ca="1" t="shared" si="7"/>
-        <v>2025-07-06</v>
+        <v>2025-03-14</v>
       </c>
     </row>
     <row r="78" spans="1:18">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="R78" t="str">
         <f ca="1" t="shared" si="7"/>
-        <v>2024-08-20</v>
+        <v>2025-05-17</v>
       </c>
     </row>
     <row r="79" spans="1:18">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="R79" t="str">
         <f ca="1" t="shared" si="7"/>
-        <v>2024-12-11</v>
+        <v>2025-11-03</v>
       </c>
     </row>
     <row r="80" spans="1:18">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="R80" t="str">
         <f ca="1" t="shared" si="7"/>
-        <v>2024-12-30</v>
+        <v>2025-09-27</v>
       </c>
     </row>
     <row r="81" spans="1:18">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="R81" t="str">
         <f ca="1" t="shared" si="7"/>
-        <v>2024-09-06</v>
+        <v>2025-09-02</v>
       </c>
     </row>
     <row r="82" spans="1:18">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="R82" t="str">
         <f ca="1" t="shared" si="7"/>
-        <v>2024-10-25</v>
+        <v>2025-07-24</v>
       </c>
     </row>
     <row r="83" spans="1:18">
@@ -10862,8 +10862,8 @@
         <v>33</v>
       </c>
       <c r="R83" t="str">
-        <f ca="1" t="shared" ref="R83:R92" si="8">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-02-24</v>
+        <f ca="1" t="shared" ref="R83:R92" si="8">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-08-11</v>
       </c>
     </row>
     <row r="84" spans="1:18">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="R84" t="str">
         <f ca="1" t="shared" si="8"/>
-        <v>2025-02-15</v>
+        <v>2024-12-27</v>
       </c>
     </row>
     <row r="85" spans="1:18">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="R85" t="str">
         <f ca="1" t="shared" si="8"/>
-        <v>2024-09-25</v>
+        <v>2025-11-20</v>
       </c>
     </row>
     <row r="86" spans="1:18">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="R86" t="str">
         <f ca="1" t="shared" si="8"/>
-        <v>2024-10-03</v>
+        <v>2024-10-04</v>
       </c>
     </row>
     <row r="87" spans="1:18">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="R87" t="str">
         <f ca="1" t="shared" si="8"/>
-        <v>2025-04-13</v>
+        <v>2025-08-04</v>
       </c>
     </row>
     <row r="88" spans="1:18">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="R88" t="str">
         <f ca="1" t="shared" si="8"/>
-        <v>2024-09-10</v>
+        <v>2025-03-11</v>
       </c>
     </row>
     <row r="89" spans="1:18">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="R89" t="str">
         <f ca="1" t="shared" si="8"/>
-        <v>2025-08-07</v>
+        <v>2024-12-10</v>
       </c>
     </row>
     <row r="90" spans="1:18">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="R90" t="str">
         <f ca="1" t="shared" si="8"/>
-        <v>2025-06-27</v>
+        <v>2024-10-06</v>
       </c>
     </row>
     <row r="91" spans="1:18">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="R91" t="str">
         <f ca="1" t="shared" si="8"/>
-        <v>2025-04-15</v>
+        <v>2024-09-29</v>
       </c>
     </row>
     <row r="92" spans="1:18">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="R92" t="str">
         <f ca="1" t="shared" si="8"/>
-        <v>2024-12-09</v>
+        <v>2025-05-09</v>
       </c>
     </row>
     <row r="93" spans="1:18">
@@ -11430,8 +11430,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R93" t="str">
-        <f ca="1" t="shared" ref="R93:R102" si="9">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-08-18</v>
+        <f ca="1" t="shared" ref="R93:R102" si="9">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-12-01</v>
       </c>
     </row>
     <row r="94" spans="1:18">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="R94" t="str">
         <f ca="1" t="shared" si="9"/>
-        <v>2025-01-07</v>
+        <v>2024-08-09</v>
       </c>
     </row>
     <row r="95" spans="1:18">
@@ -11547,7 +11547,7 @@
       </c>
       <c r="R95" t="str">
         <f ca="1" t="shared" si="9"/>
-        <v>2024-12-17</v>
+        <v>2025-08-10</v>
       </c>
     </row>
     <row r="96" spans="1:18">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="R96" t="str">
         <f ca="1" t="shared" si="9"/>
-        <v>2025-09-15</v>
+        <v>2024-11-17</v>
       </c>
     </row>
     <row r="97" spans="1:18">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="R97" t="str">
         <f ca="1" t="shared" si="9"/>
-        <v>2025-10-07</v>
+        <v>2024-11-26</v>
       </c>
     </row>
     <row r="98" spans="1:18">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="R98" t="str">
         <f ca="1" t="shared" si="9"/>
-        <v>2024-12-13</v>
+        <v>2024-12-10</v>
       </c>
     </row>
     <row r="99" spans="1:18">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="R99" t="str">
         <f ca="1" t="shared" si="9"/>
-        <v>2024-11-05</v>
+        <v>2025-09-21</v>
       </c>
     </row>
     <row r="100" spans="1:18">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="R100" t="str">
         <f ca="1" t="shared" si="9"/>
-        <v>2025-09-09</v>
+        <v>2024-10-13</v>
       </c>
     </row>
     <row r="101" spans="1:18">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="R101" t="str">
         <f ca="1" t="shared" si="9"/>
-        <v>2024-09-23</v>
+        <v>2025-01-14</v>
       </c>
     </row>
     <row r="102" spans="1:18">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="R102" t="str">
         <f ca="1" t="shared" si="9"/>
-        <v>2024-09-05</v>
+        <v>2025-06-26</v>
       </c>
     </row>
     <row r="103" spans="1:18">
@@ -11994,8 +11994,8 @@
         <v>33</v>
       </c>
       <c r="R103" t="str">
-        <f ca="1" t="shared" ref="R103:R112" si="10">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-08-02</v>
+        <f ca="1" t="shared" ref="R103:R112" si="10">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-10-02</v>
       </c>
     </row>
     <row r="104" spans="1:18">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="R104" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>2024-10-04</v>
+        <v>2025-05-20</v>
       </c>
     </row>
     <row r="105" spans="1:18">
@@ -12110,7 +12110,7 @@
       </c>
       <c r="R105" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>2025-01-10</v>
+        <v>2024-08-26</v>
       </c>
     </row>
     <row r="106" spans="1:18">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="R106" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>2025-03-10</v>
+        <v>2025-04-14</v>
       </c>
     </row>
     <row r="107" spans="1:18">
@@ -12221,7 +12221,7 @@
       </c>
       <c r="R107" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>2025-08-23</v>
+        <v>2024-10-28</v>
       </c>
     </row>
     <row r="108" spans="1:18">
@@ -12278,7 +12278,7 @@
       </c>
       <c r="R108" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>2025-04-05</v>
+        <v>2024-09-27</v>
       </c>
     </row>
     <row r="109" spans="1:18">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="R109" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>2024-08-13</v>
+        <v>2025-01-30</v>
       </c>
     </row>
     <row r="110" spans="1:18">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="R110" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>2025-08-19</v>
+        <v>2025-07-13</v>
       </c>
     </row>
     <row r="111" spans="1:18">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="R111" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>2024-12-04</v>
+        <v>2025-11-04</v>
       </c>
     </row>
     <row r="112" spans="1:18">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="R112" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>2024-12-06</v>
+        <v>2024-09-06</v>
       </c>
     </row>
     <row r="113" spans="1:18">
@@ -12559,8 +12559,8 @@
         <v>33</v>
       </c>
       <c r="R113" t="str">
-        <f ca="1" t="shared" ref="R113:R122" si="11">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-03-07</v>
+        <f ca="1" t="shared" ref="R113:R122" si="11">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-03-19</v>
       </c>
     </row>
     <row r="114" spans="1:18">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="R114" t="str">
         <f ca="1" t="shared" si="11"/>
-        <v>2024-08-29</v>
+        <v>2025-04-25</v>
       </c>
     </row>
     <row r="115" spans="1:18">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="R115" t="str">
         <f ca="1" t="shared" si="11"/>
-        <v>2025-09-20</v>
+        <v>2025-08-06</v>
       </c>
     </row>
     <row r="116" spans="1:18">
@@ -12722,7 +12722,7 @@
       </c>
       <c r="R116" t="str">
         <f ca="1" t="shared" si="11"/>
-        <v>2025-09-23</v>
+        <v>2025-05-02</v>
       </c>
     </row>
     <row r="117" spans="1:18">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="R117" t="str">
         <f ca="1" t="shared" si="11"/>
-        <v>2024-11-19</v>
+        <v>2025-06-20</v>
       </c>
     </row>
     <row r="118" spans="1:18">
@@ -12838,7 +12838,7 @@
       </c>
       <c r="R118" t="str">
         <f ca="1" t="shared" si="11"/>
-        <v>2024-12-23</v>
+        <v>2025-04-11</v>
       </c>
     </row>
     <row r="119" spans="1:18">
@@ -12896,7 +12896,7 @@
       </c>
       <c r="R119" t="str">
         <f ca="1" t="shared" si="11"/>
-        <v>2025-07-12</v>
+        <v>2025-11-28</v>
       </c>
     </row>
     <row r="120" spans="1:18">
@@ -12950,7 +12950,7 @@
       </c>
       <c r="R120" t="str">
         <f ca="1" t="shared" si="11"/>
-        <v>2025-01-31</v>
+        <v>2025-07-17</v>
       </c>
     </row>
     <row r="121" spans="1:18">
@@ -13004,7 +13004,7 @@
       </c>
       <c r="R121" t="str">
         <f ca="1" t="shared" si="11"/>
-        <v>2025-09-21</v>
+        <v>2024-09-01</v>
       </c>
     </row>
     <row r="122" spans="1:18">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="R122" t="str">
         <f ca="1" t="shared" si="11"/>
-        <v>2025-07-11</v>
+        <v>2025-04-18</v>
       </c>
     </row>
     <row r="123" spans="1:18">
@@ -13115,8 +13115,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R123" t="str">
-        <f ca="1" t="shared" ref="R123:R132" si="12">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-04-24</v>
+        <f ca="1" t="shared" ref="R123:R132" si="12">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2024-08-22</v>
       </c>
     </row>
     <row r="124" spans="1:18">
@@ -13170,7 +13170,7 @@
       </c>
       <c r="R124" t="str">
         <f ca="1" t="shared" si="12"/>
-        <v>2024-09-14</v>
+        <v>2025-04-24</v>
       </c>
     </row>
     <row r="125" spans="1:18">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="R125" t="str">
         <f ca="1" t="shared" si="12"/>
-        <v>2025-04-01</v>
+        <v>2025-06-08</v>
       </c>
     </row>
     <row r="126" spans="1:18">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="R126" t="str">
         <f ca="1" t="shared" si="12"/>
-        <v>2024-10-04</v>
+        <v>2024-10-21</v>
       </c>
     </row>
     <row r="127" spans="1:18">
@@ -13332,7 +13332,7 @@
       </c>
       <c r="R127" t="str">
         <f ca="1" t="shared" si="12"/>
-        <v>2024-10-07</v>
+        <v>2024-11-30</v>
       </c>
     </row>
     <row r="128" spans="1:18">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="R128" t="str">
         <f ca="1" t="shared" si="12"/>
-        <v>2025-07-18</v>
+        <v>2025-09-24</v>
       </c>
     </row>
     <row r="129" spans="1:18">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="R129" t="str">
         <f ca="1" t="shared" si="12"/>
-        <v>2025-02-07</v>
+        <v>2024-12-23</v>
       </c>
     </row>
     <row r="130" spans="1:18">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="R130" t="str">
         <f ca="1" t="shared" si="12"/>
-        <v>2025-02-05</v>
+        <v>2025-01-14</v>
       </c>
     </row>
     <row r="131" spans="1:18">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="R131" t="str">
         <f ca="1" t="shared" si="12"/>
-        <v>2024-10-26</v>
+        <v>2025-01-04</v>
       </c>
     </row>
     <row r="132" spans="1:18">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="R132" t="str">
         <f ca="1" t="shared" si="12"/>
-        <v>2024-11-06</v>
+        <v>2025-09-30</v>
       </c>
     </row>
     <row r="133" spans="1:18">
@@ -13667,8 +13667,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R133" t="str">
-        <f ca="1" t="shared" ref="R133:R142" si="13">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-08-25</v>
+        <f ca="1" t="shared" ref="R133:R142" si="13">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-04-03</v>
       </c>
     </row>
     <row r="134" spans="1:18">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="R134" t="str">
         <f ca="1" t="shared" si="13"/>
-        <v>2025-01-10</v>
+        <v>2025-11-21</v>
       </c>
     </row>
     <row r="135" spans="1:18">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="R135" t="str">
         <f ca="1" t="shared" si="13"/>
-        <v>2025-07-16</v>
+        <v>2024-09-04</v>
       </c>
     </row>
     <row r="136" spans="1:18">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="R136" t="str">
         <f ca="1" t="shared" si="13"/>
-        <v>2025-04-02</v>
+        <v>2025-09-22</v>
       </c>
     </row>
     <row r="137" spans="1:18">
@@ -13895,7 +13895,7 @@
       </c>
       <c r="R137" t="str">
         <f ca="1" t="shared" si="13"/>
-        <v>2025-05-23</v>
+        <v>2024-11-14</v>
       </c>
     </row>
     <row r="138" spans="1:18">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="R138" t="str">
         <f ca="1" t="shared" si="13"/>
-        <v>2025-03-03</v>
+        <v>2024-10-05</v>
       </c>
     </row>
     <row r="139" spans="1:18">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="R139" t="str">
         <f ca="1" t="shared" si="13"/>
-        <v>2025-09-10</v>
+        <v>2025-08-26</v>
       </c>
     </row>
     <row r="140" spans="1:18">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="R140" t="str">
         <f ca="1" t="shared" si="13"/>
-        <v>2024-08-15</v>
+        <v>2025-02-24</v>
       </c>
     </row>
     <row r="141" spans="1:18">
@@ -14123,7 +14123,7 @@
       </c>
       <c r="R141" t="str">
         <f ca="1" t="shared" si="13"/>
-        <v>2025-03-26</v>
+        <v>2024-09-06</v>
       </c>
     </row>
     <row r="142" spans="1:18">
@@ -14181,7 +14181,7 @@
       </c>
       <c r="R142" t="str">
         <f ca="1" t="shared" si="13"/>
-        <v>2025-01-05</v>
+        <v>2025-02-07</v>
       </c>
     </row>
     <row r="143" spans="1:18">
@@ -14238,8 +14238,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R143" t="str">
-        <f ca="1" t="shared" ref="R143:R152" si="14">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-06-03</v>
+        <f ca="1" t="shared" ref="R143:R152" si="14">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-07-24</v>
       </c>
     </row>
     <row r="144" spans="1:18">
@@ -14297,7 +14297,7 @@
       </c>
       <c r="R144" t="str">
         <f ca="1" t="shared" si="14"/>
-        <v>2025-09-13</v>
+        <v>2024-09-27</v>
       </c>
     </row>
     <row r="145" spans="1:18">
@@ -14351,7 +14351,7 @@
       </c>
       <c r="R145" t="str">
         <f ca="1" t="shared" si="14"/>
-        <v>2025-03-20</v>
+        <v>2025-10-13</v>
       </c>
     </row>
     <row r="146" spans="1:18">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="R146" t="str">
         <f ca="1" t="shared" si="14"/>
-        <v>2025-04-18</v>
+        <v>2025-03-10</v>
       </c>
     </row>
     <row r="147" spans="1:18">
@@ -14463,7 +14463,7 @@
       </c>
       <c r="R147" t="str">
         <f ca="1" t="shared" si="14"/>
-        <v>2024-08-10</v>
+        <v>2024-09-01</v>
       </c>
     </row>
     <row r="148" spans="1:18">
@@ -14521,7 +14521,7 @@
       </c>
       <c r="R148" t="str">
         <f ca="1" t="shared" si="14"/>
-        <v>2025-07-18</v>
+        <v>2025-02-20</v>
       </c>
     </row>
     <row r="149" spans="1:18">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="R149" t="str">
         <f ca="1" t="shared" si="14"/>
-        <v>2024-08-30</v>
+        <v>2024-12-31</v>
       </c>
     </row>
     <row r="150" spans="1:18">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="R150" t="str">
         <f ca="1" t="shared" si="14"/>
-        <v>2025-06-16</v>
+        <v>2024-09-18</v>
       </c>
     </row>
     <row r="151" spans="1:18">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="R151" t="str">
         <f ca="1" t="shared" si="14"/>
-        <v>2025-06-27</v>
+        <v>2024-11-29</v>
       </c>
     </row>
     <row r="152" spans="1:18">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="R152" t="str">
         <f ca="1" t="shared" si="14"/>
-        <v>2025-03-25</v>
+        <v>2025-09-24</v>
       </c>
     </row>
     <row r="153" spans="1:18">
@@ -14810,8 +14810,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R153" t="str">
-        <f ca="1" t="shared" ref="R153:R162" si="15">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-08-22</v>
+        <f ca="1" t="shared" ref="R153:R162" si="15">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-11-27</v>
       </c>
     </row>
     <row r="154" spans="1:18">
@@ -14869,7 +14869,7 @@
       </c>
       <c r="R154" t="str">
         <f ca="1" t="shared" si="15"/>
-        <v>2025-06-28</v>
+        <v>2025-10-23</v>
       </c>
     </row>
     <row r="155" spans="1:18">
@@ -14927,7 +14927,7 @@
       </c>
       <c r="R155" t="str">
         <f ca="1" t="shared" si="15"/>
-        <v>2025-10-07</v>
+        <v>2024-12-27</v>
       </c>
     </row>
     <row r="156" spans="1:18">
@@ -14985,7 +14985,7 @@
       </c>
       <c r="R156" t="str">
         <f ca="1" t="shared" si="15"/>
-        <v>2024-11-21</v>
+        <v>2024-11-19</v>
       </c>
     </row>
     <row r="157" spans="1:18">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="R157" t="str">
         <f ca="1" t="shared" si="15"/>
-        <v>2025-05-07</v>
+        <v>2025-04-08</v>
       </c>
     </row>
     <row r="158" spans="1:18">
@@ -15101,7 +15101,7 @@
       </c>
       <c r="R158" t="str">
         <f ca="1" t="shared" si="15"/>
-        <v>2025-08-22</v>
+        <v>2025-10-02</v>
       </c>
     </row>
     <row r="159" spans="1:18">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="R159" t="str">
         <f ca="1" t="shared" si="15"/>
-        <v>2025-07-10</v>
+        <v>2025-10-25</v>
       </c>
     </row>
     <row r="160" spans="1:18">
@@ -15217,7 +15217,7 @@
       </c>
       <c r="R160" t="str">
         <f ca="1" t="shared" si="15"/>
-        <v>2024-12-13</v>
+        <v>2025-09-14</v>
       </c>
     </row>
     <row r="161" spans="1:18">
@@ -15275,7 +15275,7 @@
       </c>
       <c r="R161" t="str">
         <f ca="1" t="shared" si="15"/>
-        <v>2024-09-08</v>
+        <v>2025-05-09</v>
       </c>
     </row>
     <row r="162" spans="1:18">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="R162" t="str">
         <f ca="1" t="shared" si="15"/>
-        <v>2025-01-06</v>
+        <v>2024-12-30</v>
       </c>
     </row>
     <row r="163" spans="1:18">
@@ -15390,8 +15390,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R163" t="str">
-        <f ca="1" t="shared" ref="R163:R172" si="16">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-04-09</v>
+        <f ca="1" t="shared" ref="R163:R172" si="16">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-08-17</v>
       </c>
     </row>
     <row r="164" spans="1:18">
@@ -15445,7 +15445,7 @@
       </c>
       <c r="R164" t="str">
         <f ca="1" t="shared" si="16"/>
-        <v>2024-12-26</v>
+        <v>2024-10-01</v>
       </c>
     </row>
     <row r="165" spans="1:18">
@@ -15503,7 +15503,7 @@
       </c>
       <c r="R165" t="str">
         <f ca="1" t="shared" si="16"/>
-        <v>2025-02-28</v>
+        <v>2024-09-03</v>
       </c>
     </row>
     <row r="166" spans="1:18">
@@ -15557,7 +15557,7 @@
       </c>
       <c r="R166" t="str">
         <f ca="1" t="shared" si="16"/>
-        <v>2025-04-27</v>
+        <v>2025-04-02</v>
       </c>
     </row>
     <row r="167" spans="1:18">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="R167" t="str">
         <f ca="1" t="shared" si="16"/>
-        <v>2024-08-17</v>
+        <v>2025-04-19</v>
       </c>
     </row>
     <row r="168" spans="1:18">
@@ -15673,7 +15673,7 @@
       </c>
       <c r="R168" t="str">
         <f ca="1" t="shared" si="16"/>
-        <v>2025-05-04</v>
+        <v>2025-10-21</v>
       </c>
     </row>
     <row r="169" spans="1:18">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="R169" t="str">
         <f ca="1" t="shared" si="16"/>
-        <v>2024-08-27</v>
+        <v>2025-10-22</v>
       </c>
     </row>
     <row r="170" spans="1:18">
@@ -15785,7 +15785,7 @@
       </c>
       <c r="R170" t="str">
         <f ca="1" t="shared" si="16"/>
-        <v>2024-11-01</v>
+        <v>2024-11-14</v>
       </c>
     </row>
     <row r="171" spans="1:18">
@@ -15839,7 +15839,7 @@
       </c>
       <c r="R171" t="str">
         <f ca="1" t="shared" si="16"/>
-        <v>2025-05-10</v>
+        <v>2025-10-31</v>
       </c>
     </row>
     <row r="172" spans="1:18">
@@ -15896,7 +15896,7 @@
       </c>
       <c r="R172" t="str">
         <f ca="1" t="shared" si="16"/>
-        <v>2025-01-11</v>
+        <v>2024-12-15</v>
       </c>
     </row>
     <row r="173" spans="1:18">
@@ -15952,8 +15952,8 @@
         <v>138</v>
       </c>
       <c r="R173" t="str">
-        <f ca="1" t="shared" ref="R173:R182" si="17">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-07-14</v>
+        <f ca="1" t="shared" ref="R173:R182" si="17">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-10-12</v>
       </c>
     </row>
     <row r="174" spans="1:18">
@@ -16010,7 +16010,7 @@
       </c>
       <c r="R174" t="str">
         <f ca="1" t="shared" si="17"/>
-        <v>2025-09-25</v>
+        <v>2025-05-23</v>
       </c>
     </row>
     <row r="175" spans="1:18">
@@ -16067,7 +16067,7 @@
       </c>
       <c r="R175" t="str">
         <f ca="1" t="shared" si="17"/>
-        <v>2024-12-26</v>
+        <v>2025-10-29</v>
       </c>
     </row>
     <row r="176" spans="1:18">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="R176" t="str">
         <f ca="1" t="shared" si="17"/>
-        <v>2024-11-10</v>
+        <v>2025-09-10</v>
       </c>
     </row>
     <row r="177" spans="1:18">
@@ -16183,7 +16183,7 @@
       </c>
       <c r="R177" t="str">
         <f ca="1" t="shared" si="17"/>
-        <v>2024-12-27</v>
+        <v>2025-02-22</v>
       </c>
     </row>
     <row r="178" spans="1:18">
@@ -16237,7 +16237,7 @@
       </c>
       <c r="R178" t="str">
         <f ca="1" t="shared" si="17"/>
-        <v>2025-01-15</v>
+        <v>2025-04-10</v>
       </c>
     </row>
     <row r="179" spans="1:18">
@@ -16295,7 +16295,7 @@
       </c>
       <c r="R179" t="str">
         <f ca="1" t="shared" si="17"/>
-        <v>2024-09-03</v>
+        <v>2025-04-30</v>
       </c>
     </row>
     <row r="180" spans="1:18">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="R180" t="str">
         <f ca="1" t="shared" si="17"/>
-        <v>2025-05-10</v>
+        <v>2025-06-15</v>
       </c>
     </row>
     <row r="181" spans="1:18">
@@ -16403,7 +16403,7 @@
       </c>
       <c r="R181" t="str">
         <f ca="1" t="shared" si="17"/>
-        <v>2025-01-22</v>
+        <v>2025-10-12</v>
       </c>
     </row>
     <row r="182" spans="1:18">
@@ -16461,7 +16461,7 @@
       </c>
       <c r="R182" t="str">
         <f ca="1" t="shared" si="17"/>
-        <v>2024-12-05</v>
+        <v>2025-09-08</v>
       </c>
     </row>
     <row r="183" spans="1:18">
@@ -16518,8 +16518,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R183" t="str">
-        <f ca="1" t="shared" ref="R183:R192" si="18">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-09-23</v>
+        <f ca="1" t="shared" ref="R183:R192" si="18">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-02-28</v>
       </c>
     </row>
     <row r="184" spans="1:18">
@@ -16573,7 +16573,7 @@
       </c>
       <c r="R184" t="str">
         <f ca="1" t="shared" si="18"/>
-        <v>2025-02-08</v>
+        <v>2024-09-19</v>
       </c>
     </row>
     <row r="185" spans="1:18">
@@ -16631,7 +16631,7 @@
       </c>
       <c r="R185" t="str">
         <f ca="1" t="shared" si="18"/>
-        <v>2024-12-09</v>
+        <v>2025-08-16</v>
       </c>
     </row>
     <row r="186" spans="1:18">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="R186" t="str">
         <f ca="1" t="shared" si="18"/>
-        <v>2025-03-06</v>
+        <v>2025-09-22</v>
       </c>
     </row>
     <row r="187" spans="1:18">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="R187" t="str">
         <f ca="1" t="shared" si="18"/>
-        <v>2025-07-12</v>
+        <v>2024-09-12</v>
       </c>
     </row>
     <row r="188" spans="1:18">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="R188" t="str">
         <f ca="1" t="shared" si="18"/>
-        <v>2025-09-16</v>
+        <v>2025-10-02</v>
       </c>
     </row>
     <row r="189" spans="1:18">
@@ -16857,7 +16857,7 @@
       </c>
       <c r="R189" t="str">
         <f ca="1" t="shared" si="18"/>
-        <v>2025-01-13</v>
+        <v>2025-04-21</v>
       </c>
     </row>
     <row r="190" spans="1:18">
@@ -16915,7 +16915,7 @@
       </c>
       <c r="R190" t="str">
         <f ca="1" t="shared" si="18"/>
-        <v>2025-01-31</v>
+        <v>2025-02-27</v>
       </c>
     </row>
     <row r="191" spans="1:18">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="R191" t="str">
         <f ca="1" t="shared" si="18"/>
-        <v>2025-03-26</v>
+        <v>2025-02-01</v>
       </c>
     </row>
     <row r="192" spans="1:18">
@@ -17031,7 +17031,7 @@
       </c>
       <c r="R192" t="str">
         <f ca="1" t="shared" si="18"/>
-        <v>2025-05-30</v>
+        <v>2025-09-13</v>
       </c>
     </row>
     <row r="193" spans="1:18">
@@ -17088,8 +17088,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R193" t="str">
-        <f ca="1" t="shared" ref="R193:R202" si="19">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-06-03</v>
+        <f ca="1" t="shared" ref="R193:R202" si="19">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-04-17</v>
       </c>
     </row>
     <row r="194" spans="1:18">
@@ -17147,7 +17147,7 @@
       </c>
       <c r="R194" t="str">
         <f ca="1" t="shared" si="19"/>
-        <v>2025-02-21</v>
+        <v>2024-08-26</v>
       </c>
     </row>
     <row r="195" spans="1:18">
@@ -17205,7 +17205,7 @@
       </c>
       <c r="R195" t="str">
         <f ca="1" t="shared" si="19"/>
-        <v>2025-10-07</v>
+        <v>2025-10-01</v>
       </c>
     </row>
     <row r="196" spans="1:18">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="R196" t="str">
         <f ca="1" t="shared" si="19"/>
-        <v>2025-08-27</v>
+        <v>2025-05-21</v>
       </c>
     </row>
     <row r="197" spans="1:18">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="R197" t="str">
         <f ca="1" t="shared" si="19"/>
-        <v>2025-02-15</v>
+        <v>2024-10-02</v>
       </c>
     </row>
     <row r="198" spans="1:18">
@@ -17375,7 +17375,7 @@
       </c>
       <c r="R198" t="str">
         <f ca="1" t="shared" si="19"/>
-        <v>2025-07-27</v>
+        <v>2025-09-28</v>
       </c>
     </row>
     <row r="199" spans="1:18">
@@ -17433,7 +17433,7 @@
       </c>
       <c r="R199" t="str">
         <f ca="1" t="shared" si="19"/>
-        <v>2024-11-15</v>
+        <v>2024-12-18</v>
       </c>
     </row>
     <row r="200" spans="1:18">
@@ -17487,7 +17487,7 @@
       </c>
       <c r="R200" t="str">
         <f ca="1" t="shared" si="19"/>
-        <v>2025-03-18</v>
+        <v>2025-01-08</v>
       </c>
     </row>
     <row r="201" spans="1:18">
@@ -17541,7 +17541,7 @@
       </c>
       <c r="R201" t="str">
         <f ca="1" t="shared" si="19"/>
-        <v>2024-10-21</v>
+        <v>2024-10-05</v>
       </c>
     </row>
     <row r="202" spans="1:18">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="R202" t="str">
         <f ca="1" t="shared" si="19"/>
-        <v>2024-11-24</v>
+        <v>2025-06-20</v>
       </c>
     </row>
     <row r="203" spans="1:18">
@@ -17656,8 +17656,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R203" t="str">
-        <f ca="1" t="shared" ref="R203:R212" si="20">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-09-27</v>
+        <f ca="1" t="shared" ref="R203:R212" si="20">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2024-11-11</v>
       </c>
     </row>
     <row r="204" spans="1:18">
@@ -17711,7 +17711,7 @@
       </c>
       <c r="R204" t="str">
         <f ca="1" t="shared" si="20"/>
-        <v>2024-08-12</v>
+        <v>2025-06-07</v>
       </c>
     </row>
     <row r="205" spans="1:18">
@@ -17769,7 +17769,7 @@
       </c>
       <c r="R205" t="str">
         <f ca="1" t="shared" si="20"/>
-        <v>2025-09-25</v>
+        <v>2025-08-21</v>
       </c>
     </row>
     <row r="206" spans="1:18">
@@ -17823,7 +17823,7 @@
       </c>
       <c r="R206" t="str">
         <f ca="1" t="shared" si="20"/>
-        <v>2024-10-17</v>
+        <v>2025-01-14</v>
       </c>
     </row>
     <row r="207" spans="1:18">
@@ -17881,7 +17881,7 @@
       </c>
       <c r="R207" t="str">
         <f ca="1" t="shared" si="20"/>
-        <v>2025-06-08</v>
+        <v>2025-09-11</v>
       </c>
     </row>
     <row r="208" spans="1:18">
@@ -17939,7 +17939,7 @@
       </c>
       <c r="R208" t="str">
         <f ca="1" t="shared" si="20"/>
-        <v>2025-01-04</v>
+        <v>2024-10-11</v>
       </c>
     </row>
     <row r="209" spans="1:18">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="R209" t="str">
         <f ca="1" t="shared" si="20"/>
-        <v>2024-11-02</v>
+        <v>2025-06-20</v>
       </c>
     </row>
     <row r="210" spans="1:18">
@@ -18055,7 +18055,7 @@
       </c>
       <c r="R210" t="str">
         <f ca="1" t="shared" si="20"/>
-        <v>2024-08-18</v>
+        <v>2024-09-13</v>
       </c>
     </row>
     <row r="211" spans="1:18">
@@ -18109,7 +18109,7 @@
       </c>
       <c r="R211" t="str">
         <f ca="1" t="shared" si="20"/>
-        <v>2024-12-03</v>
+        <v>2025-03-29</v>
       </c>
     </row>
     <row r="212" spans="1:18">
@@ -18167,7 +18167,7 @@
       </c>
       <c r="R212" t="str">
         <f ca="1" t="shared" si="20"/>
-        <v>2025-01-27</v>
+        <v>2025-08-30</v>
       </c>
     </row>
     <row r="213" spans="1:18">
@@ -18224,8 +18224,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R213" t="str">
-        <f ca="1" t="shared" ref="R213:R222" si="21">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-03-13</v>
+        <f ca="1" t="shared" ref="R213:R222" si="21">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2024-11-29</v>
       </c>
     </row>
     <row r="214" spans="1:18">
@@ -18283,7 +18283,7 @@
       </c>
       <c r="R214" t="str">
         <f ca="1" t="shared" si="21"/>
-        <v>2025-04-25</v>
+        <v>2025-04-12</v>
       </c>
     </row>
     <row r="215" spans="1:18">
@@ -18337,7 +18337,7 @@
       </c>
       <c r="R215" t="str">
         <f ca="1" t="shared" si="21"/>
-        <v>2025-07-05</v>
+        <v>2024-08-27</v>
       </c>
     </row>
     <row r="216" spans="1:18">
@@ -18395,7 +18395,7 @@
       </c>
       <c r="R216" t="str">
         <f ca="1" t="shared" si="21"/>
-        <v>2025-09-28</v>
+        <v>2024-10-28</v>
       </c>
     </row>
     <row r="217" spans="1:18">
@@ -18453,7 +18453,7 @@
       </c>
       <c r="R217" t="str">
         <f ca="1" t="shared" si="21"/>
-        <v>2024-11-06</v>
+        <v>2024-11-22</v>
       </c>
     </row>
     <row r="218" spans="1:18">
@@ -18511,7 +18511,7 @@
       </c>
       <c r="R218" t="str">
         <f ca="1" t="shared" si="21"/>
-        <v>2024-09-07</v>
+        <v>2025-07-23</v>
       </c>
     </row>
     <row r="219" spans="1:18">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="R219" t="str">
         <f ca="1" t="shared" si="21"/>
-        <v>2025-08-22</v>
+        <v>2025-08-25</v>
       </c>
     </row>
     <row r="220" spans="1:18">
@@ -18620,7 +18620,7 @@
       </c>
       <c r="R220" t="str">
         <f ca="1" t="shared" si="21"/>
-        <v>2025-08-05</v>
+        <v>2025-07-05</v>
       </c>
     </row>
     <row r="221" spans="1:18">
@@ -18678,7 +18678,7 @@
       </c>
       <c r="R221" t="str">
         <f ca="1" t="shared" si="21"/>
-        <v>2024-09-21</v>
+        <v>2025-11-12</v>
       </c>
     </row>
     <row r="222" spans="1:18">
@@ -18733,7 +18733,7 @@
       </c>
       <c r="R222" t="str">
         <f ca="1" t="shared" si="21"/>
-        <v>2025-07-20</v>
+        <v>2025-02-11</v>
       </c>
     </row>
     <row r="223" spans="1:18">
@@ -18790,8 +18790,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R223" t="str">
-        <f ca="1" t="shared" ref="R223:R232" si="22">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-04-13</v>
+        <f ca="1" t="shared" ref="R223:R232" si="22">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-06-09</v>
       </c>
     </row>
     <row r="224" spans="1:18">
@@ -18848,7 +18848,7 @@
       </c>
       <c r="R224" t="str">
         <f ca="1" t="shared" si="22"/>
-        <v>2025-07-28</v>
+        <v>2024-12-22</v>
       </c>
     </row>
     <row r="225" spans="1:18">
@@ -18960,7 +18960,7 @@
       </c>
       <c r="R226" t="str">
         <f ca="1" t="shared" si="22"/>
-        <v>2024-09-11</v>
+        <v>2025-09-06</v>
       </c>
     </row>
     <row r="227" spans="1:18">
@@ -19018,7 +19018,7 @@
       </c>
       <c r="R227" t="str">
         <f ca="1" t="shared" si="22"/>
-        <v>2025-08-09</v>
+        <v>2024-12-06</v>
       </c>
     </row>
     <row r="228" spans="1:18">
@@ -19073,7 +19073,7 @@
       </c>
       <c r="R228" t="str">
         <f ca="1" t="shared" si="22"/>
-        <v>2025-03-06</v>
+        <v>2025-05-25</v>
       </c>
     </row>
     <row r="229" spans="1:18">
@@ -19131,7 +19131,7 @@
       </c>
       <c r="R229" t="str">
         <f ca="1" t="shared" si="22"/>
-        <v>2024-11-30</v>
+        <v>2024-10-04</v>
       </c>
     </row>
     <row r="230" spans="1:18">
@@ -19185,7 +19185,7 @@
       </c>
       <c r="R230" t="str">
         <f ca="1" t="shared" si="22"/>
-        <v>2025-01-03</v>
+        <v>2025-08-13</v>
       </c>
     </row>
     <row r="231" spans="1:18">
@@ -19239,7 +19239,7 @@
       </c>
       <c r="R231" t="str">
         <f ca="1" t="shared" si="22"/>
-        <v>2024-12-17</v>
+        <v>2025-05-19</v>
       </c>
     </row>
     <row r="232" spans="1:18">
@@ -19296,7 +19296,7 @@
       </c>
       <c r="R232" t="str">
         <f ca="1" t="shared" si="22"/>
-        <v>2025-04-27</v>
+        <v>2024-12-13</v>
       </c>
     </row>
     <row r="233" spans="1:18">
@@ -19353,8 +19353,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R233" t="str">
-        <f ca="1" t="shared" ref="R233:R242" si="23">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-08-08</v>
+        <f ca="1" t="shared" ref="R233:R242" si="23">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-07-15</v>
       </c>
     </row>
     <row r="234" spans="1:18">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="R234" t="str">
         <f ca="1" t="shared" si="23"/>
-        <v>2025-02-13</v>
+        <v>2025-08-09</v>
       </c>
     </row>
     <row r="235" spans="1:18">
@@ -19462,7 +19462,7 @@
       </c>
       <c r="R235" t="str">
         <f ca="1" t="shared" si="23"/>
-        <v>2025-04-23</v>
+        <v>2025-08-29</v>
       </c>
     </row>
     <row r="236" spans="1:18">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="R236" t="str">
         <f ca="1" t="shared" si="23"/>
-        <v>2024-09-07</v>
+        <v>2025-11-09</v>
       </c>
     </row>
     <row r="237" spans="1:18">
@@ -19575,7 +19575,7 @@
       </c>
       <c r="R237" t="str">
         <f ca="1" t="shared" si="23"/>
-        <v>2025-03-20</v>
+        <v>2025-12-01</v>
       </c>
     </row>
     <row r="238" spans="1:18">
@@ -19633,7 +19633,7 @@
       </c>
       <c r="R238" t="str">
         <f ca="1" t="shared" si="23"/>
-        <v>2025-03-03</v>
+        <v>2024-08-13</v>
       </c>
     </row>
     <row r="239" spans="1:18">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="R239" t="str">
         <f ca="1" t="shared" si="23"/>
-        <v>2025-03-26</v>
+        <v>2025-04-02</v>
       </c>
     </row>
     <row r="240" spans="1:18">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="R240" t="str">
         <f ca="1" t="shared" si="23"/>
-        <v>2024-11-30</v>
+        <v>2025-07-26</v>
       </c>
     </row>
     <row r="241" spans="1:18">
@@ -19807,7 +19807,7 @@
       </c>
       <c r="R241" t="str">
         <f ca="1" t="shared" si="23"/>
-        <v>2024-09-11</v>
+        <v>2025-03-24</v>
       </c>
     </row>
     <row r="242" spans="1:18">
@@ -19861,7 +19861,7 @@
       </c>
       <c r="R242" t="str">
         <f ca="1" t="shared" si="23"/>
-        <v>2025-05-10</v>
+        <v>2025-10-10</v>
       </c>
     </row>
     <row r="243" spans="1:18">
@@ -19918,8 +19918,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R243" t="str">
-        <f ca="1" t="shared" ref="R243:R252" si="24">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-03-15</v>
+        <f ca="1" t="shared" ref="R243:R252" si="24">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-02-24</v>
       </c>
     </row>
     <row r="244" spans="1:18">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="R244" t="str">
         <f ca="1" t="shared" si="24"/>
-        <v>2024-08-24</v>
+        <v>2025-10-05</v>
       </c>
     </row>
     <row r="245" spans="1:18">
@@ -20027,7 +20027,7 @@
       </c>
       <c r="R245" t="str">
         <f ca="1" t="shared" si="24"/>
-        <v>2025-04-30</v>
+        <v>2025-10-25</v>
       </c>
     </row>
     <row r="246" spans="1:18">
@@ -20081,7 +20081,7 @@
       </c>
       <c r="R246" t="str">
         <f ca="1" t="shared" si="24"/>
-        <v>2024-12-12</v>
+        <v>2025-08-22</v>
       </c>
     </row>
     <row r="247" spans="1:18">
@@ -20138,7 +20138,7 @@
       </c>
       <c r="R247" t="str">
         <f ca="1" t="shared" si="24"/>
-        <v>2024-08-25</v>
+        <v>2025-03-24</v>
       </c>
     </row>
     <row r="248" spans="1:18">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="R248" t="str">
         <f ca="1" t="shared" si="24"/>
-        <v>2025-06-03</v>
+        <v>2024-09-03</v>
       </c>
     </row>
     <row r="249" spans="1:18">
@@ -20250,7 +20250,7 @@
       </c>
       <c r="R249" t="str">
         <f ca="1" t="shared" si="24"/>
-        <v>2025-10-04</v>
+        <v>2024-08-27</v>
       </c>
     </row>
     <row r="250" spans="1:18">
@@ -20308,7 +20308,7 @@
       </c>
       <c r="R250" t="str">
         <f ca="1" t="shared" si="24"/>
-        <v>2024-09-03</v>
+        <v>2024-09-08</v>
       </c>
     </row>
     <row r="251" spans="1:18">
@@ -20366,7 +20366,7 @@
       </c>
       <c r="R251" t="str">
         <f ca="1" t="shared" si="24"/>
-        <v>2024-08-23</v>
+        <v>2025-08-15</v>
       </c>
     </row>
     <row r="252" spans="1:18">
@@ -20424,7 +20424,7 @@
       </c>
       <c r="R252" t="str">
         <f ca="1" t="shared" si="24"/>
-        <v>2024-08-27</v>
+        <v>2024-08-04</v>
       </c>
     </row>
     <row r="253" spans="1:18">
@@ -20481,8 +20481,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R253" t="str">
-        <f ca="1" t="shared" ref="R253:R262" si="25">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-09-20</v>
+        <f ca="1" t="shared" ref="R253:R262" si="25">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-08-06</v>
       </c>
     </row>
     <row r="254" spans="1:18">
@@ -20540,7 +20540,7 @@
       </c>
       <c r="R254" t="str">
         <f ca="1" t="shared" si="25"/>
-        <v>2025-09-21</v>
+        <v>2025-08-05</v>
       </c>
     </row>
     <row r="255" spans="1:18">
@@ -20598,7 +20598,7 @@
       </c>
       <c r="R255" t="str">
         <f ca="1" t="shared" si="25"/>
-        <v>2025-08-01</v>
+        <v>2025-01-28</v>
       </c>
     </row>
     <row r="256" spans="1:18">
@@ -20656,7 +20656,7 @@
       </c>
       <c r="R256" t="str">
         <f ca="1" t="shared" si="25"/>
-        <v>2025-01-04</v>
+        <v>2025-02-19</v>
       </c>
     </row>
     <row r="257" spans="1:18">
@@ -20711,7 +20711,7 @@
       </c>
       <c r="R257" t="str">
         <f ca="1" t="shared" si="25"/>
-        <v>2025-09-19</v>
+        <v>2025-11-05</v>
       </c>
     </row>
     <row r="258" spans="1:18">
@@ -20769,7 +20769,7 @@
       </c>
       <c r="R258" t="str">
         <f ca="1" t="shared" si="25"/>
-        <v>2024-10-24</v>
+        <v>2024-08-11</v>
       </c>
     </row>
     <row r="259" spans="1:18">
@@ -20824,7 +20824,7 @@
       </c>
       <c r="R259" t="str">
         <f ca="1" t="shared" si="25"/>
-        <v>2025-02-17</v>
+        <v>2024-09-08</v>
       </c>
     </row>
     <row r="260" spans="1:18">
@@ -20882,7 +20882,7 @@
       </c>
       <c r="R260" t="str">
         <f ca="1" t="shared" si="25"/>
-        <v>2025-06-12</v>
+        <v>2025-03-01</v>
       </c>
     </row>
     <row r="261" spans="1:18">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="R261" t="str">
         <f ca="1" t="shared" si="25"/>
-        <v>2025-06-07</v>
+        <v>2024-10-03</v>
       </c>
     </row>
     <row r="262" spans="1:18">
@@ -20997,7 +20997,7 @@
       </c>
       <c r="R262" t="str">
         <f ca="1" t="shared" si="25"/>
-        <v>2025-04-22</v>
+        <v>2025-11-06</v>
       </c>
     </row>
     <row r="263" spans="1:18">
@@ -21054,8 +21054,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R263" t="str">
-        <f ca="1" t="shared" ref="R263:R272" si="26">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-09-05</v>
+        <f ca="1" t="shared" ref="R263:R272" si="26">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2024-10-23</v>
       </c>
     </row>
     <row r="264" spans="1:18">
@@ -21113,7 +21113,7 @@
       </c>
       <c r="R264" t="str">
         <f ca="1" t="shared" si="26"/>
-        <v>2025-08-15</v>
+        <v>2024-11-05</v>
       </c>
     </row>
     <row r="265" spans="1:18">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="R265" t="str">
         <f ca="1" t="shared" si="26"/>
-        <v>2025-04-01</v>
+        <v>2025-09-09</v>
       </c>
     </row>
     <row r="266" spans="1:18">
@@ -21226,7 +21226,7 @@
       </c>
       <c r="R266" t="str">
         <f ca="1" t="shared" si="26"/>
-        <v>2025-05-26</v>
+        <v>2025-10-01</v>
       </c>
     </row>
     <row r="267" spans="1:18">
@@ -21283,7 +21283,7 @@
       </c>
       <c r="R267" t="str">
         <f ca="1" t="shared" si="26"/>
-        <v>2025-10-06</v>
+        <v>2025-10-29</v>
       </c>
     </row>
     <row r="268" spans="1:18">
@@ -21340,7 +21340,7 @@
       </c>
       <c r="R268" t="str">
         <f ca="1" t="shared" si="26"/>
-        <v>2025-07-23</v>
+        <v>2025-01-08</v>
       </c>
     </row>
     <row r="269" spans="1:18">
@@ -21398,7 +21398,7 @@
       </c>
       <c r="R269" t="str">
         <f ca="1" t="shared" si="26"/>
-        <v>2025-04-19</v>
+        <v>2024-09-27</v>
       </c>
     </row>
     <row r="270" spans="1:18">
@@ -21452,7 +21452,7 @@
       </c>
       <c r="R270" t="str">
         <f ca="1" t="shared" si="26"/>
-        <v>2024-12-31</v>
+        <v>2025-10-16</v>
       </c>
     </row>
     <row r="271" spans="1:18">
@@ -21510,7 +21510,7 @@
       </c>
       <c r="R271" t="str">
         <f ca="1" t="shared" si="26"/>
-        <v>2024-11-17</v>
+        <v>2024-09-20</v>
       </c>
     </row>
     <row r="272" spans="1:18">
@@ -21568,7 +21568,7 @@
       </c>
       <c r="R272" t="str">
         <f ca="1" t="shared" si="26"/>
-        <v>2025-09-29</v>
+        <v>2024-10-04</v>
       </c>
     </row>
     <row r="273" spans="1:18">
@@ -21625,8 +21625,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R273" t="str">
-        <f ca="1" t="shared" ref="R273:R282" si="27">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-01-05</v>
+        <f ca="1" t="shared" ref="R273:R282" si="27">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2024-08-27</v>
       </c>
     </row>
     <row r="274" spans="1:18">
@@ -21680,7 +21680,7 @@
       </c>
       <c r="R274" t="str">
         <f ca="1" t="shared" si="27"/>
-        <v>2025-05-14</v>
+        <v>2025-06-10</v>
       </c>
     </row>
     <row r="275" spans="1:18">
@@ -21734,7 +21734,7 @@
       </c>
       <c r="R275" t="str">
         <f ca="1" t="shared" si="27"/>
-        <v>2025-01-08</v>
+        <v>2025-08-05</v>
       </c>
     </row>
     <row r="276" spans="1:18">
@@ -21788,7 +21788,7 @@
       </c>
       <c r="R276" t="str">
         <f ca="1" t="shared" si="27"/>
-        <v>2025-02-23</v>
+        <v>2025-05-18</v>
       </c>
     </row>
     <row r="277" spans="1:18">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="R277" t="str">
         <f ca="1" t="shared" si="27"/>
-        <v>2025-06-09</v>
+        <v>2025-01-19</v>
       </c>
     </row>
     <row r="278" spans="1:18">
@@ -21900,7 +21900,7 @@
       </c>
       <c r="R278" t="str">
         <f ca="1" t="shared" si="27"/>
-        <v>2025-08-25</v>
+        <v>2025-03-07</v>
       </c>
     </row>
     <row r="279" spans="1:18">
@@ -21958,7 +21958,7 @@
       </c>
       <c r="R279" t="str">
         <f ca="1" t="shared" si="27"/>
-        <v>2025-05-06</v>
+        <v>2025-11-13</v>
       </c>
     </row>
     <row r="280" spans="1:18">
@@ -22016,7 +22016,7 @@
       </c>
       <c r="R280" t="str">
         <f ca="1" t="shared" si="27"/>
-        <v>2025-02-28</v>
+        <v>2024-10-23</v>
       </c>
     </row>
     <row r="281" spans="1:18">
@@ -22074,7 +22074,7 @@
       </c>
       <c r="R281" t="str">
         <f ca="1" t="shared" si="27"/>
-        <v>2025-06-24</v>
+        <v>2025-02-07</v>
       </c>
     </row>
     <row r="282" spans="1:18">
@@ -22132,7 +22132,7 @@
       </c>
       <c r="R282" t="str">
         <f ca="1" t="shared" si="27"/>
-        <v>2025-08-31</v>
+        <v>2025-07-18</v>
       </c>
     </row>
     <row r="283" spans="1:18">
@@ -22185,8 +22185,8 @@
         <v>33</v>
       </c>
       <c r="R283" t="str">
-        <f ca="1" t="shared" ref="R283:R292" si="28">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-03-21</v>
+        <f ca="1" t="shared" ref="R283:R292" si="28">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-11-25</v>
       </c>
     </row>
     <row r="284" spans="1:18">
@@ -22240,7 +22240,7 @@
       </c>
       <c r="R284" t="str">
         <f ca="1" t="shared" si="28"/>
-        <v>2025-01-15</v>
+        <v>2025-11-03</v>
       </c>
     </row>
     <row r="285" spans="1:18">
@@ -22294,7 +22294,7 @@
       </c>
       <c r="R285" t="str">
         <f ca="1" t="shared" si="28"/>
-        <v>2024-08-26</v>
+        <v>2025-05-01</v>
       </c>
     </row>
     <row r="286" spans="1:18">
@@ -22351,7 +22351,7 @@
       </c>
       <c r="R286" t="str">
         <f ca="1" t="shared" si="28"/>
-        <v>2025-04-25</v>
+        <v>2025-07-28</v>
       </c>
     </row>
     <row r="287" spans="1:18">
@@ -22405,7 +22405,7 @@
       </c>
       <c r="R287" t="str">
         <f ca="1" t="shared" si="28"/>
-        <v>2025-05-15</v>
+        <v>2025-04-16</v>
       </c>
     </row>
     <row r="288" spans="1:18">
@@ -22463,7 +22463,7 @@
       </c>
       <c r="R288" t="str">
         <f ca="1" t="shared" si="28"/>
-        <v>2025-07-07</v>
+        <v>2025-11-12</v>
       </c>
     </row>
     <row r="289" spans="1:18">
@@ -22517,7 +22517,7 @@
       </c>
       <c r="R289" t="str">
         <f ca="1" t="shared" si="28"/>
-        <v>2025-08-13</v>
+        <v>2025-09-02</v>
       </c>
     </row>
     <row r="290" spans="1:18">
@@ -22575,7 +22575,7 @@
       </c>
       <c r="R290" t="str">
         <f ca="1" t="shared" si="28"/>
-        <v>2025-04-15</v>
+        <v>2025-01-18</v>
       </c>
     </row>
     <row r="291" spans="1:18">
@@ -22633,7 +22633,7 @@
       </c>
       <c r="R291" t="str">
         <f ca="1" t="shared" si="28"/>
-        <v>2024-11-30</v>
+        <v>2025-06-08</v>
       </c>
     </row>
     <row r="292" spans="1:18">
@@ -22687,7 +22687,7 @@
       </c>
       <c r="R292" t="str">
         <f ca="1" t="shared" si="28"/>
-        <v>2025-01-21</v>
+        <v>2024-11-21</v>
       </c>
     </row>
     <row r="293" spans="1:18">
@@ -22741,8 +22741,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R293" t="str">
-        <f ca="1" t="shared" ref="R293:R302" si="29">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-11-23</v>
+        <f ca="1" t="shared" ref="R293:R302" si="29">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2024-12-26</v>
       </c>
     </row>
     <row r="294" spans="1:18">
@@ -22800,7 +22800,7 @@
       </c>
       <c r="R294" t="str">
         <f ca="1" t="shared" si="29"/>
-        <v>2025-01-05</v>
+        <v>2024-12-28</v>
       </c>
     </row>
     <row r="295" spans="1:18">
@@ -22858,7 +22858,7 @@
       </c>
       <c r="R295" t="str">
         <f ca="1" t="shared" si="29"/>
-        <v>2025-09-26</v>
+        <v>2024-11-26</v>
       </c>
     </row>
     <row r="296" spans="1:18">
@@ -22916,7 +22916,7 @@
       </c>
       <c r="R296" t="str">
         <f ca="1" t="shared" si="29"/>
-        <v>2024-08-26</v>
+        <v>2025-10-15</v>
       </c>
     </row>
     <row r="297" spans="1:18">
@@ -22970,7 +22970,7 @@
       </c>
       <c r="R297" t="str">
         <f ca="1" t="shared" si="29"/>
-        <v>2025-07-05</v>
+        <v>2024-09-09</v>
       </c>
     </row>
     <row r="298" spans="1:18">
@@ -23024,7 +23024,7 @@
       </c>
       <c r="R298" t="str">
         <f ca="1" t="shared" si="29"/>
-        <v>2024-10-02</v>
+        <v>2025-11-18</v>
       </c>
     </row>
     <row r="299" spans="1:18">
@@ -23082,7 +23082,7 @@
       </c>
       <c r="R299" t="str">
         <f ca="1" t="shared" si="29"/>
-        <v>2025-05-10</v>
+        <v>2024-08-13</v>
       </c>
     </row>
     <row r="300" spans="1:18">
@@ -23139,7 +23139,7 @@
       </c>
       <c r="R300" t="str">
         <f ca="1" t="shared" si="29"/>
-        <v>2025-05-03</v>
+        <v>2025-08-16</v>
       </c>
     </row>
     <row r="301" spans="1:18">
@@ -23197,7 +23197,7 @@
       </c>
       <c r="R301" t="str">
         <f ca="1" t="shared" si="29"/>
-        <v>2024-09-03</v>
+        <v>2025-06-18</v>
       </c>
     </row>
     <row r="302" spans="1:18">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="R302" t="str">
         <f ca="1" t="shared" si="29"/>
-        <v>2025-06-21</v>
+        <v>2024-09-11</v>
       </c>
     </row>
     <row r="303" spans="1:18">
@@ -23304,8 +23304,8 @@
         <v>33</v>
       </c>
       <c r="R303" t="str">
-        <f ca="1" t="shared" ref="R303:R312" si="30">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-03-02</v>
+        <f ca="1" t="shared" ref="R303:R312" si="30">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2024-12-14</v>
       </c>
     </row>
     <row r="304" spans="1:18">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="R304" t="str">
         <f ca="1" t="shared" si="30"/>
-        <v>2025-04-18</v>
+        <v>2025-10-14</v>
       </c>
     </row>
     <row r="305" spans="1:18">
@@ -23421,7 +23421,7 @@
       </c>
       <c r="R305" t="str">
         <f ca="1" t="shared" si="30"/>
-        <v>2025-02-13</v>
+        <v>2025-07-19</v>
       </c>
     </row>
     <row r="306" spans="1:18">
@@ -23479,7 +23479,7 @@
       </c>
       <c r="R306" t="str">
         <f ca="1" t="shared" si="30"/>
-        <v>2025-04-05</v>
+        <v>2025-05-06</v>
       </c>
     </row>
     <row r="307" spans="1:18">
@@ -23537,7 +23537,7 @@
       </c>
       <c r="R307" t="str">
         <f ca="1" t="shared" si="30"/>
-        <v>2025-03-07</v>
+        <v>2025-02-03</v>
       </c>
     </row>
     <row r="308" spans="1:18">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="R308" t="str">
         <f ca="1" t="shared" si="30"/>
-        <v>2025-08-17</v>
+        <v>2025-05-23</v>
       </c>
     </row>
     <row r="309" spans="1:18">
@@ -23653,7 +23653,7 @@
       </c>
       <c r="R309" t="str">
         <f ca="1" t="shared" si="30"/>
-        <v>2024-12-16</v>
+        <v>2025-07-23</v>
       </c>
     </row>
     <row r="310" spans="1:18">
@@ -23711,7 +23711,7 @@
       </c>
       <c r="R310" t="str">
         <f ca="1" t="shared" si="30"/>
-        <v>2024-12-06</v>
+        <v>2024-10-01</v>
       </c>
     </row>
     <row r="311" spans="1:18">
@@ -23765,7 +23765,7 @@
       </c>
       <c r="R311" t="str">
         <f ca="1" t="shared" si="30"/>
-        <v>2025-10-03</v>
+        <v>2025-10-10</v>
       </c>
     </row>
     <row r="312" spans="1:18">
@@ -23823,7 +23823,7 @@
       </c>
       <c r="R312" t="str">
         <f ca="1" t="shared" si="30"/>
-        <v>2024-08-09</v>
+        <v>2025-03-08</v>
       </c>
     </row>
     <row r="313" spans="1:18">
@@ -23877,8 +23877,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R313" t="str">
-        <f ca="1" t="shared" ref="R313:R322" si="31">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-02-16</v>
+        <f ca="1" t="shared" ref="R313:R322" si="31">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-03-14</v>
       </c>
     </row>
     <row r="314" spans="1:18">
@@ -23932,7 +23932,7 @@
       </c>
       <c r="R314" t="str">
         <f ca="1" t="shared" si="31"/>
-        <v>2025-05-11</v>
+        <v>2025-08-26</v>
       </c>
     </row>
     <row r="315" spans="1:18">
@@ -23990,7 +23990,7 @@
       </c>
       <c r="R315" t="str">
         <f ca="1" t="shared" si="31"/>
-        <v>2025-08-02</v>
+        <v>2024-09-04</v>
       </c>
     </row>
     <row r="316" spans="1:18">
@@ -24048,7 +24048,7 @@
       </c>
       <c r="R316" t="str">
         <f ca="1" t="shared" si="31"/>
-        <v>2024-11-04</v>
+        <v>2025-04-23</v>
       </c>
     </row>
     <row r="317" spans="1:18">
@@ -24106,7 +24106,7 @@
       </c>
       <c r="R317" t="str">
         <f ca="1" t="shared" si="31"/>
-        <v>2025-05-08</v>
+        <v>2025-08-13</v>
       </c>
     </row>
     <row r="318" spans="1:18">
@@ -24161,7 +24161,7 @@
       </c>
       <c r="R318" t="str">
         <f ca="1" t="shared" si="31"/>
-        <v>2025-03-01</v>
+        <v>2025-05-07</v>
       </c>
     </row>
     <row r="319" spans="1:18">
@@ -24219,7 +24219,7 @@
       </c>
       <c r="R319" t="str">
         <f ca="1" t="shared" si="31"/>
-        <v>2024-09-24</v>
+        <v>2024-09-14</v>
       </c>
     </row>
     <row r="320" spans="1:18">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="R320" t="str">
         <f ca="1" t="shared" si="31"/>
-        <v>2024-08-01</v>
+        <v>2024-11-03</v>
       </c>
     </row>
     <row r="321" spans="1:18">
@@ -24335,7 +24335,7 @@
       </c>
       <c r="R321" t="str">
         <f ca="1" t="shared" si="31"/>
-        <v>2025-08-29</v>
+        <v>2024-10-01</v>
       </c>
     </row>
     <row r="322" spans="1:18">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="R322" t="str">
         <f ca="1" t="shared" si="31"/>
-        <v>2025-07-17</v>
+        <v>2025-10-09</v>
       </c>
     </row>
     <row r="323" spans="1:18">
@@ -24450,8 +24450,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R323" t="str">
-        <f ca="1" t="shared" ref="R323:R332" si="32">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-09-02</v>
+        <f ca="1" t="shared" ref="R323:R332" si="32">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2024-11-13</v>
       </c>
     </row>
     <row r="324" spans="1:18">
@@ -24505,7 +24505,7 @@
       </c>
       <c r="R324" t="str">
         <f ca="1" t="shared" si="32"/>
-        <v>2025-01-28</v>
+        <v>2025-09-21</v>
       </c>
     </row>
     <row r="325" spans="1:18">
@@ -24562,7 +24562,7 @@
       </c>
       <c r="R325" t="str">
         <f ca="1" t="shared" si="32"/>
-        <v>2025-08-13</v>
+        <v>2025-01-05</v>
       </c>
     </row>
     <row r="326" spans="1:18">
@@ -24616,7 +24616,7 @@
       </c>
       <c r="R326" t="str">
         <f ca="1" t="shared" si="32"/>
-        <v>2025-05-14</v>
+        <v>2024-12-10</v>
       </c>
     </row>
     <row r="327" spans="1:18">
@@ -24674,7 +24674,7 @@
       </c>
       <c r="R327" t="str">
         <f ca="1" t="shared" si="32"/>
-        <v>2025-08-20</v>
+        <v>2024-10-04</v>
       </c>
     </row>
     <row r="328" spans="1:18">
@@ -24732,7 +24732,7 @@
       </c>
       <c r="R328" t="str">
         <f ca="1" t="shared" si="32"/>
-        <v>2024-08-31</v>
+        <v>2025-11-21</v>
       </c>
     </row>
     <row r="329" spans="1:18">
@@ -24789,7 +24789,7 @@
       </c>
       <c r="R329" t="str">
         <f ca="1" t="shared" si="32"/>
-        <v>2024-09-29</v>
+        <v>2024-12-21</v>
       </c>
     </row>
     <row r="330" spans="1:18">
@@ -24843,7 +24843,7 @@
       </c>
       <c r="R330" t="str">
         <f ca="1" t="shared" si="32"/>
-        <v>2024-09-24</v>
+        <v>2024-11-20</v>
       </c>
     </row>
     <row r="331" spans="1:18">
@@ -24897,7 +24897,7 @@
       </c>
       <c r="R331" t="str">
         <f ca="1" t="shared" si="32"/>
-        <v>2025-03-16</v>
+        <v>2025-08-03</v>
       </c>
     </row>
     <row r="332" spans="1:18">
@@ -24955,7 +24955,7 @@
       </c>
       <c r="R332" t="str">
         <f ca="1" t="shared" si="32"/>
-        <v>2025-04-28</v>
+        <v>2025-05-03</v>
       </c>
     </row>
     <row r="333" spans="1:18">
@@ -25008,8 +25008,8 @@
         <v>33</v>
       </c>
       <c r="R333" t="str">
-        <f ca="1" t="shared" ref="R333:R342" si="33">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-12-10</v>
+        <f ca="1" t="shared" ref="R333:R342" si="33">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-08-30</v>
       </c>
     </row>
     <row r="334" spans="1:18">
@@ -25063,7 +25063,7 @@
       </c>
       <c r="R334" t="str">
         <f ca="1" t="shared" si="33"/>
-        <v>2024-09-18</v>
+        <v>2024-11-05</v>
       </c>
     </row>
     <row r="335" spans="1:18">
@@ -25117,7 +25117,7 @@
       </c>
       <c r="R335" t="str">
         <f ca="1" t="shared" si="33"/>
-        <v>2024-10-10</v>
+        <v>2024-08-02</v>
       </c>
     </row>
     <row r="336" spans="1:18">
@@ -25175,7 +25175,7 @@
       </c>
       <c r="R336" t="str">
         <f ca="1" t="shared" si="33"/>
-        <v>2024-09-02</v>
+        <v>2025-03-14</v>
       </c>
     </row>
     <row r="337" spans="1:18">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="R337" t="str">
         <f ca="1" t="shared" si="33"/>
-        <v>2024-10-20</v>
+        <v>2024-10-16</v>
       </c>
     </row>
     <row r="338" spans="1:18">
@@ -25291,7 +25291,7 @@
       </c>
       <c r="R338" t="str">
         <f ca="1" t="shared" si="33"/>
-        <v>2024-12-06</v>
+        <v>2024-09-13</v>
       </c>
     </row>
     <row r="339" spans="1:18">
@@ -25349,7 +25349,7 @@
       </c>
       <c r="R339" t="str">
         <f ca="1" t="shared" si="33"/>
-        <v>2024-10-18</v>
+        <v>2025-08-03</v>
       </c>
     </row>
     <row r="340" spans="1:18">
@@ -25407,7 +25407,7 @@
       </c>
       <c r="R340" t="str">
         <f ca="1" t="shared" si="33"/>
-        <v>2025-08-16</v>
+        <v>2024-08-01</v>
       </c>
     </row>
     <row r="341" spans="1:18">
@@ -25464,7 +25464,7 @@
       </c>
       <c r="R341" t="str">
         <f ca="1" t="shared" si="33"/>
-        <v>2025-09-14</v>
+        <v>2024-12-14</v>
       </c>
     </row>
     <row r="342" spans="1:18">
@@ -25522,7 +25522,7 @@
       </c>
       <c r="R342" t="str">
         <f ca="1" t="shared" si="33"/>
-        <v>2025-06-01</v>
+        <v>2025-03-21</v>
       </c>
     </row>
     <row r="343" spans="1:18">
@@ -25575,8 +25575,8 @@
         <v>33</v>
       </c>
       <c r="R343" t="str">
-        <f ca="1" t="shared" ref="R343:R352" si="34">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-08-19</v>
+        <f ca="1" t="shared" ref="R343:R352" si="34">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-03-22</v>
       </c>
     </row>
     <row r="344" spans="1:18">
@@ -25631,7 +25631,7 @@
       </c>
       <c r="R344" t="str">
         <f ca="1" t="shared" si="34"/>
-        <v>2025-03-30</v>
+        <v>2024-12-30</v>
       </c>
     </row>
     <row r="345" spans="1:18">
@@ -25686,7 +25686,7 @@
       </c>
       <c r="R345" t="str">
         <f ca="1" t="shared" si="34"/>
-        <v>2025-08-27</v>
+        <v>2025-02-17</v>
       </c>
     </row>
     <row r="346" spans="1:18">
@@ -25744,7 +25744,7 @@
       </c>
       <c r="R346" t="str">
         <f ca="1" t="shared" si="34"/>
-        <v>2024-10-21</v>
+        <v>2024-10-02</v>
       </c>
     </row>
     <row r="347" spans="1:18">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="R347" t="str">
         <f ca="1" t="shared" si="34"/>
-        <v>2024-12-03</v>
+        <v>2025-04-05</v>
       </c>
     </row>
     <row r="348" spans="1:18">
@@ -25855,7 +25855,7 @@
       </c>
       <c r="R348" t="str">
         <f ca="1" t="shared" si="34"/>
-        <v>2025-07-20</v>
+        <v>2024-08-14</v>
       </c>
     </row>
     <row r="349" spans="1:18">
@@ -25913,7 +25913,7 @@
       </c>
       <c r="R349" t="str">
         <f ca="1" t="shared" si="34"/>
-        <v>2025-09-18</v>
+        <v>2024-08-06</v>
       </c>
     </row>
     <row r="350" spans="1:18">
@@ -25971,7 +25971,7 @@
       </c>
       <c r="R350" t="str">
         <f ca="1" t="shared" si="34"/>
-        <v>2025-09-23</v>
+        <v>2025-04-18</v>
       </c>
     </row>
     <row r="351" spans="1:18">
@@ -26028,7 +26028,7 @@
       </c>
       <c r="R351" t="str">
         <f ca="1" t="shared" si="34"/>
-        <v>2024-11-30</v>
+        <v>2025-05-17</v>
       </c>
     </row>
     <row r="352" spans="1:18">
@@ -26082,7 +26082,7 @@
       </c>
       <c r="R352" t="str">
         <f ca="1" t="shared" si="34"/>
-        <v>2024-10-20</v>
+        <v>2025-06-04</v>
       </c>
     </row>
     <row r="353" spans="1:18">
@@ -26135,8 +26135,8 @@
         <v>33</v>
       </c>
       <c r="R353" t="str">
-        <f ca="1" t="shared" ref="R353:R362" si="35">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-08-16</v>
+        <f ca="1" t="shared" ref="R353:R362" si="35">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-02-18</v>
       </c>
     </row>
     <row r="354" spans="1:18">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="R354" t="str">
         <f ca="1" t="shared" si="35"/>
-        <v>2024-10-05</v>
+        <v>2025-10-14</v>
       </c>
     </row>
     <row r="355" spans="1:18">
@@ -26249,7 +26249,7 @@
       </c>
       <c r="R355" t="str">
         <f ca="1" t="shared" si="35"/>
-        <v>2025-09-29</v>
+        <v>2025-11-17</v>
       </c>
     </row>
     <row r="356" spans="1:18">
@@ -26306,7 +26306,7 @@
       </c>
       <c r="R356" t="str">
         <f ca="1" t="shared" si="35"/>
-        <v>2024-10-16</v>
+        <v>2025-05-20</v>
       </c>
     </row>
     <row r="357" spans="1:18">
@@ -26364,7 +26364,7 @@
       </c>
       <c r="R357" t="str">
         <f ca="1" t="shared" si="35"/>
-        <v>2025-04-04</v>
+        <v>2025-08-13</v>
       </c>
     </row>
     <row r="358" spans="1:18">
@@ -26422,7 +26422,7 @@
       </c>
       <c r="R358" t="str">
         <f ca="1" t="shared" si="35"/>
-        <v>2024-08-22</v>
+        <v>2025-02-23</v>
       </c>
     </row>
     <row r="359" spans="1:18">
@@ -26480,7 +26480,7 @@
       </c>
       <c r="R359" t="str">
         <f ca="1" t="shared" si="35"/>
-        <v>2024-11-17</v>
+        <v>2025-01-11</v>
       </c>
     </row>
     <row r="360" spans="1:18">
@@ -26538,7 +26538,7 @@
       </c>
       <c r="R360" t="str">
         <f ca="1" t="shared" si="35"/>
-        <v>2024-12-31</v>
+        <v>2025-03-10</v>
       </c>
     </row>
     <row r="361" spans="1:18">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="R361" t="str">
         <f ca="1" t="shared" si="35"/>
-        <v>2025-03-05</v>
+        <v>2025-04-05</v>
       </c>
     </row>
     <row r="362" spans="1:18">
@@ -26654,7 +26654,7 @@
       </c>
       <c r="R362" t="str">
         <f ca="1" t="shared" si="35"/>
-        <v>2025-08-24</v>
+        <v>2025-06-04</v>
       </c>
     </row>
     <row r="363" spans="1:18">
@@ -26711,8 +26711,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R363" t="str">
-        <f ca="1" t="shared" ref="R363:R372" si="36">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-07-26</v>
+        <f ca="1" t="shared" ref="R363:R372" si="36">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-01-21</v>
       </c>
     </row>
     <row r="364" spans="1:18">
@@ -26770,7 +26770,7 @@
       </c>
       <c r="R364" t="str">
         <f ca="1" t="shared" si="36"/>
-        <v>2025-08-08</v>
+        <v>2025-10-07</v>
       </c>
     </row>
     <row r="365" spans="1:18">
@@ -26828,7 +26828,7 @@
       </c>
       <c r="R365" t="str">
         <f ca="1" t="shared" si="36"/>
-        <v>2025-02-16</v>
+        <v>2025-04-04</v>
       </c>
     </row>
     <row r="366" spans="1:18">
@@ -26886,7 +26886,7 @@
       </c>
       <c r="R366" t="str">
         <f ca="1" t="shared" si="36"/>
-        <v>2024-08-12</v>
+        <v>2024-12-24</v>
       </c>
     </row>
     <row r="367" spans="1:18">
@@ -26944,7 +26944,7 @@
       </c>
       <c r="R367" t="str">
         <f ca="1" t="shared" si="36"/>
-        <v>2024-11-11</v>
+        <v>2024-10-31</v>
       </c>
     </row>
     <row r="368" spans="1:18">
@@ -26998,7 +26998,7 @@
       </c>
       <c r="R368" t="str">
         <f ca="1" t="shared" si="36"/>
-        <v>2024-10-15</v>
+        <v>2025-06-12</v>
       </c>
     </row>
     <row r="369" spans="1:18">
@@ -27052,7 +27052,7 @@
       </c>
       <c r="R369" t="str">
         <f ca="1" t="shared" si="36"/>
-        <v>2025-01-13</v>
+        <v>2025-04-13</v>
       </c>
     </row>
     <row r="370" spans="1:18">
@@ -27110,7 +27110,7 @@
       </c>
       <c r="R370" t="str">
         <f ca="1" t="shared" si="36"/>
-        <v>2025-09-13</v>
+        <v>2025-01-13</v>
       </c>
     </row>
     <row r="371" spans="1:18">
@@ -27168,7 +27168,7 @@
       </c>
       <c r="R371" t="str">
         <f ca="1" t="shared" si="36"/>
-        <v>2025-01-27</v>
+        <v>2024-12-27</v>
       </c>
     </row>
     <row r="372" spans="1:18">
@@ -27222,7 +27222,7 @@
       </c>
       <c r="R372" t="str">
         <f ca="1" t="shared" si="36"/>
-        <v>2025-03-03</v>
+        <v>2025-08-23</v>
       </c>
     </row>
     <row r="373" spans="1:18">
@@ -27279,8 +27279,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R373" t="str">
-        <f ca="1" t="shared" ref="R373:R382" si="37">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-07-16</v>
+        <f ca="1" t="shared" ref="R373:R382" si="37">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2024-08-26</v>
       </c>
     </row>
     <row r="374" spans="1:18">
@@ -27334,7 +27334,7 @@
       </c>
       <c r="R374" t="str">
         <f ca="1" t="shared" si="37"/>
-        <v>2024-12-24</v>
+        <v>2025-03-22</v>
       </c>
     </row>
     <row r="375" spans="1:18">
@@ -27388,7 +27388,7 @@
       </c>
       <c r="R375" t="str">
         <f ca="1" t="shared" si="37"/>
-        <v>2024-11-13</v>
+        <v>2025-05-30</v>
       </c>
     </row>
     <row r="376" spans="1:18">
@@ -27442,7 +27442,7 @@
       </c>
       <c r="R376" t="str">
         <f ca="1" t="shared" si="37"/>
-        <v>2025-01-09</v>
+        <v>2024-12-08</v>
       </c>
     </row>
     <row r="377" spans="1:18">
@@ -27500,7 +27500,7 @@
       </c>
       <c r="R377" t="str">
         <f ca="1" t="shared" si="37"/>
-        <v>2025-07-29</v>
+        <v>2025-01-24</v>
       </c>
     </row>
     <row r="378" spans="1:18">
@@ -27558,7 +27558,7 @@
       </c>
       <c r="R378" t="str">
         <f ca="1" t="shared" si="37"/>
-        <v>2025-03-14</v>
+        <v>2025-06-05</v>
       </c>
     </row>
     <row r="379" spans="1:18">
@@ -27616,7 +27616,7 @@
       </c>
       <c r="R379" t="str">
         <f ca="1" t="shared" si="37"/>
-        <v>2025-03-22</v>
+        <v>2025-04-08</v>
       </c>
     </row>
     <row r="380" spans="1:18">
@@ -27674,7 +27674,7 @@
       </c>
       <c r="R380" t="str">
         <f ca="1" t="shared" si="37"/>
-        <v>2025-10-07</v>
+        <v>2025-10-17</v>
       </c>
     </row>
     <row r="381" spans="1:18">
@@ -27732,7 +27732,7 @@
       </c>
       <c r="R381" t="str">
         <f ca="1" t="shared" si="37"/>
-        <v>2025-02-13</v>
+        <v>2024-11-07</v>
       </c>
     </row>
     <row r="382" spans="1:18">
@@ -27790,7 +27790,7 @@
       </c>
       <c r="R382" t="str">
         <f ca="1" t="shared" si="37"/>
-        <v>2025-08-23</v>
+        <v>2025-04-22</v>
       </c>
     </row>
     <row r="383" spans="1:18">
@@ -27847,8 +27847,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R383" t="str">
-        <f ca="1" t="shared" ref="R383:R392" si="38">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-12-13</v>
+        <f ca="1" t="shared" ref="R383:R392" si="38">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-03-24</v>
       </c>
     </row>
     <row r="384" spans="1:18">
@@ -27906,7 +27906,7 @@
       </c>
       <c r="R384" t="str">
         <f ca="1" t="shared" si="38"/>
-        <v>2025-06-12</v>
+        <v>2025-08-03</v>
       </c>
     </row>
     <row r="385" spans="1:18">
@@ -27964,7 +27964,7 @@
       </c>
       <c r="R385" t="str">
         <f ca="1" t="shared" si="38"/>
-        <v>2024-12-27</v>
+        <v>2024-08-26</v>
       </c>
     </row>
     <row r="386" spans="1:18">
@@ -28022,7 +28022,7 @@
       </c>
       <c r="R386" t="str">
         <f ca="1" t="shared" si="38"/>
-        <v>2025-01-11</v>
+        <v>2024-09-07</v>
       </c>
     </row>
     <row r="387" spans="1:18">
@@ -28080,7 +28080,7 @@
       </c>
       <c r="R387" t="str">
         <f ca="1" t="shared" si="38"/>
-        <v>2024-09-23</v>
+        <v>2024-12-01</v>
       </c>
     </row>
     <row r="388" spans="1:18">
@@ -28134,7 +28134,7 @@
       </c>
       <c r="R388" t="str">
         <f ca="1" t="shared" si="38"/>
-        <v>2025-02-20</v>
+        <v>2024-10-08</v>
       </c>
     </row>
     <row r="389" spans="1:18">
@@ -28192,7 +28192,7 @@
       </c>
       <c r="R389" t="str">
         <f ca="1" t="shared" si="38"/>
-        <v>2024-10-26</v>
+        <v>2025-10-20</v>
       </c>
     </row>
     <row r="390" spans="1:18">
@@ -28249,7 +28249,7 @@
       </c>
       <c r="R390" t="str">
         <f ca="1" t="shared" si="38"/>
-        <v>2025-07-19</v>
+        <v>2025-04-22</v>
       </c>
     </row>
     <row r="391" spans="1:18">
@@ -28307,7 +28307,7 @@
       </c>
       <c r="R391" t="str">
         <f ca="1" t="shared" si="38"/>
-        <v>2024-09-14</v>
+        <v>2025-01-25</v>
       </c>
     </row>
     <row r="392" spans="1:18">
@@ -28361,7 +28361,7 @@
       </c>
       <c r="R392" t="str">
         <f ca="1" t="shared" si="38"/>
-        <v>2025-04-05</v>
+        <v>2025-02-19</v>
       </c>
     </row>
     <row r="393" spans="1:18">
@@ -28414,8 +28414,8 @@
         <v>33</v>
       </c>
       <c r="R393" t="str">
-        <f ca="1" t="shared" ref="R393:R402" si="39">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-09-17</v>
+        <f ca="1" t="shared" ref="R393:R402" si="39">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-05-13</v>
       </c>
     </row>
     <row r="394" spans="1:18">
@@ -28470,7 +28470,7 @@
       </c>
       <c r="R394" t="str">
         <f ca="1" t="shared" si="39"/>
-        <v>2025-08-01</v>
+        <v>2025-01-16</v>
       </c>
     </row>
     <row r="395" spans="1:18">
@@ -28528,7 +28528,7 @@
       </c>
       <c r="R395" t="str">
         <f ca="1" t="shared" si="39"/>
-        <v>2025-10-05</v>
+        <v>2024-08-01</v>
       </c>
     </row>
     <row r="396" spans="1:18">
@@ -28582,7 +28582,7 @@
       </c>
       <c r="R396" t="str">
         <f ca="1" t="shared" si="39"/>
-        <v>2024-11-23</v>
+        <v>2025-03-16</v>
       </c>
     </row>
     <row r="397" spans="1:18">
@@ -28639,7 +28639,7 @@
       </c>
       <c r="R397" t="str">
         <f ca="1" t="shared" si="39"/>
-        <v>2024-08-03</v>
+        <v>2024-09-08</v>
       </c>
     </row>
     <row r="398" spans="1:18">
@@ -28696,7 +28696,7 @@
       </c>
       <c r="R398" t="str">
         <f ca="1" t="shared" si="39"/>
-        <v>2025-08-22</v>
+        <v>2025-07-07</v>
       </c>
     </row>
     <row r="399" spans="1:18">
@@ -28750,7 +28750,7 @@
       </c>
       <c r="R399" t="str">
         <f ca="1" t="shared" si="39"/>
-        <v>2024-12-21</v>
+        <v>2025-05-04</v>
       </c>
     </row>
     <row r="400" spans="1:18">
@@ -28804,7 +28804,7 @@
       </c>
       <c r="R400" t="str">
         <f ca="1" t="shared" si="39"/>
-        <v>2025-05-26</v>
+        <v>2025-11-26</v>
       </c>
     </row>
     <row r="401" spans="1:18">
@@ -28862,7 +28862,7 @@
       </c>
       <c r="R401" t="str">
         <f ca="1" t="shared" si="39"/>
-        <v>2025-10-07</v>
+        <v>2025-09-10</v>
       </c>
     </row>
     <row r="402" spans="1:18">
@@ -28916,7 +28916,7 @@
       </c>
       <c r="R402" t="str">
         <f ca="1" t="shared" si="39"/>
-        <v>2025-06-11</v>
+        <v>2025-02-15</v>
       </c>
     </row>
     <row r="403" spans="1:18">
@@ -28973,8 +28973,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R403" t="str">
-        <f ca="1" t="shared" ref="R403:R412" si="40">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-01-04</v>
+        <f ca="1" t="shared" ref="R403:R412" si="40">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2024-09-04</v>
       </c>
     </row>
     <row r="404" spans="1:18">
@@ -29032,7 +29032,7 @@
       </c>
       <c r="R404" t="str">
         <f ca="1" t="shared" si="40"/>
-        <v>2024-10-10</v>
+        <v>2024-12-01</v>
       </c>
     </row>
     <row r="405" spans="1:18">
@@ -29090,7 +29090,7 @@
       </c>
       <c r="R405" t="str">
         <f ca="1" t="shared" si="40"/>
-        <v>2025-08-07</v>
+        <v>2025-11-28</v>
       </c>
     </row>
     <row r="406" spans="1:18">
@@ -29144,7 +29144,7 @@
       </c>
       <c r="R406" t="str">
         <f ca="1" t="shared" si="40"/>
-        <v>2025-06-22</v>
+        <v>2024-08-03</v>
       </c>
     </row>
     <row r="407" spans="1:18">
@@ -29202,7 +29202,7 @@
       </c>
       <c r="R407" t="str">
         <f ca="1" t="shared" si="40"/>
-        <v>2024-11-14</v>
+        <v>2024-08-12</v>
       </c>
     </row>
     <row r="408" spans="1:18">
@@ -29260,7 +29260,7 @@
       </c>
       <c r="R408" t="str">
         <f ca="1" t="shared" si="40"/>
-        <v>2025-02-09</v>
+        <v>2025-06-20</v>
       </c>
     </row>
     <row r="409" spans="1:18">
@@ -29318,7 +29318,7 @@
       </c>
       <c r="R409" t="str">
         <f ca="1" t="shared" si="40"/>
-        <v>2025-03-17</v>
+        <v>2024-12-30</v>
       </c>
     </row>
     <row r="410" spans="1:18">
@@ -29373,7 +29373,7 @@
       </c>
       <c r="R410" t="str">
         <f ca="1" t="shared" si="40"/>
-        <v>2024-11-22</v>
+        <v>2025-10-10</v>
       </c>
     </row>
     <row r="411" spans="1:18">
@@ -29431,7 +29431,7 @@
       </c>
       <c r="R411" t="str">
         <f ca="1" t="shared" si="40"/>
-        <v>2025-07-28</v>
+        <v>2025-07-13</v>
       </c>
     </row>
     <row r="412" spans="1:18">
@@ -29489,7 +29489,7 @@
       </c>
       <c r="R412" t="str">
         <f ca="1" t="shared" si="40"/>
-        <v>2024-12-13</v>
+        <v>2025-01-27</v>
       </c>
     </row>
     <row r="413" spans="1:18">
@@ -29546,8 +29546,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R413" t="str">
-        <f ca="1" t="shared" ref="R413:R422" si="41">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-09-13</v>
+        <f ca="1" t="shared" ref="R413:R422" si="41">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-01-04</v>
       </c>
     </row>
     <row r="414" spans="1:18">
@@ -29601,7 +29601,7 @@
       </c>
       <c r="R414" t="str">
         <f ca="1" t="shared" si="41"/>
-        <v>2024-08-02</v>
+        <v>2025-05-15</v>
       </c>
     </row>
     <row r="415" spans="1:18">
@@ -29659,7 +29659,7 @@
       </c>
       <c r="R415" t="str">
         <f ca="1" t="shared" si="41"/>
-        <v>2025-05-11</v>
+        <v>2024-12-23</v>
       </c>
     </row>
     <row r="416" spans="1:18">
@@ -29717,7 +29717,7 @@
       </c>
       <c r="R416" t="str">
         <f ca="1" t="shared" si="41"/>
-        <v>2024-11-22</v>
+        <v>2025-08-24</v>
       </c>
     </row>
     <row r="417" spans="1:18">
@@ -29775,7 +29775,7 @@
       </c>
       <c r="R417" t="str">
         <f ca="1" t="shared" si="41"/>
-        <v>2024-12-16</v>
+        <v>2025-04-18</v>
       </c>
     </row>
     <row r="418" spans="1:18">
@@ -29833,7 +29833,7 @@
       </c>
       <c r="R418" t="str">
         <f ca="1" t="shared" si="41"/>
-        <v>2024-09-19</v>
+        <v>2025-01-04</v>
       </c>
     </row>
     <row r="419" spans="1:18">
@@ -29887,7 +29887,7 @@
       </c>
       <c r="R419" t="str">
         <f ca="1" t="shared" si="41"/>
-        <v>2025-07-29</v>
+        <v>2024-09-07</v>
       </c>
     </row>
     <row r="420" spans="1:18">
@@ -29945,7 +29945,7 @@
       </c>
       <c r="R420" t="str">
         <f ca="1" t="shared" si="41"/>
-        <v>2025-06-13</v>
+        <v>2024-10-04</v>
       </c>
     </row>
     <row r="421" spans="1:18">
@@ -30003,7 +30003,7 @@
       </c>
       <c r="R421" t="str">
         <f ca="1" t="shared" si="41"/>
-        <v>2025-05-02</v>
+        <v>2025-04-03</v>
       </c>
     </row>
     <row r="422" spans="1:18">
@@ -30057,7 +30057,7 @@
       </c>
       <c r="R422" t="str">
         <f ca="1" t="shared" si="41"/>
-        <v>2024-11-11</v>
+        <v>2025-07-25</v>
       </c>
     </row>
     <row r="423" spans="1:18">
@@ -30110,8 +30110,8 @@
         <v>33</v>
       </c>
       <c r="R423" t="str">
-        <f ca="1" t="shared" ref="R423:R432" si="42">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-04-20</v>
+        <f ca="1" t="shared" ref="R423:R432" si="42">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2024-10-05</v>
       </c>
     </row>
     <row r="424" spans="1:18">
@@ -30169,7 +30169,7 @@
       </c>
       <c r="R424" t="str">
         <f ca="1" t="shared" si="42"/>
-        <v>2025-04-20</v>
+        <v>2025-04-08</v>
       </c>
     </row>
     <row r="425" spans="1:18">
@@ -30227,7 +30227,7 @@
       </c>
       <c r="R425" t="str">
         <f ca="1" t="shared" si="42"/>
-        <v>2024-12-14</v>
+        <v>2025-03-05</v>
       </c>
     </row>
     <row r="426" spans="1:18">
@@ -30285,7 +30285,7 @@
       </c>
       <c r="R426" t="str">
         <f ca="1" t="shared" si="42"/>
-        <v>2025-10-01</v>
+        <v>2024-11-07</v>
       </c>
     </row>
     <row r="427" spans="1:18">
@@ -30343,7 +30343,7 @@
       </c>
       <c r="R427" t="str">
         <f ca="1" t="shared" si="42"/>
-        <v>2024-08-24</v>
+        <v>2025-06-23</v>
       </c>
     </row>
     <row r="428" spans="1:18">
@@ -30401,7 +30401,7 @@
       </c>
       <c r="R428" t="str">
         <f ca="1" t="shared" si="42"/>
-        <v>2025-08-19</v>
+        <v>2024-11-04</v>
       </c>
     </row>
     <row r="429" spans="1:18">
@@ -30459,7 +30459,7 @@
       </c>
       <c r="R429" t="str">
         <f ca="1" t="shared" si="42"/>
-        <v>2025-07-15</v>
+        <v>2024-12-20</v>
       </c>
     </row>
     <row r="430" spans="1:18">
@@ -30517,7 +30517,7 @@
       </c>
       <c r="R430" t="str">
         <f ca="1" t="shared" si="42"/>
-        <v>2025-01-13</v>
+        <v>2025-08-21</v>
       </c>
     </row>
     <row r="431" spans="1:18">
@@ -30571,7 +30571,7 @@
       </c>
       <c r="R431" t="str">
         <f ca="1" t="shared" si="42"/>
-        <v>2025-05-02</v>
+        <v>2024-12-04</v>
       </c>
     </row>
     <row r="432" spans="1:18">
@@ -30629,7 +30629,7 @@
       </c>
       <c r="R432" t="str">
         <f ca="1" t="shared" si="42"/>
-        <v>2024-09-26</v>
+        <v>2025-06-17</v>
       </c>
     </row>
     <row r="433" spans="1:18">
@@ -30686,8 +30686,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R433" t="str">
-        <f ca="1" t="shared" ref="R433:R442" si="43">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-01-26</v>
+        <f ca="1" t="shared" ref="R433:R442" si="43">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-02-24</v>
       </c>
     </row>
     <row r="434" spans="1:18">
@@ -30741,7 +30741,7 @@
       </c>
       <c r="R434" t="str">
         <f ca="1" t="shared" si="43"/>
-        <v>2025-05-02</v>
+        <v>2025-09-30</v>
       </c>
     </row>
     <row r="435" spans="1:18">
@@ -30799,7 +30799,7 @@
       </c>
       <c r="R435" t="str">
         <f ca="1" t="shared" si="43"/>
-        <v>2025-02-23</v>
+        <v>2024-09-23</v>
       </c>
     </row>
     <row r="436" spans="1:18">
@@ -30853,7 +30853,7 @@
       </c>
       <c r="R436" t="str">
         <f ca="1" t="shared" si="43"/>
-        <v>2025-05-17</v>
+        <v>2025-04-08</v>
       </c>
     </row>
     <row r="437" spans="1:18">
@@ -30911,7 +30911,7 @@
       </c>
       <c r="R437" t="str">
         <f ca="1" t="shared" si="43"/>
-        <v>2025-02-27</v>
+        <v>2025-03-12</v>
       </c>
     </row>
     <row r="438" spans="1:18">
@@ -30969,7 +30969,7 @@
       </c>
       <c r="R438" t="str">
         <f ca="1" t="shared" si="43"/>
-        <v>2025-03-09</v>
+        <v>2025-05-31</v>
       </c>
     </row>
     <row r="439" spans="1:18">
@@ -31023,7 +31023,7 @@
       </c>
       <c r="R439" t="str">
         <f ca="1" t="shared" si="43"/>
-        <v>2025-08-14</v>
+        <v>2025-08-17</v>
       </c>
     </row>
     <row r="440" spans="1:18">
@@ -31081,7 +31081,7 @@
       </c>
       <c r="R440" t="str">
         <f ca="1" t="shared" si="43"/>
-        <v>2024-12-18</v>
+        <v>2024-08-02</v>
       </c>
     </row>
     <row r="441" spans="1:18">
@@ -31135,7 +31135,7 @@
       </c>
       <c r="R441" t="str">
         <f ca="1" t="shared" si="43"/>
-        <v>2025-04-18</v>
+        <v>2025-08-15</v>
       </c>
     </row>
     <row r="442" spans="1:18">
@@ -31193,7 +31193,7 @@
       </c>
       <c r="R442" t="str">
         <f ca="1" t="shared" si="43"/>
-        <v>2025-01-11</v>
+        <v>2025-07-31</v>
       </c>
     </row>
     <row r="443" spans="1:18">
@@ -31250,8 +31250,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R443" t="str">
-        <f ca="1" t="shared" ref="R443:R452" si="44">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-03-29</v>
+        <f ca="1" t="shared" ref="R443:R452" si="44">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-02-12</v>
       </c>
     </row>
     <row r="444" spans="1:18">
@@ -31309,7 +31309,7 @@
       </c>
       <c r="R444" t="str">
         <f ca="1" t="shared" si="44"/>
-        <v>2025-08-22</v>
+        <v>2024-11-17</v>
       </c>
     </row>
     <row r="445" spans="1:18">
@@ -31367,7 +31367,7 @@
       </c>
       <c r="R445" t="str">
         <f ca="1" t="shared" si="44"/>
-        <v>2024-09-24</v>
+        <v>2025-05-19</v>
       </c>
     </row>
     <row r="446" spans="1:18">
@@ -31425,7 +31425,7 @@
       </c>
       <c r="R446" t="str">
         <f ca="1" t="shared" si="44"/>
-        <v>2024-09-11</v>
+        <v>2025-08-15</v>
       </c>
     </row>
     <row r="447" spans="1:18">
@@ -31479,7 +31479,7 @@
       </c>
       <c r="R447" t="str">
         <f ca="1" t="shared" si="44"/>
-        <v>2024-08-07</v>
+        <v>2024-12-14</v>
       </c>
     </row>
     <row r="448" spans="1:18">
@@ -31537,7 +31537,7 @@
       </c>
       <c r="R448" t="str">
         <f ca="1" t="shared" si="44"/>
-        <v>2024-11-18</v>
+        <v>2025-01-06</v>
       </c>
     </row>
     <row r="449" spans="1:18">
@@ -31595,7 +31595,7 @@
       </c>
       <c r="R449" t="str">
         <f ca="1" t="shared" si="44"/>
-        <v>2025-08-19</v>
+        <v>2024-11-23</v>
       </c>
     </row>
     <row r="450" spans="1:18">
@@ -31653,7 +31653,7 @@
       </c>
       <c r="R450" t="str">
         <f ca="1" t="shared" si="44"/>
-        <v>2025-09-16</v>
+        <v>2025-09-25</v>
       </c>
     </row>
     <row r="451" spans="1:18">
@@ -31711,7 +31711,7 @@
       </c>
       <c r="R451" t="str">
         <f ca="1" t="shared" si="44"/>
-        <v>2024-10-21</v>
+        <v>2025-10-09</v>
       </c>
     </row>
     <row r="452" spans="1:18">
@@ -31769,7 +31769,7 @@
       </c>
       <c r="R452" t="str">
         <f ca="1" t="shared" si="44"/>
-        <v>2024-08-17</v>
+        <v>2025-09-16</v>
       </c>
     </row>
     <row r="453" spans="1:18">
@@ -31826,8 +31826,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R453" t="str">
-        <f ca="1" t="shared" ref="R453:R462" si="45">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-11-15</v>
+        <f ca="1" t="shared" ref="R453:R462" si="45">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-02-14</v>
       </c>
     </row>
     <row r="454" spans="1:18">
@@ -31885,7 +31885,7 @@
       </c>
       <c r="R454" t="str">
         <f ca="1" t="shared" si="45"/>
-        <v>2025-03-22</v>
+        <v>2025-06-22</v>
       </c>
     </row>
     <row r="455" spans="1:18">
@@ -31943,7 +31943,7 @@
       </c>
       <c r="R455" t="str">
         <f ca="1" t="shared" si="45"/>
-        <v>2024-11-01</v>
+        <v>2025-07-22</v>
       </c>
     </row>
     <row r="456" spans="1:18">
@@ -32001,7 +32001,7 @@
       </c>
       <c r="R456" t="str">
         <f ca="1" t="shared" si="45"/>
-        <v>2025-09-03</v>
+        <v>2025-11-28</v>
       </c>
     </row>
     <row r="457" spans="1:18">
@@ -32059,7 +32059,7 @@
       </c>
       <c r="R457" t="str">
         <f ca="1" t="shared" si="45"/>
-        <v>2024-11-21</v>
+        <v>2025-06-05</v>
       </c>
     </row>
     <row r="458" spans="1:18">
@@ -32117,7 +32117,7 @@
       </c>
       <c r="R458" t="str">
         <f ca="1" t="shared" si="45"/>
-        <v>2025-01-14</v>
+        <v>2024-12-29</v>
       </c>
     </row>
     <row r="459" spans="1:18">
@@ -32175,7 +32175,7 @@
       </c>
       <c r="R459" t="str">
         <f ca="1" t="shared" si="45"/>
-        <v>2024-08-30</v>
+        <v>2025-01-11</v>
       </c>
     </row>
     <row r="460" spans="1:18">
@@ -32233,7 +32233,7 @@
       </c>
       <c r="R460" t="str">
         <f ca="1" t="shared" si="45"/>
-        <v>2025-02-20</v>
+        <v>2025-08-19</v>
       </c>
     </row>
     <row r="461" spans="1:18">
@@ -32291,7 +32291,7 @@
       </c>
       <c r="R461" t="str">
         <f ca="1" t="shared" si="45"/>
-        <v>2024-09-15</v>
+        <v>2025-04-24</v>
       </c>
     </row>
     <row r="462" spans="1:18">
@@ -32345,7 +32345,7 @@
       </c>
       <c r="R462" t="str">
         <f ca="1" t="shared" si="45"/>
-        <v>2025-02-03</v>
+        <v>2025-02-24</v>
       </c>
     </row>
     <row r="463" spans="1:18">
@@ -32398,8 +32398,8 @@
         <v>33</v>
       </c>
       <c r="R463" t="str">
-        <f ca="1" t="shared" ref="R463:R472" si="46">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-09-01</v>
+        <f ca="1" t="shared" ref="R463:R472" si="46">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2024-09-17</v>
       </c>
     </row>
     <row r="464" spans="1:18">
@@ -32457,7 +32457,7 @@
       </c>
       <c r="R464" t="str">
         <f ca="1" t="shared" si="46"/>
-        <v>2025-01-22</v>
+        <v>2025-05-17</v>
       </c>
     </row>
     <row r="465" spans="1:18">
@@ -32511,7 +32511,7 @@
       </c>
       <c r="R465" t="str">
         <f ca="1" t="shared" si="46"/>
-        <v>2024-08-25</v>
+        <v>2025-09-14</v>
       </c>
     </row>
     <row r="466" spans="1:18">
@@ -32569,7 +32569,7 @@
       </c>
       <c r="R466" t="str">
         <f ca="1" t="shared" si="46"/>
-        <v>2025-06-24</v>
+        <v>2024-10-13</v>
       </c>
     </row>
     <row r="467" spans="1:18">
@@ -32627,7 +32627,7 @@
       </c>
       <c r="R467" t="str">
         <f ca="1" t="shared" si="46"/>
-        <v>2025-07-08</v>
+        <v>2025-07-27</v>
       </c>
     </row>
     <row r="468" spans="1:18">
@@ -32685,7 +32685,7 @@
       </c>
       <c r="R468" t="str">
         <f ca="1" t="shared" si="46"/>
-        <v>2025-07-28</v>
+        <v>2025-07-01</v>
       </c>
     </row>
     <row r="469" spans="1:18">
@@ -32743,7 +32743,7 @@
       </c>
       <c r="R469" t="str">
         <f ca="1" t="shared" si="46"/>
-        <v>2025-09-09</v>
+        <v>2025-09-26</v>
       </c>
     </row>
     <row r="470" spans="1:18">
@@ -32801,7 +32801,7 @@
       </c>
       <c r="R470" t="str">
         <f ca="1" t="shared" si="46"/>
-        <v>2025-06-02</v>
+        <v>2025-05-30</v>
       </c>
     </row>
     <row r="471" spans="1:18">
@@ -32858,7 +32858,7 @@
       </c>
       <c r="R471" t="str">
         <f ca="1" t="shared" si="46"/>
-        <v>2024-10-22</v>
+        <v>2025-09-16</v>
       </c>
     </row>
     <row r="472" spans="1:18">
@@ -32915,7 +32915,7 @@
       </c>
       <c r="R472" t="str">
         <f ca="1" t="shared" si="46"/>
-        <v>2025-01-03</v>
+        <v>2025-03-06</v>
       </c>
     </row>
     <row r="473" spans="1:18">
@@ -32972,8 +32972,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R473" t="str">
-        <f ca="1" t="shared" ref="R473:R482" si="47">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-07-23</v>
+        <f ca="1" t="shared" ref="R473:R482" si="47">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-03-29</v>
       </c>
     </row>
     <row r="474" spans="1:18">
@@ -33031,7 +33031,7 @@
       </c>
       <c r="R474" t="str">
         <f ca="1" t="shared" si="47"/>
-        <v>2025-06-22</v>
+        <v>2024-12-11</v>
       </c>
     </row>
     <row r="475" spans="1:18">
@@ -33089,7 +33089,7 @@
       </c>
       <c r="R475" t="str">
         <f ca="1" t="shared" si="47"/>
-        <v>2025-01-23</v>
+        <v>2025-04-23</v>
       </c>
     </row>
     <row r="476" spans="1:18">
@@ -33143,7 +33143,7 @@
       </c>
       <c r="R476" t="str">
         <f ca="1" t="shared" si="47"/>
-        <v>2024-08-18</v>
+        <v>2024-11-19</v>
       </c>
     </row>
     <row r="477" spans="1:18">
@@ -33200,7 +33200,7 @@
       </c>
       <c r="R477" t="str">
         <f ca="1" t="shared" si="47"/>
-        <v>2024-09-29</v>
+        <v>2024-09-24</v>
       </c>
     </row>
     <row r="478" spans="1:18">
@@ -33257,7 +33257,7 @@
       </c>
       <c r="R478" t="str">
         <f ca="1" t="shared" si="47"/>
-        <v>2024-08-24</v>
+        <v>2024-09-04</v>
       </c>
     </row>
     <row r="479" spans="1:18">
@@ -33315,7 +33315,7 @@
       </c>
       <c r="R479" t="str">
         <f ca="1" t="shared" si="47"/>
-        <v>2024-09-08</v>
+        <v>2025-10-11</v>
       </c>
     </row>
     <row r="480" spans="1:18">
@@ -33369,7 +33369,7 @@
       </c>
       <c r="R480" t="str">
         <f ca="1" t="shared" si="47"/>
-        <v>2024-12-07</v>
+        <v>2025-07-13</v>
       </c>
     </row>
     <row r="481" spans="1:18">
@@ -33427,7 +33427,7 @@
       </c>
       <c r="R481" t="str">
         <f ca="1" t="shared" si="47"/>
-        <v>2025-07-09</v>
+        <v>2024-10-22</v>
       </c>
     </row>
     <row r="482" spans="1:18">
@@ -33485,7 +33485,7 @@
       </c>
       <c r="R482" t="str">
         <f ca="1" t="shared" si="47"/>
-        <v>2024-09-05</v>
+        <v>2025-01-31</v>
       </c>
     </row>
     <row r="483" spans="1:18">
@@ -33542,8 +33542,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R483" t="str">
-        <f ca="1" t="shared" ref="R483:R492" si="48">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-01-08</v>
+        <f ca="1" t="shared" ref="R483:R492" si="48">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-08-21</v>
       </c>
     </row>
     <row r="484" spans="1:18">
@@ -33597,7 +33597,7 @@
       </c>
       <c r="R484" t="str">
         <f ca="1" t="shared" si="48"/>
-        <v>2025-08-30</v>
+        <v>2025-05-28</v>
       </c>
     </row>
     <row r="485" spans="1:18">
@@ -33651,7 +33651,7 @@
       </c>
       <c r="R485" t="str">
         <f ca="1" t="shared" si="48"/>
-        <v>2025-02-04</v>
+        <v>2024-10-08</v>
       </c>
     </row>
     <row r="486" spans="1:18">
@@ -33709,7 +33709,7 @@
       </c>
       <c r="R486" t="str">
         <f ca="1" t="shared" si="48"/>
-        <v>2025-05-07</v>
+        <v>2025-03-23</v>
       </c>
     </row>
     <row r="487" spans="1:18">
@@ -33763,7 +33763,7 @@
       </c>
       <c r="R487" t="str">
         <f ca="1" t="shared" si="48"/>
-        <v>2025-01-14</v>
+        <v>2024-12-28</v>
       </c>
     </row>
     <row r="488" spans="1:18">
@@ -33821,7 +33821,7 @@
       </c>
       <c r="R488" t="str">
         <f ca="1" t="shared" si="48"/>
-        <v>2024-12-29</v>
+        <v>2024-09-02</v>
       </c>
     </row>
     <row r="489" spans="1:18">
@@ -33879,7 +33879,7 @@
       </c>
       <c r="R489" t="str">
         <f ca="1" t="shared" si="48"/>
-        <v>2025-07-25</v>
+        <v>2025-03-13</v>
       </c>
     </row>
     <row r="490" spans="1:18">
@@ -33937,7 +33937,7 @@
       </c>
       <c r="R490" t="str">
         <f ca="1" t="shared" si="48"/>
-        <v>2025-09-12</v>
+        <v>2025-09-11</v>
       </c>
     </row>
     <row r="491" spans="1:18">
@@ -33991,7 +33991,7 @@
       </c>
       <c r="R491" t="str">
         <f ca="1" t="shared" si="48"/>
-        <v>2025-02-20</v>
+        <v>2025-06-21</v>
       </c>
     </row>
     <row r="492" spans="1:18">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="R492" t="str">
         <f ca="1" t="shared" si="48"/>
-        <v>2024-10-26</v>
+        <v>2024-08-24</v>
       </c>
     </row>
     <row r="493" spans="1:18">
@@ -34100,8 +34100,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R493" t="str">
-        <f ca="1" t="shared" ref="R493:R502" si="49">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-07-06</v>
+        <f ca="1" t="shared" ref="R493:R502" si="49">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-07-21</v>
       </c>
     </row>
     <row r="494" spans="1:18">
@@ -34159,7 +34159,7 @@
       </c>
       <c r="R494" t="str">
         <f ca="1" t="shared" si="49"/>
-        <v>2025-10-02</v>
+        <v>2024-10-07</v>
       </c>
     </row>
     <row r="495" spans="1:18">
@@ -34214,7 +34214,7 @@
       </c>
       <c r="R495" t="str">
         <f ca="1" t="shared" si="49"/>
-        <v>2025-07-10</v>
+        <v>2025-10-20</v>
       </c>
     </row>
     <row r="496" spans="1:18">
@@ -34272,7 +34272,7 @@
       </c>
       <c r="R496" t="str">
         <f ca="1" t="shared" si="49"/>
-        <v>2025-10-02</v>
+        <v>2025-04-06</v>
       </c>
     </row>
     <row r="497" spans="1:18">
@@ -34326,7 +34326,7 @@
       </c>
       <c r="R497" t="str">
         <f ca="1" t="shared" si="49"/>
-        <v>2025-05-31</v>
+        <v>2025-05-03</v>
       </c>
     </row>
     <row r="498" spans="1:18">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="R498" t="str">
         <f ca="1" t="shared" si="49"/>
-        <v>2025-04-03</v>
+        <v>2025-06-27</v>
       </c>
     </row>
     <row r="499" spans="1:18">
@@ -34438,7 +34438,7 @@
       </c>
       <c r="R499" t="str">
         <f ca="1" t="shared" si="49"/>
-        <v>2025-06-05</v>
+        <v>2025-09-12</v>
       </c>
     </row>
     <row r="500" spans="1:18">
@@ -34492,7 +34492,7 @@
       </c>
       <c r="R500" t="str">
         <f ca="1" t="shared" si="49"/>
-        <v>2025-04-26</v>
+        <v>2025-10-10</v>
       </c>
     </row>
     <row r="501" spans="1:18">
@@ -34550,7 +34550,7 @@
       </c>
       <c r="R501" t="str">
         <f ca="1" t="shared" si="49"/>
-        <v>2024-12-04</v>
+        <v>2025-05-31</v>
       </c>
     </row>
     <row r="502" spans="1:18">
@@ -34607,7 +34607,7 @@
       </c>
       <c r="R502" t="str">
         <f ca="1" t="shared" si="49"/>
-        <v>2025-05-06</v>
+        <v>2024-12-16</v>
       </c>
     </row>
     <row r="503" spans="1:18">
@@ -34664,8 +34664,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R503" t="str">
-        <f ca="1" t="shared" ref="R503:R512" si="50">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-02-23</v>
+        <f ca="1" t="shared" ref="R503:R512" si="50">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-04-13</v>
       </c>
     </row>
     <row r="504" spans="1:18">
@@ -34723,7 +34723,7 @@
       </c>
       <c r="R504" t="str">
         <f ca="1" t="shared" si="50"/>
-        <v>2025-09-07</v>
+        <v>2024-08-11</v>
       </c>
     </row>
     <row r="505" spans="1:18">
@@ -34781,7 +34781,7 @@
       </c>
       <c r="R505" t="str">
         <f ca="1" t="shared" si="50"/>
-        <v>2025-07-27</v>
+        <v>2024-08-15</v>
       </c>
     </row>
     <row r="506" spans="1:18">
@@ -34839,7 +34839,7 @@
       </c>
       <c r="R506" t="str">
         <f ca="1" t="shared" si="50"/>
-        <v>2025-06-24</v>
+        <v>2025-02-20</v>
       </c>
     </row>
     <row r="507" spans="1:18">
@@ -34894,7 +34894,7 @@
       </c>
       <c r="R507" t="str">
         <f ca="1" t="shared" si="50"/>
-        <v>2024-09-27</v>
+        <v>2025-03-31</v>
       </c>
     </row>
     <row r="508" spans="1:18">
@@ -34952,7 +34952,7 @@
       </c>
       <c r="R508" t="str">
         <f ca="1" t="shared" si="50"/>
-        <v>2024-11-21</v>
+        <v>2024-10-11</v>
       </c>
     </row>
     <row r="509" spans="1:18">
@@ -35006,7 +35006,7 @@
       </c>
       <c r="R509" t="str">
         <f ca="1" t="shared" si="50"/>
-        <v>2025-03-18</v>
+        <v>2025-08-14</v>
       </c>
     </row>
     <row r="510" spans="1:18">
@@ -35064,7 +35064,7 @@
       </c>
       <c r="R510" t="str">
         <f ca="1" t="shared" si="50"/>
-        <v>2025-03-02</v>
+        <v>2024-10-22</v>
       </c>
     </row>
     <row r="511" spans="1:18">
@@ -35118,7 +35118,7 @@
       </c>
       <c r="R511" t="str">
         <f ca="1" t="shared" si="50"/>
-        <v>2025-01-07</v>
+        <v>2024-12-13</v>
       </c>
     </row>
     <row r="512" spans="1:18">
@@ -35172,7 +35172,7 @@
       </c>
       <c r="R512" t="str">
         <f ca="1" t="shared" si="50"/>
-        <v>2025-08-31</v>
+        <v>2024-12-13</v>
       </c>
     </row>
     <row r="513" spans="1:18">
@@ -35225,8 +35225,8 @@
         <v>33</v>
       </c>
       <c r="R513" t="str">
-        <f ca="1" t="shared" ref="R513:R522" si="51">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-09-29</v>
+        <f ca="1" t="shared" ref="R513:R522" si="51">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2024-12-24</v>
       </c>
     </row>
     <row r="514" spans="1:18">
@@ -35280,7 +35280,7 @@
       </c>
       <c r="R514" t="str">
         <f ca="1" t="shared" si="51"/>
-        <v>2025-02-11</v>
+        <v>2024-10-23</v>
       </c>
     </row>
     <row r="515" spans="1:18">
@@ -35334,7 +35334,7 @@
       </c>
       <c r="R515" t="str">
         <f ca="1" t="shared" si="51"/>
-        <v>2024-12-19</v>
+        <v>2025-06-21</v>
       </c>
     </row>
     <row r="516" spans="1:18">
@@ -35392,7 +35392,7 @@
       </c>
       <c r="R516" t="str">
         <f ca="1" t="shared" si="51"/>
-        <v>2025-07-18</v>
+        <v>2025-07-10</v>
       </c>
     </row>
     <row r="517" spans="1:18">
@@ -35446,7 +35446,7 @@
       </c>
       <c r="R517" t="str">
         <f ca="1" t="shared" si="51"/>
-        <v>2024-11-08</v>
+        <v>2024-09-08</v>
       </c>
     </row>
     <row r="518" spans="1:18">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="R518" t="str">
         <f ca="1" t="shared" si="51"/>
-        <v>2024-10-15</v>
+        <v>2025-04-07</v>
       </c>
     </row>
     <row r="519" spans="1:18">
@@ -35562,7 +35562,7 @@
       </c>
       <c r="R519" t="str">
         <f ca="1" t="shared" si="51"/>
-        <v>2025-05-31</v>
+        <v>2025-04-17</v>
       </c>
     </row>
     <row r="520" spans="1:18">
@@ -35616,7 +35616,7 @@
       </c>
       <c r="R520" t="str">
         <f ca="1" t="shared" si="51"/>
-        <v>2024-08-27</v>
+        <v>2025-09-23</v>
       </c>
     </row>
     <row r="521" spans="1:18">
@@ -35673,7 +35673,7 @@
       </c>
       <c r="R521" t="str">
         <f ca="1" t="shared" si="51"/>
-        <v>2025-04-16</v>
+        <v>2025-08-10</v>
       </c>
     </row>
     <row r="522" spans="1:18">
@@ -35727,7 +35727,7 @@
       </c>
       <c r="R522" t="str">
         <f ca="1" t="shared" si="51"/>
-        <v>2024-10-03</v>
+        <v>2024-09-01</v>
       </c>
     </row>
     <row r="523" spans="1:18">
@@ -35780,8 +35780,8 @@
         <v>33</v>
       </c>
       <c r="R523" t="str">
-        <f ca="1" t="shared" ref="R523:R532" si="52">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-12-29</v>
+        <f ca="1" t="shared" ref="R523:R532" si="52">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2024-11-04</v>
       </c>
     </row>
     <row r="524" spans="1:18">
@@ -35838,7 +35838,7 @@
       </c>
       <c r="R524" t="str">
         <f ca="1" t="shared" si="52"/>
-        <v>2025-08-28</v>
+        <v>2025-04-13</v>
       </c>
     </row>
     <row r="525" spans="1:18">
@@ -35892,7 +35892,7 @@
       </c>
       <c r="R525" t="str">
         <f ca="1" t="shared" si="52"/>
-        <v>2025-10-07</v>
+        <v>2025-04-27</v>
       </c>
     </row>
     <row r="526" spans="1:18">
@@ -35950,7 +35950,7 @@
       </c>
       <c r="R526" t="str">
         <f ca="1" t="shared" si="52"/>
-        <v>2025-03-13</v>
+        <v>2025-02-04</v>
       </c>
     </row>
     <row r="527" spans="1:18">
@@ -36008,7 +36008,7 @@
       </c>
       <c r="R527" t="str">
         <f ca="1" t="shared" si="52"/>
-        <v>2025-03-14</v>
+        <v>2024-08-04</v>
       </c>
     </row>
     <row r="528" spans="1:18">
@@ -36065,7 +36065,7 @@
       </c>
       <c r="R528" t="str">
         <f ca="1" t="shared" si="52"/>
-        <v>2025-01-06</v>
+        <v>2025-04-21</v>
       </c>
     </row>
     <row r="529" spans="1:18">
@@ -36119,7 +36119,7 @@
       </c>
       <c r="R529" t="str">
         <f ca="1" t="shared" si="52"/>
-        <v>2024-09-13</v>
+        <v>2024-09-08</v>
       </c>
     </row>
     <row r="530" spans="1:18">
@@ -36176,7 +36176,7 @@
       </c>
       <c r="R530" t="str">
         <f ca="1" t="shared" si="52"/>
-        <v>2025-09-24</v>
+        <v>2024-08-12</v>
       </c>
     </row>
     <row r="531" spans="1:18">
@@ -36234,7 +36234,7 @@
       </c>
       <c r="R531" t="str">
         <f ca="1" t="shared" si="52"/>
-        <v>2024-08-06</v>
+        <v>2025-10-23</v>
       </c>
     </row>
     <row r="532" spans="1:18">
@@ -36292,7 +36292,7 @@
       </c>
       <c r="R532" t="str">
         <f ca="1" t="shared" si="52"/>
-        <v>2025-08-20</v>
+        <v>2025-04-21</v>
       </c>
     </row>
     <row r="533" spans="1:18">
@@ -36349,8 +36349,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R533" t="str">
-        <f ca="1" t="shared" ref="R533:R542" si="53">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-12-02</v>
+        <f ca="1" t="shared" ref="R533:R542" si="53">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-08-14</v>
       </c>
     </row>
     <row r="534" spans="1:18">
@@ -36408,7 +36408,7 @@
       </c>
       <c r="R534" t="str">
         <f ca="1" t="shared" si="53"/>
-        <v>2025-07-29</v>
+        <v>2025-10-24</v>
       </c>
     </row>
     <row r="535" spans="1:18">
@@ -36462,7 +36462,7 @@
       </c>
       <c r="R535" t="str">
         <f ca="1" t="shared" si="53"/>
-        <v>2024-09-18</v>
+        <v>2025-01-05</v>
       </c>
     </row>
     <row r="536" spans="1:18">
@@ -36520,7 +36520,7 @@
       </c>
       <c r="R536" t="str">
         <f ca="1" t="shared" si="53"/>
-        <v>2025-03-29</v>
+        <v>2024-09-25</v>
       </c>
     </row>
     <row r="537" spans="1:18">
@@ -36574,7 +36574,7 @@
       </c>
       <c r="R537" t="str">
         <f ca="1" t="shared" si="53"/>
-        <v>2025-02-01</v>
+        <v>2025-05-19</v>
       </c>
     </row>
     <row r="538" spans="1:18">
@@ -36631,7 +36631,7 @@
       </c>
       <c r="R538" t="str">
         <f ca="1" t="shared" si="53"/>
-        <v>2024-08-04</v>
+        <v>2025-06-12</v>
       </c>
     </row>
     <row r="539" spans="1:18">
@@ -36685,7 +36685,7 @@
       </c>
       <c r="R539" t="str">
         <f ca="1" t="shared" si="53"/>
-        <v>2025-08-31</v>
+        <v>2025-02-14</v>
       </c>
     </row>
     <row r="540" spans="1:18">
@@ -36743,7 +36743,7 @@
       </c>
       <c r="R540" t="str">
         <f ca="1" t="shared" si="53"/>
-        <v>2025-09-20</v>
+        <v>2025-02-27</v>
       </c>
     </row>
     <row r="541" spans="1:18">
@@ -36801,7 +36801,7 @@
       </c>
       <c r="R541" t="str">
         <f ca="1" t="shared" si="53"/>
-        <v>2024-11-27</v>
+        <v>2025-10-11</v>
       </c>
     </row>
     <row r="542" spans="1:18">
@@ -36859,7 +36859,7 @@
       </c>
       <c r="R542" t="str">
         <f ca="1" t="shared" si="53"/>
-        <v>2025-06-07</v>
+        <v>2025-03-15</v>
       </c>
     </row>
     <row r="543" spans="1:18">
@@ -36912,8 +36912,8 @@
         <v>33</v>
       </c>
       <c r="R543" t="str">
-        <f ca="1" t="shared" ref="R543:R552" si="54">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-08-18</v>
+        <f ca="1" t="shared" ref="R543:R552" si="54">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2024-09-23</v>
       </c>
     </row>
     <row r="544" spans="1:18">
@@ -36971,7 +36971,7 @@
       </c>
       <c r="R544" t="str">
         <f ca="1" t="shared" si="54"/>
-        <v>2025-01-29</v>
+        <v>2025-07-18</v>
       </c>
     </row>
     <row r="545" spans="1:18">
@@ -37025,7 +37025,7 @@
       </c>
       <c r="R545" t="str">
         <f ca="1" t="shared" si="54"/>
-        <v>2024-11-09</v>
+        <v>2025-09-29</v>
       </c>
     </row>
     <row r="546" spans="1:18">
@@ -37083,7 +37083,7 @@
       </c>
       <c r="R546" t="str">
         <f ca="1" t="shared" si="54"/>
-        <v>2024-12-20</v>
+        <v>2024-09-01</v>
       </c>
     </row>
     <row r="547" spans="1:18">
@@ -37137,7 +37137,7 @@
       </c>
       <c r="R547" t="str">
         <f ca="1" t="shared" si="54"/>
-        <v>2024-08-29</v>
+        <v>2024-12-25</v>
       </c>
     </row>
     <row r="548" spans="1:18">
@@ -37195,7 +37195,7 @@
       </c>
       <c r="R548" t="str">
         <f ca="1" t="shared" si="54"/>
-        <v>2025-02-21</v>
+        <v>2025-10-20</v>
       </c>
     </row>
     <row r="549" spans="1:18">
@@ -37249,7 +37249,7 @@
       </c>
       <c r="R549" t="str">
         <f ca="1" t="shared" si="54"/>
-        <v>2024-11-26</v>
+        <v>2025-06-28</v>
       </c>
     </row>
     <row r="550" spans="1:18">
@@ -37303,7 +37303,7 @@
       </c>
       <c r="R550" t="str">
         <f ca="1" t="shared" si="54"/>
-        <v>2024-08-26</v>
+        <v>2025-04-27</v>
       </c>
     </row>
     <row r="551" spans="1:18">
@@ -37360,7 +37360,7 @@
       </c>
       <c r="R551" t="str">
         <f ca="1" t="shared" si="54"/>
-        <v>2025-03-29</v>
+        <v>2025-05-25</v>
       </c>
     </row>
     <row r="552" spans="1:18">
@@ -37414,7 +37414,7 @@
       </c>
       <c r="R552" t="str">
         <f ca="1" t="shared" si="54"/>
-        <v>2024-10-13</v>
+        <v>2024-10-19</v>
       </c>
     </row>
     <row r="553" spans="1:18">
@@ -37470,8 +37470,8 @@
         <v>138</v>
       </c>
       <c r="R553" t="str">
-        <f ca="1" t="shared" ref="R553:R562" si="55">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-04-21</v>
+        <f ca="1" t="shared" ref="R553:R562" si="55">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2024-09-17</v>
       </c>
     </row>
     <row r="554" spans="1:18">
@@ -37529,7 +37529,7 @@
       </c>
       <c r="R554" t="str">
         <f ca="1" t="shared" si="55"/>
-        <v>2025-03-23</v>
+        <v>2025-05-16</v>
       </c>
     </row>
     <row r="555" spans="1:18">
@@ -37587,7 +37587,7 @@
       </c>
       <c r="R555" t="str">
         <f ca="1" t="shared" si="55"/>
-        <v>2025-10-04</v>
+        <v>2025-05-17</v>
       </c>
     </row>
     <row r="556" spans="1:18">
@@ -37645,7 +37645,7 @@
       </c>
       <c r="R556" t="str">
         <f ca="1" t="shared" si="55"/>
-        <v>2025-03-09</v>
+        <v>2025-11-26</v>
       </c>
     </row>
     <row r="557" spans="1:18">
@@ -37703,7 +37703,7 @@
       </c>
       <c r="R557" t="str">
         <f ca="1" t="shared" si="55"/>
-        <v>2024-12-17</v>
+        <v>2025-10-28</v>
       </c>
     </row>
     <row r="558" spans="1:18">
@@ -37761,7 +37761,7 @@
       </c>
       <c r="R558" t="str">
         <f ca="1" t="shared" si="55"/>
-        <v>2024-11-04</v>
+        <v>2025-03-03</v>
       </c>
     </row>
     <row r="559" spans="1:18">
@@ -37819,7 +37819,7 @@
       </c>
       <c r="R559" t="str">
         <f ca="1" t="shared" si="55"/>
-        <v>2025-04-18</v>
+        <v>2024-12-08</v>
       </c>
     </row>
     <row r="560" spans="1:18">
@@ -37877,7 +37877,7 @@
       </c>
       <c r="R560" t="str">
         <f ca="1" t="shared" si="55"/>
-        <v>2025-08-21</v>
+        <v>2024-10-07</v>
       </c>
     </row>
     <row r="561" spans="1:18">
@@ -37935,7 +37935,7 @@
       </c>
       <c r="R561" t="str">
         <f ca="1" t="shared" si="55"/>
-        <v>2025-01-22</v>
+        <v>2025-11-16</v>
       </c>
     </row>
     <row r="562" spans="1:18">
@@ -37993,7 +37993,7 @@
       </c>
       <c r="R562" t="str">
         <f ca="1" t="shared" si="55"/>
-        <v>2024-08-03</v>
+        <v>2025-01-20</v>
       </c>
     </row>
     <row r="563" spans="1:18">
@@ -38050,8 +38050,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R563" t="str">
-        <f ca="1" t="shared" ref="R563:R572" si="56">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-04-12</v>
+        <f ca="1" t="shared" ref="R563:R572" si="56">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2024-12-17</v>
       </c>
     </row>
     <row r="564" spans="1:18">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="R564" t="str">
         <f ca="1" t="shared" si="56"/>
-        <v>2024-10-26</v>
+        <v>2025-06-25</v>
       </c>
     </row>
     <row r="565" spans="1:18">
@@ -38167,7 +38167,7 @@
       </c>
       <c r="R565" t="str">
         <f ca="1" t="shared" si="56"/>
-        <v>2024-08-31</v>
+        <v>2024-12-22</v>
       </c>
     </row>
     <row r="566" spans="1:18">
@@ -38221,7 +38221,7 @@
       </c>
       <c r="R566" t="str">
         <f ca="1" t="shared" si="56"/>
-        <v>2024-08-11</v>
+        <v>2025-01-26</v>
       </c>
     </row>
     <row r="567" spans="1:18">
@@ -38279,7 +38279,7 @@
       </c>
       <c r="R567" t="str">
         <f ca="1" t="shared" si="56"/>
-        <v>2025-06-28</v>
+        <v>2025-07-04</v>
       </c>
     </row>
     <row r="568" spans="1:18">
@@ -38337,7 +38337,7 @@
       </c>
       <c r="R568" t="str">
         <f ca="1" t="shared" si="56"/>
-        <v>2025-04-16</v>
+        <v>2025-06-21</v>
       </c>
     </row>
     <row r="569" spans="1:18">
@@ -38395,7 +38395,7 @@
       </c>
       <c r="R569" t="str">
         <f ca="1" t="shared" si="56"/>
-        <v>2025-07-24</v>
+        <v>2025-11-15</v>
       </c>
     </row>
     <row r="570" spans="1:18">
@@ -38453,7 +38453,7 @@
       </c>
       <c r="R570" t="str">
         <f ca="1" t="shared" si="56"/>
-        <v>2025-06-20</v>
+        <v>2025-02-16</v>
       </c>
     </row>
     <row r="571" spans="1:18">
@@ -38507,7 +38507,7 @@
       </c>
       <c r="R571" t="str">
         <f ca="1" t="shared" si="56"/>
-        <v>2025-05-02</v>
+        <v>2025-10-24</v>
       </c>
     </row>
     <row r="572" spans="1:18">
@@ -38565,7 +38565,7 @@
       </c>
       <c r="R572" t="str">
         <f ca="1" t="shared" si="56"/>
-        <v>2025-04-16</v>
+        <v>2025-09-11</v>
       </c>
     </row>
     <row r="573" spans="1:18">
@@ -38618,8 +38618,8 @@
         <v>33</v>
       </c>
       <c r="R573" t="str">
-        <f ca="1" t="shared" ref="R573:R582" si="57">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-05-28</v>
+        <f ca="1" t="shared" ref="R573:R582" si="57">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2024-08-22</v>
       </c>
     </row>
     <row r="574" spans="1:18">
@@ -38677,7 +38677,7 @@
       </c>
       <c r="R574" t="str">
         <f ca="1" t="shared" si="57"/>
-        <v>2024-09-15</v>
+        <v>2025-11-01</v>
       </c>
     </row>
     <row r="575" spans="1:18">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="R575" t="str">
         <f ca="1" t="shared" si="57"/>
-        <v>2025-04-11</v>
+        <v>2024-09-27</v>
       </c>
     </row>
     <row r="576" spans="1:18">
@@ -38793,7 +38793,7 @@
       </c>
       <c r="R576" t="str">
         <f ca="1" t="shared" si="57"/>
-        <v>2024-09-13</v>
+        <v>2025-08-26</v>
       </c>
     </row>
     <row r="577" spans="1:18">
@@ -38851,7 +38851,7 @@
       </c>
       <c r="R577" t="str">
         <f ca="1" t="shared" si="57"/>
-        <v>2025-09-22</v>
+        <v>2025-01-16</v>
       </c>
     </row>
     <row r="578" spans="1:18">
@@ -38909,7 +38909,7 @@
       </c>
       <c r="R578" t="str">
         <f ca="1" t="shared" si="57"/>
-        <v>2025-03-11</v>
+        <v>2024-12-10</v>
       </c>
     </row>
     <row r="579" spans="1:18">
@@ -38963,7 +38963,7 @@
       </c>
       <c r="R579" t="str">
         <f ca="1" t="shared" si="57"/>
-        <v>2024-09-14</v>
+        <v>2025-03-08</v>
       </c>
     </row>
     <row r="580" spans="1:18">
@@ -39020,7 +39020,7 @@
       </c>
       <c r="R580" t="str">
         <f ca="1" t="shared" si="57"/>
-        <v>2025-08-22</v>
+        <v>2025-09-21</v>
       </c>
     </row>
     <row r="581" spans="1:18">
@@ -39078,7 +39078,7 @@
       </c>
       <c r="R581" t="str">
         <f ca="1" t="shared" si="57"/>
-        <v>2025-01-13</v>
+        <v>2024-10-13</v>
       </c>
     </row>
     <row r="582" spans="1:18">
@@ -39133,7 +39133,7 @@
       </c>
       <c r="R582" t="str">
         <f ca="1" t="shared" si="57"/>
-        <v>2025-10-06</v>
+        <v>2025-03-01</v>
       </c>
     </row>
     <row r="583" spans="1:18">
@@ -39190,8 +39190,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R583" t="str">
-        <f ca="1" t="shared" ref="R583:R592" si="58">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-08-25</v>
+        <f ca="1" t="shared" ref="R583:R592" si="58">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-06-11</v>
       </c>
     </row>
     <row r="584" spans="1:18">
@@ -39248,7 +39248,7 @@
       </c>
       <c r="R584" t="str">
         <f ca="1" t="shared" si="58"/>
-        <v>2024-09-01</v>
+        <v>2025-08-17</v>
       </c>
     </row>
     <row r="585" spans="1:18">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="R585" t="str">
         <f ca="1" t="shared" si="58"/>
-        <v>2025-07-17</v>
+        <v>2025-02-26</v>
       </c>
     </row>
     <row r="586" spans="1:18">
@@ -39364,7 +39364,7 @@
       </c>
       <c r="R586" t="str">
         <f ca="1" t="shared" si="58"/>
-        <v>2024-10-10</v>
+        <v>2025-10-20</v>
       </c>
     </row>
     <row r="587" spans="1:18">
@@ -39422,7 +39422,7 @@
       </c>
       <c r="R587" t="str">
         <f ca="1" t="shared" si="58"/>
-        <v>2025-05-31</v>
+        <v>2024-12-25</v>
       </c>
     </row>
     <row r="588" spans="1:18">
@@ -39476,7 +39476,7 @@
       </c>
       <c r="R588" t="str">
         <f ca="1" t="shared" si="58"/>
-        <v>2024-10-31</v>
+        <v>2024-09-11</v>
       </c>
     </row>
     <row r="589" spans="1:18">
@@ -39534,7 +39534,7 @@
       </c>
       <c r="R589" t="str">
         <f ca="1" t="shared" si="58"/>
-        <v>2024-08-13</v>
+        <v>2025-09-24</v>
       </c>
     </row>
     <row r="590" spans="1:18">
@@ -39588,7 +39588,7 @@
       </c>
       <c r="R590" t="str">
         <f ca="1" t="shared" si="58"/>
-        <v>2025-03-07</v>
+        <v>2025-10-26</v>
       </c>
     </row>
     <row r="591" spans="1:18">
@@ -39646,7 +39646,7 @@
       </c>
       <c r="R591" t="str">
         <f ca="1" t="shared" si="58"/>
-        <v>2025-02-18</v>
+        <v>2024-09-07</v>
       </c>
     </row>
     <row r="592" spans="1:18">
@@ -39704,7 +39704,7 @@
       </c>
       <c r="R592" t="str">
         <f ca="1" t="shared" si="58"/>
-        <v>2024-11-13</v>
+        <v>2025-09-11</v>
       </c>
     </row>
     <row r="593" spans="1:18">
@@ -39761,8 +39761,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R593" t="str">
-        <f ca="1" t="shared" ref="R593:R602" si="59">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-04-13</v>
+        <f ca="1" t="shared" ref="R593:R602" si="59">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-05-13</v>
       </c>
     </row>
     <row r="594" spans="1:18">
@@ -39816,7 +39816,7 @@
       </c>
       <c r="R594" t="str">
         <f ca="1" t="shared" si="59"/>
-        <v>2025-02-27</v>
+        <v>2025-06-07</v>
       </c>
     </row>
     <row r="595" spans="1:18">
@@ -39871,7 +39871,7 @@
       </c>
       <c r="R595" t="str">
         <f ca="1" t="shared" si="59"/>
-        <v>2024-10-12</v>
+        <v>2025-11-26</v>
       </c>
     </row>
     <row r="596" spans="1:18">
@@ -39929,7 +39929,7 @@
       </c>
       <c r="R596" t="str">
         <f ca="1" t="shared" si="59"/>
-        <v>2025-03-14</v>
+        <v>2025-03-20</v>
       </c>
     </row>
     <row r="597" spans="1:18">
@@ -39983,7 +39983,7 @@
       </c>
       <c r="R597" t="str">
         <f ca="1" t="shared" si="59"/>
-        <v>2024-09-03</v>
+        <v>2025-05-21</v>
       </c>
     </row>
     <row r="598" spans="1:18">
@@ -40040,7 +40040,7 @@
       </c>
       <c r="R598" t="str">
         <f ca="1" t="shared" si="59"/>
-        <v>2025-04-07</v>
+        <v>2025-08-18</v>
       </c>
     </row>
     <row r="599" spans="1:18">
@@ -40094,7 +40094,7 @@
       </c>
       <c r="R599" t="str">
         <f ca="1" t="shared" si="59"/>
-        <v>2025-07-24</v>
+        <v>2025-02-14</v>
       </c>
     </row>
     <row r="600" spans="1:18">
@@ -40148,7 +40148,7 @@
       </c>
       <c r="R600" t="str">
         <f ca="1" t="shared" si="59"/>
-        <v>2025-05-13</v>
+        <v>2025-06-17</v>
       </c>
     </row>
     <row r="601" spans="1:18">
@@ -40202,7 +40202,7 @@
       </c>
       <c r="R601" t="str">
         <f ca="1" t="shared" si="59"/>
-        <v>2025-03-22</v>
+        <v>2024-12-16</v>
       </c>
     </row>
     <row r="602" spans="1:18">
@@ -40260,7 +40260,7 @@
       </c>
       <c r="R602" t="str">
         <f ca="1" t="shared" si="59"/>
-        <v>2025-02-10</v>
+        <v>2025-06-17</v>
       </c>
     </row>
     <row r="603" spans="1:18">
@@ -40316,8 +40316,8 @@
         <v>138</v>
       </c>
       <c r="R603" t="str">
-        <f ca="1" t="shared" ref="R603:R612" si="60">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-06-28</v>
+        <f ca="1" t="shared" ref="R603:R612" si="60">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-07-26</v>
       </c>
     </row>
     <row r="604" spans="1:18">
@@ -40375,7 +40375,7 @@
       </c>
       <c r="R604" t="str">
         <f ca="1" t="shared" si="60"/>
-        <v>2025-10-07</v>
+        <v>2025-11-28</v>
       </c>
     </row>
     <row r="605" spans="1:18">
@@ -40429,7 +40429,7 @@
       </c>
       <c r="R605" t="str">
         <f ca="1" t="shared" si="60"/>
-        <v>2024-12-14</v>
+        <v>2025-10-08</v>
       </c>
     </row>
     <row r="606" spans="1:18">
@@ -40486,7 +40486,7 @@
       </c>
       <c r="R606" t="str">
         <f ca="1" t="shared" si="60"/>
-        <v>2024-09-27</v>
+        <v>2025-07-07</v>
       </c>
     </row>
     <row r="607" spans="1:18">
@@ -40544,7 +40544,7 @@
       </c>
       <c r="R607" t="str">
         <f ca="1" t="shared" si="60"/>
-        <v>2025-07-07</v>
+        <v>2024-11-27</v>
       </c>
     </row>
     <row r="608" spans="1:18">
@@ -40598,7 +40598,7 @@
       </c>
       <c r="R608" t="str">
         <f ca="1" t="shared" si="60"/>
-        <v>2025-01-18</v>
+        <v>2025-06-07</v>
       </c>
     </row>
     <row r="609" spans="1:18">
@@ -40656,7 +40656,7 @@
       </c>
       <c r="R609" t="str">
         <f ca="1" t="shared" si="60"/>
-        <v>2024-09-20</v>
+        <v>2025-04-12</v>
       </c>
     </row>
     <row r="610" spans="1:18">
@@ -40714,7 +40714,7 @@
       </c>
       <c r="R610" t="str">
         <f ca="1" t="shared" si="60"/>
-        <v>2025-07-07</v>
+        <v>2025-05-27</v>
       </c>
     </row>
     <row r="611" spans="1:18">
@@ -40769,7 +40769,7 @@
       </c>
       <c r="R611" t="str">
         <f ca="1" t="shared" si="60"/>
-        <v>2024-08-02</v>
+        <v>2025-02-28</v>
       </c>
     </row>
     <row r="612" spans="1:18">
@@ -40823,7 +40823,7 @@
       </c>
       <c r="R612" t="str">
         <f ca="1" t="shared" si="60"/>
-        <v>2025-07-23</v>
+        <v>2024-09-06</v>
       </c>
     </row>
     <row r="613" spans="1:18">
@@ -40880,8 +40880,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R613" t="str">
-        <f ca="1" t="shared" ref="R613:R622" si="61">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-02-06</v>
+        <f ca="1" t="shared" ref="R613:R622" si="61">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-09-23</v>
       </c>
     </row>
     <row r="614" spans="1:18">
@@ -40935,7 +40935,7 @@
       </c>
       <c r="R614" t="str">
         <f ca="1" t="shared" si="61"/>
-        <v>2024-12-10</v>
+        <v>2025-08-16</v>
       </c>
     </row>
     <row r="615" spans="1:18">
@@ -40992,7 +40992,7 @@
       </c>
       <c r="R615" t="str">
         <f ca="1" t="shared" si="61"/>
-        <v>2024-12-09</v>
+        <v>2024-12-10</v>
       </c>
     </row>
     <row r="616" spans="1:18">
@@ -41050,7 +41050,7 @@
       </c>
       <c r="R616" t="str">
         <f ca="1" t="shared" si="61"/>
-        <v>2025-05-13</v>
+        <v>2024-11-16</v>
       </c>
     </row>
     <row r="617" spans="1:18">
@@ -41108,7 +41108,7 @@
       </c>
       <c r="R617" t="str">
         <f ca="1" t="shared" si="61"/>
-        <v>2025-07-23</v>
+        <v>2025-04-28</v>
       </c>
     </row>
     <row r="618" spans="1:18">
@@ -41166,7 +41166,7 @@
       </c>
       <c r="R618" t="str">
         <f ca="1" t="shared" si="61"/>
-        <v>2025-05-15</v>
+        <v>2025-08-11</v>
       </c>
     </row>
     <row r="619" spans="1:18">
@@ -41223,7 +41223,7 @@
       </c>
       <c r="R619" t="str">
         <f ca="1" t="shared" si="61"/>
-        <v>2025-05-04</v>
+        <v>2025-02-26</v>
       </c>
     </row>
     <row r="620" spans="1:18">
@@ -41280,7 +41280,7 @@
       </c>
       <c r="R620" t="str">
         <f ca="1" t="shared" si="61"/>
-        <v>2025-05-22</v>
+        <v>2025-03-02</v>
       </c>
     </row>
     <row r="621" spans="1:18">
@@ -41337,7 +41337,7 @@
       </c>
       <c r="R621" t="str">
         <f ca="1" t="shared" si="61"/>
-        <v>2024-08-07</v>
+        <v>2025-11-12</v>
       </c>
     </row>
     <row r="622" spans="1:18">
@@ -41394,7 +41394,7 @@
       </c>
       <c r="R622" t="str">
         <f ca="1" t="shared" si="61"/>
-        <v>2025-07-29</v>
+        <v>2025-10-29</v>
       </c>
     </row>
     <row r="623" spans="1:18">
@@ -41447,8 +41447,8 @@
         <v>33</v>
       </c>
       <c r="R623" t="str">
-        <f ca="1" t="shared" ref="R623:R632" si="62">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-04-17</v>
+        <f ca="1" t="shared" ref="R623:R632" si="62">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-10-13</v>
       </c>
     </row>
     <row r="624" spans="1:18">
@@ -41506,7 +41506,7 @@
       </c>
       <c r="R624" t="str">
         <f ca="1" t="shared" si="62"/>
-        <v>2025-07-25</v>
+        <v>2024-09-27</v>
       </c>
     </row>
     <row r="625" spans="1:18">
@@ -41560,7 +41560,7 @@
       </c>
       <c r="R625" t="str">
         <f ca="1" t="shared" si="62"/>
-        <v>2025-04-05</v>
+        <v>2025-10-30</v>
       </c>
     </row>
     <row r="626" spans="1:18">
@@ -41618,7 +41618,7 @@
       </c>
       <c r="R626" t="str">
         <f ca="1" t="shared" si="62"/>
-        <v>2024-08-25</v>
+        <v>2025-03-12</v>
       </c>
     </row>
     <row r="627" spans="1:18">
@@ -41676,7 +41676,7 @@
       </c>
       <c r="R627" t="str">
         <f ca="1" t="shared" si="62"/>
-        <v>2024-08-31</v>
+        <v>2025-11-01</v>
       </c>
     </row>
     <row r="628" spans="1:18">
@@ -41731,7 +41731,7 @@
       </c>
       <c r="R628" t="str">
         <f ca="1" t="shared" si="62"/>
-        <v>2025-01-25</v>
+        <v>2025-05-20</v>
       </c>
     </row>
     <row r="629" spans="1:18">
@@ -41789,7 +41789,7 @@
       </c>
       <c r="R629" t="str">
         <f ca="1" t="shared" si="62"/>
-        <v>2025-05-12</v>
+        <v>2025-01-05</v>
       </c>
     </row>
     <row r="630" spans="1:18">
@@ -41847,7 +41847,7 @@
       </c>
       <c r="R630" t="str">
         <f ca="1" t="shared" si="62"/>
-        <v>2025-09-09</v>
+        <v>2025-08-03</v>
       </c>
     </row>
     <row r="631" spans="1:18">
@@ -41905,7 +41905,7 @@
       </c>
       <c r="R631" t="str">
         <f ca="1" t="shared" si="62"/>
-        <v>2025-05-22</v>
+        <v>2024-08-28</v>
       </c>
     </row>
     <row r="632" spans="1:18">
@@ -41959,7 +41959,7 @@
       </c>
       <c r="R632" t="str">
         <f ca="1" t="shared" si="62"/>
-        <v>2025-04-12</v>
+        <v>2025-09-25</v>
       </c>
     </row>
     <row r="633" spans="1:18">
@@ -42016,8 +42016,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R633" t="str">
-        <f ca="1" t="shared" ref="R633:R642" si="63">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-08-05</v>
+        <f ca="1" t="shared" ref="R633:R642" si="63">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-04-17</v>
       </c>
     </row>
     <row r="634" spans="1:18">
@@ -42072,7 +42072,7 @@
       </c>
       <c r="R634" t="str">
         <f ca="1" t="shared" si="63"/>
-        <v>2025-09-09</v>
+        <v>2025-02-23</v>
       </c>
     </row>
     <row r="635" spans="1:18">
@@ -42127,7 +42127,7 @@
       </c>
       <c r="R635" t="str">
         <f ca="1" t="shared" si="63"/>
-        <v>2025-02-05</v>
+        <v>2025-02-21</v>
       </c>
     </row>
     <row r="636" spans="1:18">
@@ -42185,7 +42185,7 @@
       </c>
       <c r="R636" t="str">
         <f ca="1" t="shared" si="63"/>
-        <v>2025-04-21</v>
+        <v>2024-12-20</v>
       </c>
     </row>
     <row r="637" spans="1:18">
@@ -42243,7 +42243,7 @@
       </c>
       <c r="R637" t="str">
         <f ca="1" t="shared" si="63"/>
-        <v>2025-07-25</v>
+        <v>2025-04-02</v>
       </c>
     </row>
     <row r="638" spans="1:18">
@@ -42301,7 +42301,7 @@
       </c>
       <c r="R638" t="str">
         <f ca="1" t="shared" si="63"/>
-        <v>2025-05-08</v>
+        <v>2024-12-12</v>
       </c>
     </row>
     <row r="639" spans="1:18">
@@ -42355,7 +42355,7 @@
       </c>
       <c r="R639" t="str">
         <f ca="1" t="shared" si="63"/>
-        <v>2024-11-08</v>
+        <v>2025-07-15</v>
       </c>
     </row>
     <row r="640" spans="1:18">
@@ -42410,7 +42410,7 @@
       </c>
       <c r="R640" t="str">
         <f ca="1" t="shared" si="63"/>
-        <v>2024-12-27</v>
+        <v>2025-06-14</v>
       </c>
     </row>
     <row r="641" spans="1:18">
@@ -42468,7 +42468,7 @@
       </c>
       <c r="R641" t="str">
         <f ca="1" t="shared" si="63"/>
-        <v>2024-10-26</v>
+        <v>2025-05-01</v>
       </c>
     </row>
     <row r="642" spans="1:18">
@@ -42522,7 +42522,7 @@
       </c>
       <c r="R642" t="str">
         <f ca="1" t="shared" si="63"/>
-        <v>2024-10-10</v>
+        <v>2024-10-03</v>
       </c>
     </row>
     <row r="643" spans="1:18">
@@ -42579,8 +42579,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R643" t="str">
-        <f ca="1" t="shared" ref="R643:R652" si="64">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-09-04</v>
+        <f ca="1" t="shared" ref="R643:R652" si="64">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2024-08-06</v>
       </c>
     </row>
     <row r="644" spans="1:18">
@@ -42638,7 +42638,7 @@
       </c>
       <c r="R644" t="str">
         <f ca="1" t="shared" si="64"/>
-        <v>2024-08-12</v>
+        <v>2025-09-24</v>
       </c>
     </row>
     <row r="645" spans="1:18">
@@ -42692,7 +42692,7 @@
       </c>
       <c r="R645" t="str">
         <f ca="1" t="shared" si="64"/>
-        <v>2024-10-15</v>
+        <v>2025-01-20</v>
       </c>
     </row>
     <row r="646" spans="1:18">
@@ -42750,7 +42750,7 @@
       </c>
       <c r="R646" t="str">
         <f ca="1" t="shared" si="64"/>
-        <v>2025-07-13</v>
+        <v>2025-09-15</v>
       </c>
     </row>
     <row r="647" spans="1:18">
@@ -42807,7 +42807,7 @@
       </c>
       <c r="R647" t="str">
         <f ca="1" t="shared" si="64"/>
-        <v>2025-08-18</v>
+        <v>2024-08-05</v>
       </c>
     </row>
     <row r="648" spans="1:18">
@@ -42861,7 +42861,7 @@
       </c>
       <c r="R648" t="str">
         <f ca="1" t="shared" si="64"/>
-        <v>2024-09-26</v>
+        <v>2025-08-01</v>
       </c>
     </row>
     <row r="649" spans="1:18">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="R649" t="str">
         <f ca="1" t="shared" si="64"/>
-        <v>2025-07-21</v>
+        <v>2025-07-28</v>
       </c>
     </row>
     <row r="650" spans="1:18">
@@ -42977,7 +42977,7 @@
       </c>
       <c r="R650" t="str">
         <f ca="1" t="shared" si="64"/>
-        <v>2025-01-25</v>
+        <v>2025-10-04</v>
       </c>
     </row>
     <row r="651" spans="1:18">
@@ -43035,7 +43035,7 @@
       </c>
       <c r="R651" t="str">
         <f ca="1" t="shared" si="64"/>
-        <v>2025-06-11</v>
+        <v>2024-08-17</v>
       </c>
     </row>
     <row r="652" spans="1:18">
@@ -43089,7 +43089,7 @@
       </c>
       <c r="R652" t="str">
         <f ca="1" t="shared" si="64"/>
-        <v>2024-09-21</v>
+        <v>2025-07-28</v>
       </c>
     </row>
     <row r="653" spans="1:18">
@@ -43145,8 +43145,8 @@
         <v>138</v>
       </c>
       <c r="R653" t="str">
-        <f ca="1" t="shared" ref="R653:R662" si="65">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-10-25</v>
+        <f ca="1" t="shared" ref="R653:R662" si="65">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2024-09-20</v>
       </c>
     </row>
     <row r="654" spans="1:18">
@@ -43200,7 +43200,7 @@
       </c>
       <c r="R654" t="str">
         <f ca="1" t="shared" si="65"/>
-        <v>2024-08-15</v>
+        <v>2024-09-24</v>
       </c>
     </row>
     <row r="655" spans="1:18">
@@ -43257,7 +43257,7 @@
       </c>
       <c r="R655" t="str">
         <f ca="1" t="shared" si="65"/>
-        <v>2025-03-16</v>
+        <v>2025-09-03</v>
       </c>
     </row>
     <row r="656" spans="1:18">
@@ -43315,7 +43315,7 @@
       </c>
       <c r="R656" t="str">
         <f ca="1" t="shared" si="65"/>
-        <v>2025-04-11</v>
+        <v>2025-06-10</v>
       </c>
     </row>
     <row r="657" spans="1:18">
@@ -43373,7 +43373,7 @@
       </c>
       <c r="R657" t="str">
         <f ca="1" t="shared" si="65"/>
-        <v>2025-05-27</v>
+        <v>2024-08-31</v>
       </c>
     </row>
     <row r="658" spans="1:18">
@@ -43431,7 +43431,7 @@
       </c>
       <c r="R658" t="str">
         <f ca="1" t="shared" si="65"/>
-        <v>2025-02-08</v>
+        <v>2025-04-13</v>
       </c>
     </row>
     <row r="659" spans="1:18">
@@ -43486,7 +43486,7 @@
       </c>
       <c r="R659" t="str">
         <f ca="1" t="shared" si="65"/>
-        <v>2025-08-04</v>
+        <v>2024-12-05</v>
       </c>
     </row>
     <row r="660" spans="1:18">
@@ -43540,7 +43540,7 @@
       </c>
       <c r="R660" t="str">
         <f ca="1" t="shared" si="65"/>
-        <v>2025-01-22</v>
+        <v>2025-03-27</v>
       </c>
     </row>
     <row r="661" spans="1:18">
@@ -43594,7 +43594,7 @@
       </c>
       <c r="R661" t="str">
         <f ca="1" t="shared" si="65"/>
-        <v>2025-03-27</v>
+        <v>2025-06-26</v>
       </c>
     </row>
     <row r="662" spans="1:18">
@@ -43652,7 +43652,7 @@
       </c>
       <c r="R662" t="str">
         <f ca="1" t="shared" si="65"/>
-        <v>2024-08-03</v>
+        <v>2025-07-06</v>
       </c>
     </row>
     <row r="663" spans="1:18">
@@ -43709,8 +43709,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R663" t="str">
-        <f ca="1" t="shared" ref="R663:R672" si="66">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-09-10</v>
+        <f ca="1" t="shared" ref="R663:R672" si="66">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-08-04</v>
       </c>
     </row>
     <row r="664" spans="1:18">
@@ -43764,7 +43764,7 @@
       </c>
       <c r="R664" t="str">
         <f ca="1" t="shared" si="66"/>
-        <v>2025-09-13</v>
+        <v>2025-10-10</v>
       </c>
     </row>
     <row r="665" spans="1:18">
@@ -43822,7 +43822,7 @@
       </c>
       <c r="R665" t="str">
         <f ca="1" t="shared" si="66"/>
-        <v>2025-07-04</v>
+        <v>2025-04-21</v>
       </c>
     </row>
     <row r="666" spans="1:18">
@@ -43876,7 +43876,7 @@
       </c>
       <c r="R666" t="str">
         <f ca="1" t="shared" si="66"/>
-        <v>2024-10-12</v>
+        <v>2025-05-30</v>
       </c>
     </row>
     <row r="667" spans="1:18">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="R667" t="str">
         <f ca="1" t="shared" si="66"/>
-        <v>2025-07-13</v>
+        <v>2025-02-12</v>
       </c>
     </row>
     <row r="668" spans="1:18">
@@ -43988,7 +43988,7 @@
       </c>
       <c r="R668" t="str">
         <f ca="1" t="shared" si="66"/>
-        <v>2024-08-23</v>
+        <v>2025-11-04</v>
       </c>
     </row>
     <row r="669" spans="1:18">
@@ -44042,7 +44042,7 @@
       </c>
       <c r="R669" t="str">
         <f ca="1" t="shared" si="66"/>
-        <v>2024-10-14</v>
+        <v>2025-09-23</v>
       </c>
     </row>
     <row r="670" spans="1:18">
@@ -44096,7 +44096,7 @@
       </c>
       <c r="R670" t="str">
         <f ca="1" t="shared" si="66"/>
-        <v>2025-09-30</v>
+        <v>2024-12-09</v>
       </c>
     </row>
     <row r="671" spans="1:18">
@@ -44154,7 +44154,7 @@
       </c>
       <c r="R671" t="str">
         <f ca="1" t="shared" si="66"/>
-        <v>2024-11-14</v>
+        <v>2025-09-18</v>
       </c>
     </row>
     <row r="672" spans="1:18">
@@ -44212,7 +44212,7 @@
       </c>
       <c r="R672" t="str">
         <f ca="1" t="shared" si="66"/>
-        <v>2025-09-18</v>
+        <v>2024-08-30</v>
       </c>
     </row>
     <row r="673" spans="1:18">
@@ -44269,8 +44269,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R673" t="str">
-        <f ca="1" t="shared" ref="R673:R682" si="67">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-03-07</v>
+        <f ca="1" t="shared" ref="R673:R682" si="67">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-05-20</v>
       </c>
     </row>
     <row r="674" spans="1:18">
@@ -44328,7 +44328,7 @@
       </c>
       <c r="R674" t="str">
         <f ca="1" t="shared" si="67"/>
-        <v>2025-08-23</v>
+        <v>2025-09-12</v>
       </c>
     </row>
     <row r="675" spans="1:18">
@@ -44386,7 +44386,7 @@
       </c>
       <c r="R675" t="str">
         <f ca="1" t="shared" si="67"/>
-        <v>2025-02-25</v>
+        <v>2024-08-29</v>
       </c>
     </row>
     <row r="676" spans="1:18">
@@ -44444,7 +44444,7 @@
       </c>
       <c r="R676" t="str">
         <f ca="1" t="shared" si="67"/>
-        <v>2025-03-15</v>
+        <v>2024-08-07</v>
       </c>
     </row>
     <row r="677" spans="1:18">
@@ -44498,7 +44498,7 @@
       </c>
       <c r="R677" t="str">
         <f ca="1" t="shared" si="67"/>
-        <v>2025-08-25</v>
+        <v>2025-04-27</v>
       </c>
     </row>
     <row r="678" spans="1:18">
@@ -44556,7 +44556,7 @@
       </c>
       <c r="R678" t="str">
         <f ca="1" t="shared" si="67"/>
-        <v>2024-10-11</v>
+        <v>2025-04-26</v>
       </c>
     </row>
     <row r="679" spans="1:18">
@@ -44614,7 +44614,7 @@
       </c>
       <c r="R679" t="str">
         <f ca="1" t="shared" si="67"/>
-        <v>2024-09-21</v>
+        <v>2024-11-12</v>
       </c>
     </row>
     <row r="680" spans="1:18">
@@ -44668,7 +44668,7 @@
       </c>
       <c r="R680" t="str">
         <f ca="1" t="shared" si="67"/>
-        <v>2024-10-07</v>
+        <v>2024-11-05</v>
       </c>
     </row>
     <row r="681" spans="1:18">
@@ -44726,7 +44726,7 @@
       </c>
       <c r="R681" t="str">
         <f ca="1" t="shared" si="67"/>
-        <v>2024-10-16</v>
+        <v>2025-03-01</v>
       </c>
     </row>
     <row r="682" spans="1:18">
@@ -44783,7 +44783,7 @@
       </c>
       <c r="R682" t="str">
         <f ca="1" t="shared" si="67"/>
-        <v>2025-07-08</v>
+        <v>2025-01-16</v>
       </c>
     </row>
     <row r="683" spans="1:18">
@@ -44836,8 +44836,8 @@
         <v>33</v>
       </c>
       <c r="R683" t="str">
-        <f ca="1" t="shared" ref="R683:R692" si="68">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-09-11</v>
+        <f ca="1" t="shared" ref="R683:R692" si="68">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2024-12-11</v>
       </c>
     </row>
     <row r="684" spans="1:18">
@@ -44895,7 +44895,7 @@
       </c>
       <c r="R684" t="str">
         <f ca="1" t="shared" si="68"/>
-        <v>2024-08-13</v>
+        <v>2025-09-23</v>
       </c>
     </row>
     <row r="685" spans="1:18">
@@ -44952,7 +44952,7 @@
       </c>
       <c r="R685" t="str">
         <f ca="1" t="shared" si="68"/>
-        <v>2025-09-12</v>
+        <v>2025-11-06</v>
       </c>
     </row>
     <row r="686" spans="1:18">
@@ -45010,7 +45010,7 @@
       </c>
       <c r="R686" t="str">
         <f ca="1" t="shared" si="68"/>
-        <v>2024-12-31</v>
+        <v>2025-05-05</v>
       </c>
     </row>
     <row r="687" spans="1:18">
@@ -45068,7 +45068,7 @@
       </c>
       <c r="R687" t="str">
         <f ca="1" t="shared" si="68"/>
-        <v>2025-04-19</v>
+        <v>2025-07-19</v>
       </c>
     </row>
     <row r="688" spans="1:18">
@@ -45122,7 +45122,7 @@
       </c>
       <c r="R688" t="str">
         <f ca="1" t="shared" si="68"/>
-        <v>2025-03-14</v>
+        <v>2025-05-29</v>
       </c>
     </row>
     <row r="689" spans="1:18">
@@ -45176,7 +45176,7 @@
       </c>
       <c r="R689" t="str">
         <f ca="1" t="shared" si="68"/>
-        <v>2024-10-10</v>
+        <v>2025-03-26</v>
       </c>
     </row>
     <row r="690" spans="1:18">
@@ -45230,7 +45230,7 @@
       </c>
       <c r="R690" t="str">
         <f ca="1" t="shared" si="68"/>
-        <v>2025-02-07</v>
+        <v>2025-09-15</v>
       </c>
     </row>
     <row r="691" spans="1:18">
@@ -45284,7 +45284,7 @@
       </c>
       <c r="R691" t="str">
         <f ca="1" t="shared" si="68"/>
-        <v>2025-03-28</v>
+        <v>2025-07-04</v>
       </c>
     </row>
     <row r="692" spans="1:18">
@@ -45342,7 +45342,7 @@
       </c>
       <c r="R692" t="str">
         <f ca="1" t="shared" si="68"/>
-        <v>2025-01-28</v>
+        <v>2025-09-28</v>
       </c>
     </row>
     <row r="693" spans="1:18">
@@ -45399,8 +45399,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R693" t="str">
-        <f ca="1" t="shared" ref="R693:R702" si="69">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2024-09-29</v>
+        <f ca="1" t="shared" ref="R693:R702" si="69">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-05-09</v>
       </c>
     </row>
     <row r="694" spans="1:18">
@@ -45458,7 +45458,7 @@
       </c>
       <c r="R694" t="str">
         <f ca="1" t="shared" si="69"/>
-        <v>2025-07-14</v>
+        <v>2024-12-16</v>
       </c>
     </row>
     <row r="695" spans="1:18">
@@ -45516,7 +45516,7 @@
       </c>
       <c r="R695" t="str">
         <f ca="1" t="shared" si="69"/>
-        <v>2024-09-10</v>
+        <v>2025-06-29</v>
       </c>
     </row>
     <row r="696" spans="1:18">
@@ -45570,7 +45570,7 @@
       </c>
       <c r="R696" t="str">
         <f ca="1" t="shared" si="69"/>
-        <v>2025-06-05</v>
+        <v>2024-10-29</v>
       </c>
     </row>
     <row r="697" spans="1:18">
@@ -45627,7 +45627,7 @@
       </c>
       <c r="R697" t="str">
         <f ca="1" t="shared" si="69"/>
-        <v>2024-12-12</v>
+        <v>2025-06-23</v>
       </c>
     </row>
     <row r="698" spans="1:18">
@@ -45685,7 +45685,7 @@
       </c>
       <c r="R698" t="str">
         <f ca="1" t="shared" si="69"/>
-        <v>2025-08-02</v>
+        <v>2025-07-14</v>
       </c>
     </row>
     <row r="699" spans="1:18">
@@ -45743,7 +45743,7 @@
       </c>
       <c r="R699" t="str">
         <f ca="1" t="shared" si="69"/>
-        <v>2025-07-08</v>
+        <v>2025-08-04</v>
       </c>
     </row>
     <row r="700" spans="1:18">
@@ -45801,7 +45801,7 @@
       </c>
       <c r="R700" t="str">
         <f ca="1" t="shared" si="69"/>
-        <v>2025-04-19</v>
+        <v>2025-08-30</v>
       </c>
     </row>
     <row r="701" spans="1:18">
@@ -45859,7 +45859,7 @@
       </c>
       <c r="R701" t="str">
         <f ca="1" t="shared" si="69"/>
-        <v>2025-09-08</v>
+        <v>2025-04-15</v>
       </c>
     </row>
     <row r="702" spans="1:18">
@@ -45917,7 +45917,7 @@
       </c>
       <c r="R702" t="str">
         <f ca="1" t="shared" si="69"/>
-        <v>2025-08-02</v>
+        <v>2025-06-11</v>
       </c>
     </row>
     <row r="703" spans="1:18">
@@ -45974,8 +45974,8 @@
         <v>#NAME?</v>
       </c>
       <c r="R703" t="str">
-        <f ca="1" t="shared" ref="R703:R710" si="70">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,10,8)),"yyyy-mm-dd")</f>
-        <v>2025-02-24</v>
+        <f ca="1" t="shared" ref="R703:R710" si="70">TEXT(RANDBETWEEN(DATE(2024,8,1),DATE(2025,12,3)),"yyyy-mm-dd")</f>
+        <v>2025-10-08</v>
       </c>
     </row>
     <row r="704" spans="1:18">
@@ -46033,7 +46033,7 @@
       </c>
       <c r="R704" t="str">
         <f ca="1" t="shared" si="70"/>
-        <v>2025-03-29</v>
+        <v>2025-10-04</v>
       </c>
     </row>
     <row r="705" spans="1:18">
@@ -46091,7 +46091,7 @@
       </c>
       <c r="R705" t="str">
         <f ca="1" t="shared" si="70"/>
-        <v>2024-12-18</v>
+        <v>2024-12-17</v>
       </c>
     </row>
     <row r="706" spans="1:18">
@@ -46149,7 +46149,7 @@
       </c>
       <c r="R706" t="str">
         <f ca="1" t="shared" si="70"/>
-        <v>2025-08-14</v>
+        <v>2024-09-05</v>
       </c>
     </row>
     <row r="707" spans="1:18">
@@ -46207,7 +46207,7 @@
       </c>
       <c r="R707" t="str">
         <f ca="1" t="shared" si="70"/>
-        <v>2025-04-12</v>
+        <v>2025-10-08</v>
       </c>
     </row>
     <row r="708" spans="1:18">
@@ -46265,7 +46265,7 @@
       </c>
       <c r="R708" t="str">
         <f ca="1" t="shared" si="70"/>
-        <v>2025-09-16</v>
+        <v>2025-08-27</v>
       </c>
     </row>
     <row r="709" spans="1:18">
@@ -46319,7 +46319,7 @@
       </c>
       <c r="R709" t="str">
         <f ca="1" t="shared" si="70"/>
-        <v>2024-12-06</v>
+        <v>2024-12-08</v>
       </c>
     </row>
     <row r="710" spans="1:18">
@@ -46377,7 +46377,7 @@
       </c>
       <c r="R710" t="str">
         <f ca="1" t="shared" si="70"/>
-        <v>2025-09-16</v>
+        <v>2025-10-26</v>
       </c>
     </row>
   </sheetData>
